--- a/youtube-world-history-research/output/video_analysis_sheet_filled.xlsx
+++ b/youtube-world-history-research/output/video_analysis_sheet_filled.xlsx
@@ -16,7 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+  </numFmts>
   <fonts count="3">
     <font>
       <name val="Calibri"/>
@@ -63,7 +65,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -72,6 +74,12 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -442,17 +450,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:K31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="44" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
-    <col width="30" customWidth="1" min="7" max="7"/>
-    <col width="36" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="36" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -468,30 +479,45 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>登録者数</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>動画タイトル</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>動画URL</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>再生数</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>再生数÷登録者数</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>誰に向けた動画か</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>見たら何が得られると約束しているか</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>どんな感情を動かしているか（驚き・不安・好奇心など）</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>サムネの構図・文字数・色・人物の表情</t>
         </is>
@@ -508,32 +534,41 @@
           <t>https://www.youtube.com/@sekaishi_ura</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="4" t="n">
+        <v>263000</v>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>なぜ最強だったはずのモンゴル帝国は ヨーロッパを侵略できなかったのか？【歴史解説】</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=y0cwR7ttIaY</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="F2" s="4" t="n">
+        <v>549553</v>
+      </c>
+      <c r="G2" s="5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H2" s="6" t="inlineStr">
         <is>
           <t>モンゴル帝国の強さは知っているが、その限界は知らない歴史・戦争好きの大人</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="I2" s="6" t="inlineStr">
         <is>
           <t>「最強」のモンゴルがヨーロッパで止まった本当の理由（地理・補給・政治事情）がわかる</t>
         </is>
       </c>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="J2" s="6" t="inlineStr">
         <is>
           <t>好奇心（最強なのになぜ？という矛盾）、意外性</t>
         </is>
       </c>
-      <c r="H2" s="4" t="inlineStr">
+      <c r="K2" s="6" t="inlineStr">
         <is>
           <t>【未確認】モンゴル騎兵とヨーロッパ（騎士・城）を対比させているか／「なぜ止まった？」系の問いを文字にしているか</t>
         </is>
@@ -550,32 +585,41 @@
           <t>https://www.youtube.com/@sekaishi_ura</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="4" t="n">
+        <v>263000</v>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>【立場逆転】侵略しに来たのに狩られる側に…モンゴル目線で見る元寇の恐怖【歴史解説】</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=t_Kje4VAKiE</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="F3" s="4" t="n">
+        <v>1299382</v>
+      </c>
+      <c r="G3" s="5" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="H3" s="6" t="inlineStr">
         <is>
           <t>元寇を「神風で勝った」程度にしか知らない日本人全般</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="I3" s="6" t="inlineStr">
         <is>
           <t>攻めた側（モンゴル）の目線で見ると、日本の武士がどれほど恐ろしかったかがわかる</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="J3" s="6" t="inlineStr">
         <is>
           <t>立場が逆転する痛快さ、日本への誇らしさ、恐怖</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="K3" s="6" t="inlineStr">
         <is>
           <t>【未確認】怯えるモンゴル兵と武士の構図か／「狩られる側」など逆転を示す言葉があるか</t>
         </is>
@@ -592,32 +636,41 @@
           <t>https://www.youtube.com/@sekaishi_ura</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="4" t="n">
+        <v>263000</v>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>【恐怖】日本のバケモン海賊「倭寇」、さすがに厄介すぎる【歴史解説】</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=62_F5SjtZCM</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="F4" s="4" t="n">
+        <v>741800</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
         <is>
           <t>倭寇を教科書の単語でしか知らない日本人の歴史好き</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="I4" s="6" t="inlineStr">
         <is>
           <t>東アジアを荒らした「日本の海賊」の実態と、どれほど厄介だったかがわかる</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="J4" s="6" t="inlineStr">
         <is>
           <t>恐怖、「日本人がそこまで？」という驚きと少しの誇らしさ</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="K4" s="6" t="inlineStr">
         <is>
           <t>【未確認】凶悪な表情の海賊を大きく置いているか／「バケモン」のような強い言葉を文字にしているか</t>
         </is>
@@ -634,32 +687,41 @@
           <t>https://www.youtube.com/@sekaishi_ura</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" s="4" t="n">
+        <v>263000</v>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>街角の子供から戦場の兵士まで...世界を支配したコカ・コーラの歴史【歴史解説】</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=e-i5fvSbPM0</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="F5" s="4" t="n">
+        <v>278564</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
         <is>
           <t>歴史好きに限らない一般層。身近な商品の裏話が好きな人</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="I5" s="6" t="inlineStr">
         <is>
           <t>誰もが知るコカ・コーラが、子どもから戦場の兵士まで世界を支配するまでの歴史がわかる</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="J5" s="6" t="inlineStr">
         <is>
           <t>身近なものの意外性、好奇心</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="K5" s="6" t="inlineStr">
         <is>
           <t>【未確認】コーラ瓶などの商品を象徴的に大きく使っているか／戦場や兵士との組み合わせがあるか</t>
         </is>
@@ -676,32 +738,41 @@
           <t>https://www.youtube.com/@sekaishi_ura</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" s="4" t="n">
+        <v>263000</v>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>【総集編】犯罪者が建国し、凡ミスで滅亡...歴史上存在したヤバすぎる国たち【歴史解説】</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=_CE6EZ7nBWY</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="F6" s="4" t="n">
+        <v>409355</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
         <is>
           <t>作業中や寝る前に長く流したい歴史好き。チャンネルの既存視聴者</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="I6" s="6" t="inlineStr">
         <is>
           <t>犯罪者が作った国や凡ミスで滅んだ国など、ヤバい国の話を2時間近くまとめて楽しめる</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="J6" s="6" t="inlineStr">
         <is>
           <t>驚き、笑い（くだらなさ）、怖いもの見たさ</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="K6" s="6" t="inlineStr">
         <is>
           <t>【未確認】「総集編」の表示があるか／複数の国や人物をどう並べているか</t>
         </is>
@@ -718,32 +789,41 @@
           <t>https://www.youtube.com/@sekaishi_ura</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" s="4" t="n">
+        <v>263000</v>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>【致〇率99%】敵陣に最初に突入する兵士のモチベーションは何だったのか？【歴史解説】</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=lOGdA7_YDe0</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="F7" s="4" t="n">
+        <v>3214321</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
         <is>
           <t>戦争・軍事ものが好きな男性中心。歴史ファン以外まで広い層</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="I7" s="6" t="inlineStr">
         <is>
           <t>死亡率99%の突入役に人が志願した理由（報酬・名誉・制度）がわかる</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="J7" s="6" t="inlineStr">
         <is>
           <t>恐怖、「なぜそんなことを？」という疑問</t>
         </is>
       </c>
-      <c r="H7" s="4" t="inlineStr">
+      <c r="K7" s="6" t="inlineStr">
         <is>
           <t>【未確認】城壁にはしごで登る兵士など死地の場面か／「99%」の数字を大きく入れているか</t>
         </is>
@@ -760,32 +840,41 @@
           <t>https://www.youtube.com/@sekaishi_ura</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" s="4" t="n">
+        <v>263000</v>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>ビックリするほどしょーもない理由で滅亡した国３選【歴史解説】</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="E8" s="3" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=EXsFtJWLtLw</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="F8" s="4" t="n">
+        <v>414461</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
         <is>
           <t>気軽に歴史の雑学を楽しみたい層</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="I8" s="6" t="inlineStr">
         <is>
           <t>信じられないほどくだらない理由で国が滅んだ実例を3つ知れる</t>
         </is>
       </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="J8" s="6" t="inlineStr">
         <is>
           <t>笑い、「国が滅ぶ」と「しょーもない」の落差による驚き</t>
         </is>
       </c>
-      <c r="H8" s="4" t="inlineStr">
+      <c r="K8" s="6" t="inlineStr">
         <is>
           <t>【未確認】王や人物の脱力した表情など「しょーもなさ」をどう絵にしているか／「3選」を文字にしているか</t>
         </is>
@@ -802,32 +891,41 @@
           <t>https://www.youtube.com/@sekaishi_ura</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C9" s="4" t="n">
+        <v>263000</v>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>なぜ攻撃力最強のはずの機関銃は、軍人たちから嫌われまくっていたのか？【歴史解説】</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="E9" s="3" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=oqU0VDyQiUE</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="F9" s="4" t="n">
+        <v>317807</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
         <is>
           <t>兵器・軍事史が好きな層</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="I9" s="6" t="inlineStr">
         <is>
           <t>最強の兵器のはずの機関銃が、なぜ軍人たちに嫌われていたかがわかる</t>
         </is>
       </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="J9" s="6" t="inlineStr">
         <is>
           <t>矛盾への好奇心、意外性</t>
         </is>
       </c>
-      <c r="H9" s="4" t="inlineStr">
+      <c r="K9" s="6" t="inlineStr">
         <is>
           <t>【未確認】機関銃と、不満そうな軍人の表情を組み合わせているか</t>
         </is>
@@ -844,32 +942,41 @@
           <t>https://www.youtube.com/@sekaishi_ura</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C10" s="4" t="n">
+        <v>263000</v>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>「歩兵」が中世ヨーロッパの戦場を”地獄”に変えたと言われる理由【歴史解説】</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="E10" s="3" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=mMzDpd9NA38</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="F10" s="4" t="n">
+        <v>1516503</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
         <is>
           <t>中世ヨーロッパ・騎士・戦争が好きな層</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr">
+      <c r="I10" s="6" t="inlineStr">
         <is>
           <t>騎士が主役だった中世の戦争が、歩兵の台頭でなぜ地獄になったかがわかる</t>
         </is>
       </c>
-      <c r="G10" s="4" t="inlineStr">
+      <c r="J10" s="6" t="inlineStr">
         <is>
           <t>恐怖、騎士の時代が終わることへのロマン</t>
         </is>
       </c>
-      <c r="H10" s="4" t="inlineStr">
+      <c r="K10" s="6" t="inlineStr">
         <is>
           <t>【未確認】槍兵の密集陣や、騎士が倒される場面か／「地獄」の言葉を文字にしているか</t>
         </is>
@@ -886,32 +993,41 @@
           <t>https://www.youtube.com/@sekaishi_ura</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C11" s="4" t="n">
+        <v>263000</v>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>防御力最強のはずの「城塞都市」が日本で採用されなかった意外な理由【歴史解説】</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="E11" s="3" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=ebAl58P2JRc</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="F11" s="4" t="n">
+        <v>3164917</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
         <is>
           <t>日本と海外の比較が好きな、日本人の歴史好き全般</t>
         </is>
       </c>
-      <c r="F11" s="4" t="inlineStr">
+      <c r="I11" s="6" t="inlineStr">
         <is>
           <t>世界では当たり前の城塞都市が、なぜ日本では作られなかったかがわかる（日欧比較）</t>
         </is>
       </c>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="J11" s="6" t="inlineStr">
         <is>
           <t>「言われてみれば確かに」という好奇心、日本についての発見</t>
         </is>
       </c>
-      <c r="H11" s="4" t="inlineStr">
+      <c r="K11" s="6" t="inlineStr">
         <is>
           <t>【未確認】ヨーロッパの城壁都市と日本の城下町を並べた対比構図か</t>
         </is>
@@ -928,32 +1044,41 @@
           <t>https://www.youtube.com/@%E3%81%8A%E3%82%82%E3%81%97%E3%82%8D%E4%B8%96%E7%95%8C%E5%8F%B2%E3%83%A9%E3%83%9C</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C12" s="4" t="n">
+        <v>7160</v>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>なぜインドは「人口世界一」になったのか？14億人を生んだ最強の地形と残酷な歴史</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="E12" s="3" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=sky5rp3O0fg</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="F12" s="4" t="n">
+        <v>14759</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
         <is>
           <t>ニュースで「インドが人口世界一」と聞いた大人</t>
         </is>
       </c>
-      <c r="F12" s="4" t="inlineStr">
+      <c r="I12" s="6" t="inlineStr">
         <is>
           <t>14億人を生んだ地形と、その裏の残酷な歴史がわかる</t>
         </is>
       </c>
-      <c r="G12" s="4" t="inlineStr">
+      <c r="J12" s="6" t="inlineStr">
         <is>
           <t>好奇心、「残酷な歴史」への少しの不安</t>
         </is>
       </c>
-      <c r="H12" s="4" t="inlineStr">
+      <c r="K12" s="6" t="inlineStr">
         <is>
           <t>【未確認】インドの地図や人の多さを見せているか／「14億」の数字を入れているか</t>
         </is>
@@ -970,32 +1095,41 @@
           <t>https://www.youtube.com/@%E3%81%8A%E3%82%82%E3%81%97%E3%82%8D%E4%B8%96%E7%95%8C%E5%8F%B2%E3%83%A9%E3%83%9C</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C13" s="4" t="n">
+        <v>7160</v>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>【驚愕の地理】日本より細長い国が存在した！？チリ・ノルウェー・ベトナムが抱える過酷な宿命と驚きの共通点</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="E13" s="3" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=_rEy7JfXiKE</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="F13" s="4" t="n">
+        <v>10723</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
         <is>
           <t>地図や地理の雑学が好きな人</t>
         </is>
       </c>
-      <c r="F13" s="4" t="inlineStr">
+      <c r="I13" s="6" t="inlineStr">
         <is>
           <t>チリ・ノルウェー・ベトナムが細長い理由と、3国の意外な共通点がわかる</t>
         </is>
       </c>
-      <c r="G13" s="4" t="inlineStr">
+      <c r="J13" s="6" t="inlineStr">
         <is>
           <t>驚き、地図を眺める楽しさ</t>
         </is>
       </c>
-      <c r="H13" s="4" t="inlineStr">
+      <c r="K13" s="6" t="inlineStr">
         <is>
           <t>【未確認】3つの国の形を並べて見せているか</t>
         </is>
@@ -1012,32 +1146,41 @@
           <t>https://www.youtube.com/@%E3%81%8A%E3%82%82%E3%81%97%E3%82%8D%E4%B8%96%E7%95%8C%E5%8F%B2%E3%83%A9%E3%83%9C</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C14" s="4" t="n">
+        <v>7160</v>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>【大人の歴史物語】なぜ北米の巨大な島「グリーンランド」は、遠く離れたデンマーク領なのか？ 〜嘘と勘違いから始まった数奇な運命〜</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="E14" s="3" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=b8Hy-06K0mY</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="F14" s="4" t="n">
+        <v>43346</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
         <is>
           <t>時事ニュースでグリーンランドの名前を聞いた大人。地図を見て疑問に思ったことがある人</t>
         </is>
       </c>
-      <c r="F14" s="4" t="inlineStr">
+      <c r="I14" s="6" t="inlineStr">
         <is>
           <t>北米にある巨大な島が、なぜ遠いデンマークの領土なのかがわかる</t>
         </is>
       </c>
-      <c r="G14" s="4" t="inlineStr">
+      <c r="J14" s="6" t="inlineStr">
         <is>
           <t>素朴な疑問が解ける好奇心、「嘘と勘違い」という意外な経緯への興味</t>
         </is>
       </c>
-      <c r="H14" s="4" t="inlineStr">
+      <c r="K14" s="6" t="inlineStr">
         <is>
           <t>【未確認】地図上でグリーンランドとデンマークの距離を見せているか</t>
         </is>
@@ -1054,32 +1197,41 @@
           <t>https://www.youtube.com/@%E3%81%8A%E3%82%82%E3%81%97%E3%82%8D%E4%B8%96%E7%95%8C%E5%8F%B2%E3%83%A9%E3%83%9C</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C15" s="4" t="n">
+        <v>7160</v>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>【地政学と歴史】中国はなぜ日本海に出られないのか？ロシアに奪われた「15kmの壁」の真実</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="E15" s="3" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=0fQNhKQyVcg</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="F15" s="4" t="n">
+        <v>9957</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
         <is>
           <t>地政学や国際ニュースに関心がある日本人</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr">
+      <c r="I15" s="6" t="inlineStr">
         <is>
           <t>中国が日本海に出られない「15kmの壁」の歴史的な経緯がわかる</t>
         </is>
       </c>
-      <c r="G15" s="4" t="inlineStr">
+      <c r="J15" s="6" t="inlineStr">
         <is>
           <t>驚き、日本の安全保障に関わることへの関心</t>
         </is>
       </c>
-      <c r="H15" s="4" t="inlineStr">
+      <c r="K15" s="6" t="inlineStr">
         <is>
           <t>【未確認】問題の15km部分を地図で拡大しているか</t>
         </is>
@@ -1096,32 +1248,41 @@
           <t>https://www.youtube.com/@%E3%81%8A%E3%82%82%E3%81%97%E3%82%8D%E4%B8%96%E7%95%8C%E5%8F%B2%E3%83%A9%E3%83%9C</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C16" s="4" t="n">
+        <v>7160</v>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>なぜ中央アジアは「5つのスタン」に分かれたのか？【シルクロードの真実】</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="E16" s="3" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=L1HApBYXYaw</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
+      <c r="F16" s="4" t="n">
+        <v>145756</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
         <is>
           <t>「〜スタン」という国が多いことを不思議に思ったことがある人</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr">
+      <c r="I16" s="6" t="inlineStr">
         <is>
           <t>中央アジアが5つの国に分かれた理由がわかる</t>
         </is>
       </c>
-      <c r="G16" s="4" t="inlineStr">
+      <c r="J16" s="6" t="inlineStr">
         <is>
           <t>素朴な疑問が解ける好奇心</t>
         </is>
       </c>
-      <c r="H16" s="4" t="inlineStr">
+      <c r="K16" s="6" t="inlineStr">
         <is>
           <t>【未確認】5か国の地図や国旗を並べているか</t>
         </is>
@@ -1138,32 +1299,41 @@
           <t>https://www.youtube.com/@%E3%81%8A%E3%82%82%E3%81%97%E3%82%8D%E4%B8%96%E7%95%8C%E5%8F%B2%E3%83%A9%E3%83%9C</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C17" s="4" t="n">
+        <v>7160</v>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>ロシア最大の痛恨…なぜ「世界最大の宝の山」を手放したのか？坪単価0.2円で売られたアラスカの悲劇と歴史の皮肉</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="E17" s="3" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=YgU5vvbNHFc</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="F17" s="4" t="n">
+        <v>117755</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
         <is>
           <t>歴史や地政学の「損得」の話が好きな人</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="I17" s="6" t="inlineStr">
         <is>
           <t>ロシアがアラスカを安値で手放した理由と、その後の皮肉な結末がわかる</t>
         </is>
       </c>
-      <c r="G17" s="4" t="inlineStr">
+      <c r="J17" s="6" t="inlineStr">
         <is>
           <t>「もったいない」という驚き、皮肉の面白さ</t>
         </is>
       </c>
-      <c r="H17" s="4" t="inlineStr">
+      <c r="K17" s="6" t="inlineStr">
         <is>
           <t>【未確認】「0.2円」など値段の数字を大きく入れているか／ロシアとアメリカを対比しているか</t>
         </is>
@@ -1180,32 +1350,41 @@
           <t>https://www.youtube.com/@%E3%81%8A%E3%82%82%E3%81%97%E3%82%8D%E4%B8%96%E7%95%8C%E5%8F%B2%E3%83%A9%E3%83%9C</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C18" s="4" t="n">
+        <v>7160</v>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>一見すると双子なのに…オランダとベルギーはなぜ「別の国」になったのか？【引き裂かれた歴史】</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="E18" s="3" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=WTxwe4d4qXM</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
+      <c r="F18" s="4" t="n">
+        <v>231422</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
         <is>
           <t>似ている国の違いが気になる人、ヨーロッパ旅行が好きな人</t>
         </is>
       </c>
-      <c r="F18" s="4" t="inlineStr">
+      <c r="I18" s="6" t="inlineStr">
         <is>
           <t>双子のように似たオランダとベルギーが、なぜ別の国になったかがわかる</t>
         </is>
       </c>
-      <c r="G18" s="4" t="inlineStr">
+      <c r="J18" s="6" t="inlineStr">
         <is>
           <t>好奇心、「引き裂かれた」というドラマ性</t>
         </is>
       </c>
-      <c r="H18" s="4" t="inlineStr">
+      <c r="K18" s="6" t="inlineStr">
         <is>
           <t>【未確認】2国の国旗や地図を並べているか</t>
         </is>
@@ -1222,32 +1401,41 @@
           <t>https://www.youtube.com/@%E3%81%8A%E3%82%82%E3%81%97%E3%82%8D%E4%B8%96%E7%95%8C%E5%8F%B2%E3%83%A9%E3%83%9C</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="C19" s="4" t="n">
+        <v>7160</v>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>国旗も言葉もほぼ同じなのに…北欧が「一つの国」になれなかった理由</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr">
+      <c r="E19" s="3" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=rJqy3SXia3Y</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="F19" s="4" t="n">
+        <v>376231</v>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
         <is>
           <t>北欧が好きな人、ヨーロッパに興味がある大人</t>
         </is>
       </c>
-      <c r="F19" s="4" t="inlineStr">
+      <c r="I19" s="6" t="inlineStr">
         <is>
           <t>国旗も言葉も似ている北欧の国々が、なぜ一つの国にならなかったかがわかる</t>
         </is>
       </c>
-      <c r="G19" s="4" t="inlineStr">
+      <c r="J19" s="6" t="inlineStr">
         <is>
           <t>好奇心、似ているのに別々という意外性</t>
         </is>
       </c>
-      <c r="H19" s="4" t="inlineStr">
+      <c r="K19" s="6" t="inlineStr">
         <is>
           <t>【未確認】よく似た北欧の国旗を並べて見せているか</t>
         </is>
@@ -1264,32 +1452,41 @@
           <t>https://www.youtube.com/@%E3%81%8A%E3%82%82%E3%81%97%E3%82%8D%E4%B8%96%E7%95%8C%E5%8F%B2%E3%83%A9%E3%83%9C</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="C20" s="4" t="n">
+        <v>7160</v>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>一つ屋根の下に二つの家族？イベリア半島が「２つに分かれた」歴史の裏側</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr">
+      <c r="E20" s="3" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=dkrkDvQjz-4</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
+      <c r="F20" s="4" t="n">
+        <v>221200</v>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
         <is>
           <t>スペインやポルトガルに興味がある人</t>
         </is>
       </c>
-      <c r="F20" s="4" t="inlineStr">
+      <c r="I20" s="6" t="inlineStr">
         <is>
           <t>同じ半島にあるスペインとポルトガルが、なぜ2つに分かれたかがわかる</t>
         </is>
       </c>
-      <c r="G20" s="4" t="inlineStr">
+      <c r="J20" s="6" t="inlineStr">
         <is>
           <t>好奇心、「一つ屋根の下の二つの家族」というたとえによる親しみ</t>
         </is>
       </c>
-      <c r="H20" s="4" t="inlineStr">
+      <c r="K20" s="6" t="inlineStr">
         <is>
           <t>【未確認】半島の地図を2色に塗り分けているか</t>
         </is>
@@ -1306,32 +1503,41 @@
           <t>https://www.youtube.com/@%E3%81%8A%E3%82%82%E3%81%97%E3%82%8D%E4%B8%96%E7%95%8C%E5%8F%B2%E3%83%A9%E3%83%9C</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="C21" s="4" t="n">
+        <v>7160</v>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>同じ言語なのに、なぜ別の国？ドイツとオーストリアの複雑すぎる愛憎史</t>
         </is>
       </c>
-      <c r="D21" s="3" t="inlineStr">
+      <c r="E21" s="3" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=MIE3-uo--r4</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
+      <c r="F21" s="4" t="n">
+        <v>174273</v>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
         <is>
           <t>ドイツとオーストリアの違いが気になる人、ヨーロッパ史が好きな人</t>
         </is>
       </c>
-      <c r="F21" s="4" t="inlineStr">
+      <c r="I21" s="6" t="inlineStr">
         <is>
           <t>同じ言語なのに別の国である理由と、2国の愛憎の歴史がわかる</t>
         </is>
       </c>
-      <c r="G21" s="4" t="inlineStr">
+      <c r="J21" s="6" t="inlineStr">
         <is>
           <t>好奇心、愛憎ドラマへの興味</t>
         </is>
       </c>
-      <c r="H21" s="4" t="inlineStr">
+      <c r="K21" s="6" t="inlineStr">
         <is>
           <t>【未確認】2国の国旗や人物を対立させる構図か</t>
         </is>
@@ -1348,32 +1554,41 @@
           <t>https://www.youtube.com/@hello-senjo</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="C22" s="4" t="n">
+        <v>19600</v>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>ヘルマン・ゲーリング｜残酷すぎる最期。53歳で死去したヒトラーの後継者【第二次世界大戦】</t>
         </is>
       </c>
-      <c r="D22" s="3" t="inlineStr">
+      <c r="E22" s="3" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=BtAGQokhyUE</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr">
+      <c r="F22" s="4" t="n">
+        <v>81175</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H22" s="6" t="inlineStr">
         <is>
           <t>第二次世界大戦やナチスに興味がある層</t>
         </is>
       </c>
-      <c r="F22" s="4" t="inlineStr">
+      <c r="I22" s="6" t="inlineStr">
         <is>
           <t>ヒトラーの後継者だったゲーリングが、どんな最期を迎えたかがわかる</t>
         </is>
       </c>
-      <c r="G22" s="4" t="inlineStr">
+      <c r="J22" s="6" t="inlineStr">
         <is>
           <t>怖いもの見たさ、因果応報への関心</t>
         </is>
       </c>
-      <c r="H22" s="4" t="inlineStr">
+      <c r="K22" s="6" t="inlineStr">
         <is>
           <t>【未確認】人物の顔を大きく置いているか／「最期」「53歳」などの文字があるか</t>
         </is>
@@ -1390,32 +1605,41 @@
           <t>https://www.youtube.com/@hello-senjo</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="C23" s="4" t="n">
+        <v>19600</v>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>イルマ・グレーゼ｜22歳で処刑された悪魔。ナチスが最も恐れた女の残酷すぎる最期【第二次世界大戦】</t>
         </is>
       </c>
-      <c r="D23" s="3" t="inlineStr">
+      <c r="E23" s="3" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=XBXVSbh4w1k</t>
         </is>
       </c>
-      <c r="E23" s="4" t="inlineStr">
+      <c r="F23" s="4" t="n">
+        <v>576986</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="H23" s="6" t="inlineStr">
         <is>
           <t>第二次世界大戦・ナチスに興味がある層、「悪女」や事件ものが好きな層</t>
         </is>
       </c>
-      <c r="F23" s="4" t="inlineStr">
+      <c r="I23" s="6" t="inlineStr">
         <is>
           <t>22歳で処刑されたナチスの女性看守が、何をして、どう最期を迎えたかがわかる</t>
         </is>
       </c>
-      <c r="G23" s="4" t="inlineStr">
+      <c r="J23" s="6" t="inlineStr">
         <is>
           <t>恐怖と嫌悪、「若い女性が」という意外性</t>
         </is>
       </c>
-      <c r="H23" s="4" t="inlineStr">
+      <c r="K23" s="6" t="inlineStr">
         <is>
           <t>【未確認】若い女性の顔写真を使っているか／「22歳」「悪魔」の文字があるか</t>
         </is>
@@ -1432,32 +1656,41 @@
           <t>https://www.youtube.com/@hello-senjo</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="C24" s="4" t="n">
+        <v>19600</v>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>ラインハルト・ハイドリヒ｜数百万人を虐殺した悪魔。ナチスが最も恐れた男の残酷すぎる最期【第二次世界大戦】</t>
         </is>
       </c>
-      <c r="D24" s="3" t="inlineStr">
+      <c r="E24" s="3" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=K4AcedCAqj4</t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr">
+      <c r="F24" s="4" t="n">
+        <v>147795</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="H24" s="6" t="inlineStr">
         <is>
           <t>第二次世界大戦・ナチスに興味がある層</t>
         </is>
       </c>
-      <c r="F24" s="4" t="inlineStr">
+      <c r="I24" s="6" t="inlineStr">
         <is>
           <t>数百万人の虐殺に関わったハイドリヒの人物像と、その最期がわかる</t>
         </is>
       </c>
-      <c r="G24" s="4" t="inlineStr">
+      <c r="J24" s="6" t="inlineStr">
         <is>
           <t>恐怖、悪人が裁かれるかどうかへの関心</t>
         </is>
       </c>
-      <c r="H24" s="4" t="inlineStr">
+      <c r="K24" s="6" t="inlineStr">
         <is>
           <t>【未確認】人物の顔と「悪魔」「最期」の文字の組み合わせか</t>
         </is>
@@ -1474,32 +1707,41 @@
           <t>https://www.youtube.com/@hello-senjo</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="C25" s="4" t="n">
+        <v>19600</v>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>毛沢東の最期！4500万人を殺した男の残酷すぎる44日間【第二次世界大戦】</t>
         </is>
       </c>
-      <c r="D25" s="3" t="inlineStr">
+      <c r="E25" s="3" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=UdZXaobRj_U</t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr">
+      <c r="F25" s="4" t="n">
+        <v>184827</v>
+      </c>
+      <c r="G25" s="5" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="H25" s="6" t="inlineStr">
         <is>
           <t>近現代史・独裁者に興味がある層</t>
         </is>
       </c>
-      <c r="F25" s="4" t="inlineStr">
+      <c r="I25" s="6" t="inlineStr">
         <is>
           <t>毛沢東が死ぬまでの44日間に何が起きたかがわかる</t>
         </is>
       </c>
-      <c r="G25" s="4" t="inlineStr">
+      <c r="J25" s="6" t="inlineStr">
         <is>
           <t>怖いもの見たさ、独裁者の結末への関心</t>
         </is>
       </c>
-      <c r="H25" s="4" t="inlineStr">
+      <c r="K25" s="6" t="inlineStr">
         <is>
           <t>【未確認】晩年の顔か／「44日間」「4500万人」の数字を入れているか</t>
         </is>
@@ -1516,32 +1758,41 @@
           <t>https://www.youtube.com/@hello-senjo</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="C26" s="4" t="n">
+        <v>19600</v>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>ラヴレンチー・ベリヤ｜数百万人を虐殺した悪魔。スターリンが絶賛したソ連の秘密警察長官【第二次世界大戦】</t>
         </is>
       </c>
-      <c r="D26" s="3" t="inlineStr">
+      <c r="E26" s="3" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=6KhwEtMg3-M</t>
         </is>
       </c>
-      <c r="E26" s="4" t="inlineStr">
+      <c r="F26" s="4" t="n">
+        <v>108893</v>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="H26" s="6" t="inlineStr">
         <is>
           <t>ソ連史・独裁体制に興味がある層</t>
         </is>
       </c>
-      <c r="F26" s="4" t="inlineStr">
+      <c r="I26" s="6" t="inlineStr">
         <is>
           <t>スターリンの右腕だった秘密警察長官ベリヤの正体と結末がわかる</t>
         </is>
       </c>
-      <c r="G26" s="4" t="inlineStr">
+      <c r="J26" s="6" t="inlineStr">
         <is>
           <t>恐怖、権力者の裏側への好奇心</t>
         </is>
       </c>
-      <c r="H26" s="4" t="inlineStr">
+      <c r="K26" s="6" t="inlineStr">
         <is>
           <t>【未確認】人物の顔とスターリンを並べているか</t>
         </is>
@@ -1558,32 +1809,41 @@
           <t>https://www.youtube.com/@hello-senjo</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
+      <c r="C27" s="4" t="n">
+        <v>19600</v>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>エルヴィン・ロンメル｜ヒトラーに殺された男。伝説の無敵将校「砂漠の狐」の残酷すぎる最期【第二次世界大戦】</t>
         </is>
       </c>
-      <c r="D27" s="3" t="inlineStr">
+      <c r="E27" s="3" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=b0K8lXRPE_g</t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr">
+      <c r="F27" s="4" t="n">
+        <v>184439</v>
+      </c>
+      <c r="G27" s="5" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="H27" s="6" t="inlineStr">
         <is>
           <t>第二次世界大戦の軍人・名将に興味がある層</t>
         </is>
       </c>
-      <c r="F27" s="4" t="inlineStr">
+      <c r="I27" s="6" t="inlineStr">
         <is>
           <t>「砂漠の狐」と呼ばれた名将ロンメルが、なぜヒトラーに殺されたかがわかる</t>
         </is>
       </c>
-      <c r="G27" s="4" t="inlineStr">
+      <c r="J27" s="6" t="inlineStr">
         <is>
           <t>悲劇への同情、英雄が裏切られる理不尽さへの怒り</t>
         </is>
       </c>
-      <c r="H27" s="4" t="inlineStr">
+      <c r="K27" s="6" t="inlineStr">
         <is>
           <t>【未確認】人物の顔と「ヒトラーに殺された」の文字があるか</t>
         </is>
@@ -1600,32 +1860,41 @@
           <t>https://www.youtube.com/@hello-senjo</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="C28" s="4" t="n">
+        <v>19600</v>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>アドルフ・アイヒマン｜500万人を殺した男。ナチスが最も恐れた男の残酷すぎる最期【第二次世界大戦】</t>
         </is>
       </c>
-      <c r="D28" s="3" t="inlineStr">
+      <c r="E28" s="3" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=bHrzNTlZntI</t>
         </is>
       </c>
-      <c r="E28" s="4" t="inlineStr">
+      <c r="F28" s="4" t="n">
+        <v>245871</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="H28" s="6" t="inlineStr">
         <is>
           <t>第二次世界大戦・ナチスに興味がある層</t>
         </is>
       </c>
-      <c r="F28" s="4" t="inlineStr">
+      <c r="I28" s="6" t="inlineStr">
         <is>
           <t>ユダヤ人移送を指揮したアイヒマンの人物像と、逃亡から処刑までの最期がわかる</t>
         </is>
       </c>
-      <c r="G28" s="4" t="inlineStr">
+      <c r="J28" s="6" t="inlineStr">
         <is>
           <t>恐怖、正義が下されるかどうかへの関心</t>
         </is>
       </c>
-      <c r="H28" s="4" t="inlineStr">
+      <c r="K28" s="6" t="inlineStr">
         <is>
           <t>【未確認】人物の顔と「500万人」の数字を入れているか</t>
         </is>
@@ -1642,32 +1911,41 @@
           <t>https://www.youtube.com/@hello-senjo</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
+      <c r="C29" s="4" t="n">
+        <v>19600</v>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>スターリンの最期！1000万人を殺した男の残酷すぎる7日間【第二次世界大戦】</t>
         </is>
       </c>
-      <c r="D29" s="3" t="inlineStr">
+      <c r="E29" s="3" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=Rqgbenusa_8</t>
         </is>
       </c>
-      <c r="E29" s="4" t="inlineStr">
+      <c r="F29" s="4" t="n">
+        <v>510806</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="H29" s="6" t="inlineStr">
         <is>
           <t>近現代史・独裁者に興味がある層</t>
         </is>
       </c>
-      <c r="F29" s="4" t="inlineStr">
+      <c r="I29" s="6" t="inlineStr">
         <is>
           <t>スターリンが倒れてから死ぬまでの7日間に何が起きたかがわかる</t>
         </is>
       </c>
-      <c r="G29" s="4" t="inlineStr">
+      <c r="J29" s="6" t="inlineStr">
         <is>
           <t>怖いもの見たさ、独裁者が見捨てられる皮肉</t>
         </is>
       </c>
-      <c r="H29" s="4" t="inlineStr">
+      <c r="K29" s="6" t="inlineStr">
         <is>
           <t>【未確認】人物の顔と「7日間」「1000万人」の数字があるか</t>
         </is>
@@ -1684,32 +1962,41 @@
           <t>https://www.youtube.com/@hello-senjo</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="C30" s="4" t="n">
+        <v>19600</v>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>ムッソリーニの最期！逆さ吊りで公開処刑されるまでの残酷すぎる10日間【第二次世界大戦】</t>
         </is>
       </c>
-      <c r="D30" s="3" t="inlineStr">
+      <c r="E30" s="3" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=ANxbHSdWPUg</t>
         </is>
       </c>
-      <c r="E30" s="4" t="inlineStr">
+      <c r="F30" s="4" t="n">
+        <v>210398</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="H30" s="6" t="inlineStr">
         <is>
           <t>第二次世界大戦・独裁者に興味がある層</t>
         </is>
       </c>
-      <c r="F30" s="4" t="inlineStr">
+      <c r="I30" s="6" t="inlineStr">
         <is>
           <t>ムッソリーニが逆さ吊りで公開処刑されるまでの10日間がわかる</t>
         </is>
       </c>
-      <c r="G30" s="4" t="inlineStr">
+      <c r="J30" s="6" t="inlineStr">
         <is>
           <t>衝撃、怖いもの見たさ</t>
         </is>
       </c>
-      <c r="H30" s="4" t="inlineStr">
+      <c r="K30" s="6" t="inlineStr">
         <is>
           <t>【未確認】人物の顔と「逆さ吊り」「10日間」の文字があるか</t>
         </is>
@@ -1726,32 +2013,41 @@
           <t>https://www.youtube.com/@hello-senjo</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="C31" s="4" t="n">
+        <v>19600</v>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>ヒトラーの最期！最恐独裁者の悲惨すぎる最後の48時間【第二次世界大戦】</t>
         </is>
       </c>
-      <c r="D31" s="3" t="inlineStr">
+      <c r="E31" s="3" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=PINVVV6JeGg</t>
         </is>
       </c>
-      <c r="E31" s="4" t="inlineStr">
+      <c r="F31" s="4" t="n">
+        <v>243970</v>
+      </c>
+      <c r="G31" s="5" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="H31" s="6" t="inlineStr">
         <is>
           <t>第二次世界大戦・ヒトラーに興味がある層（最も広い入口）</t>
         </is>
       </c>
-      <c r="F31" s="4" t="inlineStr">
+      <c r="I31" s="6" t="inlineStr">
         <is>
           <t>ヒトラーが死ぬまでの最後の48時間に、地下壕で何が起きていたかがわかる</t>
         </is>
       </c>
-      <c r="G31" s="4" t="inlineStr">
+      <c r="J31" s="6" t="inlineStr">
         <is>
           <t>怖いもの見たさ、緊迫感</t>
         </is>
       </c>
-      <c r="H31" s="4" t="inlineStr">
+      <c r="K31" s="6" t="inlineStr">
         <is>
           <t>【未確認】ヒトラーの顔と「48時間」の文字があるか</t>
         </is>
@@ -1760,65 +2056,65 @@
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B5" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D5" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B8" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D8" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D9" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D10" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D11" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D12" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D13" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B14" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D14" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B15" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D15" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B16" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D16" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B17" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D17" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B18" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D18" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId34"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B19" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D19" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B20" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D20" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B21" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D21" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId40"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B22" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D22" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId42"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B23" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D23" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId44"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B24" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D24" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId46"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B25" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D25" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId48"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B26" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D26" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId50"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B27" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D27" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId52"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B28" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D28" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId54"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B29" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D29" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId56"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B30" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D30" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId58"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B31" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D31" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId60"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/youtube-world-history-research/output/video_analysis_sheet_filled.xlsx
+++ b/youtube-world-history-research/output/video_analysis_sheet_filled.xlsx
@@ -479,7 +479,7 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>登録者数</t>
+          <t>登録者数（10/8〜9時点）</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
@@ -494,7 +494,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>再生数</t>
+          <t>再生数（10/15時点）</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">

--- a/youtube-world-history-research/output/video_analysis_sheet_filled.xlsx
+++ b/youtube-world-history-research/output/video_analysis_sheet_filled.xlsx
@@ -570,7 +570,11 @@
       </c>
       <c r="K2" s="6" t="inlineStr">
         <is>
-          <t>【未確認】モンゴル騎兵とヨーロッパ（騎士・城）を対比させているか／「なぜ止まった？」系の問いを文字にしているか</t>
+          <t>【構図】上下2段。上の約3分の1が文字、下の約3分の2が絵。絵は合戦の一場面を引きで切り取ったもので、中央〜右下で3〜4騎の甲冑の騎馬武者が馬ごと崩れ落ちている（落馬・前のめりに倒れる馬）。
+【文字】「最強が負けた日」1行7文字。文字帯は高さの約34%（縁取り込み）、横幅の約95%まで広げ、左右の余白はほぼなし。1文字の高さは画像の約3割（漢字1字＝幅の約16%）。字間は詰めている。「最強」と「負けた」の正反対の言葉をぶつけ、誰の話かは文字で明かさない（タイトル側で「モンゴル」と明かす分担）。
+【色】背景は茶色・くすんだ金・暗い緑の古画トーンで全体に暗め。目立つ色は2つだけ：文字の黄色（太いゴシック体＋黒の縁取り）と、人物を囲む赤い縁取り。
+【人物の表情】顔は小さく表情はほぼ読めない。のけぞる体・投げ出された手足・崩れる馬など、体の動きで「負けた瞬間」を見せている。
+【絵の風合い】中世の戦記を描いた写本・絵巻の挿絵風。ペルシア細密画（ミニアチュール）風の可能性が高い（平らな金茶色の背景、点々と描いた草、立体感の少ない線描）。</t>
         </is>
       </c>
     </row>
@@ -621,7 +625,11 @@
       </c>
       <c r="K3" s="6" t="inlineStr">
         <is>
-          <t>【未確認】怯えるモンゴル兵と武士の構図か／「狩られる側」など逆転を示す言葉があるか</t>
+          <t>【構図】上下の帯文字で絵をはさむサンドイッチ型。中段は左右の対決構図：左に身を寄せ合って縮こまるモンゴル兵5〜6人（狩られる側）、右に刀を振り上げて左へ突進する日本の武者（狩る側）。武者の進行方向（右→左）がモンゴル兵に向かい、視線が「追う側→追われる側」に流れる。
+【文字】4要素で画面の約半分が文字。①上の帯「モンゴル目線で見る元寇」11文字：高さの約16%・幅の約98%、黄色＋黒縁。②左上の吹き出し「怖い怖い怖い怖い怖」9文字（わざと途中で切る）：白い四角に黒文字、高さ約12%・幅約47%。③右の叫び吹き出し「逃がすかおらあぁぁ」約9文字：白いギザギザ吹き出しに赤文字。④下の帯「トラウマ体験すぎる…」10文字：高さの約20%・幅の約95%で一番大きい、赤＋白縁。主役の帯文字は合計21文字。「〜すぎる…」「おらあぁぁ」「怖い」連打など、ネット口語・マンガのセリフ表現で硬い題材をくだけさせている。
+【色】背景は褐色・セピアの古画トーン。文字は上が黄色・下が赤の強い2色を上下に分け、白い吹き出しが間をつなぐ。モンゴル兵は黄土色・オレンジ系で一塊に、武者は青・赤・金など色数が多くこちらが目立つ。
+【人物の表情】モンゴル兵：目を見開き口を開け、頭を抱える・身をすくめる誇張された恐怖顔（ややコミカル）。武者：目をむき歯をむき出しにした鬼の形相で叫ぶ。文字を読まなくても「怖がる側／襲う側」が一瞬でわかる。
+【絵の風合い】右の武者は江戸の武者絵（浮世絵・錦絵）風（歌川国芳のような躍動感）。左のモンゴル兵は古い合戦絵巻の人物をマンガ的に誇張した描き方。</t>
         </is>
       </c>
     </row>

--- a/youtube-world-history-research/output/video_analysis_sheet_filled.xlsx
+++ b/youtube-world-history-research/output/video_analysis_sheet_filled.xlsx
@@ -680,7 +680,11 @@
       </c>
       <c r="K4" s="6" t="inlineStr">
         <is>
-          <t>【未確認】凶悪な表情の海賊を大きく置いているか／「バケモン」のような強い言葉を文字にしているか</t>
+          <t>【構図】上の黒帯にタイトル1行、中段は中央の赤い縦線で左右2分割の比較構図、下に横幅いっぱいの大きな吹き出し。左：小舟の上で慌てる大陸側の兵たち、右：小舟で武器を振りかざす倭寇の集団。
+【文字】4要素の会話劇。①上帯「海外から見た倭寇、怖すぎる」13文字：黒帯に黄色、高さ約14%・幅約96%。②左の吹き出し「お前ら何者？」6文字：白地に黒。③右の吹き出し「え、ただのゴロツキだよ？」12文字：黒＋「ただのゴロツキ」だけ赤。④下の大吹き出し「じゃあなんでそんな強ぇんだよ…」15文字：白地に赤、高さ約18%で一番大きい。「問い→とぼけ→ツッコミ」の3段で笑わせる。
+【色】黒帯×黄色、中央の赤線、白い吹き出しに赤文字。絵は青い海と黄土・赤の衣服。
+【人物の表情】左の兵は目と口を開けた驚き・恐怖の顔。右の倭寇は余裕のニヤけ顔で、強さと軽さの落差を見せる。
+【絵の風合い】中国・日本の古い絵巻（倭寇図巻のような合戦絵巻）風の線描に彩色したイラスト。</t>
         </is>
       </c>
     </row>
@@ -731,7 +735,11 @@
       </c>
       <c r="K5" s="6" t="inlineStr">
         <is>
-          <t>【未確認】コーラ瓶などの商品を象徴的に大きく使っているか／戦場や兵士との組み合わせがあるか</t>
+          <t>【構図】中央にコカ・コーラの瓶を縦いっぱいに大きく置く三分割。左に瓶でコーラを飲む米兵（ヘルメット姿）、右に1920年代風の女性（ヘッドバンド・真珠のネックレス）。背景に古い看板・木箱・炭酸の泡。吹き出しなし。
+【文字】「コーラの歴史」6文字のみ、上部約3割に横幅いっぱい。「コーラ」は赤〜オレンジの燃えるような立体文字、「の歴史」は金色の立体文字。このチャンネルでは珍しく文字が少ない。
+【色】全体がコーラの琥珀色・茶色と赤・金でまとまっている。
+【人物の表情】兵士も女性も笑顔で瓶から飲んでいる（楽しさ・親しみ）。
+【絵の風合い】1940年代アメリカのヴィンテージ広告ポスター風の写実イラスト（AI生成らしい質感）。※再生数÷登録者数は1.1倍で30本中最低。いつもの「会話劇＋ツッコミ」型を外した回でもある。</t>
         </is>
       </c>
     </row>
@@ -782,7 +790,11 @@
       </c>
       <c r="K6" s="6" t="inlineStr">
         <is>
-          <t>【未確認】「総集編」の表示があるか／複数の国や人物をどう並べているか</t>
+          <t>【構図】画面を4分割して異なる「国」の絵を並べ（左上：城壁都市の彩色古地図、右上：工場群の俯瞰、左下：煙の上がる町と兵の列、右下：海上の鉄の要塞〈シーランド公国の写真〉）、その中央を大文字が横断する。人物の吹き出しなし。
+【文字】「実在した異常な国」8文字：赤＋白の縁取り＋黒い影、高さ約24%・幅約95%、画面の真ん中。その下に「11選」白＋黒縁。
+【色】4枚の絵はそれぞれ緑・茶・青の別トーンで、中央の赤い大文字が一番目立つ。
+【人物の表情】人物はほぼなし（左下に小さな兵の列のみ）。
+【絵の風合い】中世の彩色地図・版画風イラストと写真のコラージュ。「凡ミスで滅んだ国3選」と同じテンプレート。</t>
         </is>
       </c>
     </row>
@@ -833,7 +845,11 @@
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
-          <t>【未確認】城壁にはしごで登る兵士など死地の場面か／「99%」の数字を大きく入れているか</t>
+          <t>【構図】上の黒帯にタイトル、下は黄緑一色の背景に、城壁の上で弓を引く兵（左）と、はしごで城壁を登る兵（右）を対角線上に配置。それぞれに吹き出し。
+【文字】①上帯「先頭の兵士って、何考えてたの？」15文字：黒帯に黄色、高さ約16%・幅いっぱい。②弓兵の吹き出し「●ぬよ？」：赤丸の伏せ字＋赤文字（「死ぬよ？」を想像させる）。③登る兵の吹き出し「ですよね。」：白地に黒。脅しへの冷静な返事でシュールな笑いを作る。
+【色】黒帯×黄色、背景の黄緑ベタがとても目立つ。白い城壁と赤い服、赤い伏せ字。
+【人物の表情】弓兵は狙いを定める真顔、登る兵は無表情で淡々。表情は控えめで、吹き出しのセリフで感情を作っている。
+【絵の風合い】鉛筆の線画に水彩で色をつけた、図鑑・教科書の挿絵のような手描き風イラスト。背景だけ単色のベタ塗り。</t>
         </is>
       </c>
     </row>
@@ -884,7 +900,11 @@
       </c>
       <c r="K8" s="6" t="inlineStr">
         <is>
-          <t>【未確認】王や人物の脱力した表情など「しょーもなさ」をどう絵にしているか／「3選」を文字にしているか</t>
+          <t>【構図】画面を4分割（左上：海に浮かぶ山の島、右上：工場群の俯瞰、左下：煙の上がる町と兵の列、右下：山あいの木造集落）し、中央を大文字が横断する。「実在した異常な国11選」と同じテンプレート。
+【文字】「凡ミスで滅んだ国」8文字：赤＋白の縁取り、高さ約22%・幅約95%。その下に「3選」白＋黒縁。
+【色】4枚の絵は青・茶・緑の別トーン、中央の赤い大文字が一番目立つ。
+【人物の表情】人物はほぼなし。
+【絵の風合い】古い彩色版画・油絵風の風景イラスト（AI生成らしい質感）。</t>
         </is>
       </c>
     </row>
@@ -935,7 +955,11 @@
       </c>
       <c r="K9" s="6" t="inlineStr">
         <is>
-          <t>【未確認】機関銃と、不満そうな軍人の表情を組み合わせているか</t>
+          <t>【構図】左に縦3行の大きな問い、中央に重機関銃（弾帯・弾薬箱つき）の写真を切り抜いて配置、右端に軍服の将校2人。右下に大きな吹き出し2つ。赤い矢印で文字から機関銃を指す。
+【文字】①「なぜ軍人は／機関銃を／嫌ったのか？」3行15文字：黄色＋黒縁、画面左半分・高さの約半分。②吹き出し「使わねぇよ」5文字：白地に黒。③大吹き出し「●●だから。」：赤丸2つの伏せ字＋赤文字、高さ約25%（答えを隠して続きを見させる）。
+【色】エメラルドグリーンのベタ背景（放射状の模様入り）、黄色の文字、赤い矢印・伏せ字。
+【人物の表情】将校たちは口ひげで、機関銃を見下ろす不機嫌・ふてぶてしい顔。
+【絵の風合い】機関銃は写真の切り抜き、将校は19世紀の新聞挿絵・風刺画風のイラスト。</t>
         </is>
       </c>
     </row>
@@ -986,7 +1010,11 @@
       </c>
       <c r="K10" s="6" t="inlineStr">
         <is>
-          <t>【未確認】槍兵の密集陣や、騎士が倒される場面か／「地獄」の言葉を文字にしているか</t>
+          <t>【構図】上の黒帯にタイトル、中段は左から「倒れた騎士」「斧槍を振りかぶる歩兵（赤い縁取り）」「右に密集した槍兵の隊列」と、勢いが右から左へ流れる配置。吹き出し2つ。
+【文字】①上帯「※中世の歩兵、怖すぎ問題」12文字：黒帯に黄色、高さ約15%・幅いっぱい。②騎士の吹き出し「こ、降参…」。③歩兵の吹き出し「じゃ●すね？」：赤丸の伏せ字＋「す」赤（「殺すね？」を想像させる）。降参を無視する冷酷さを会話で見せる。
+【色】淡い緑のベタ背景、鎧の金・青、歩兵を囲む赤い縁取り、赤い伏せ字。
+【人物の表情】騎士は力なく倒れて顔をそむける、歩兵は無表情で淡々と斧を振り下ろす（冷酷さ）。
+【絵の風合い】中世ヨーロッパの彩飾写本の挿絵（ミニアチュール）風。</t>
         </is>
       </c>
     </row>
@@ -1037,7 +1065,11 @@
       </c>
       <c r="K11" s="6" t="inlineStr">
         <is>
-          <t>【未確認】ヨーロッパの城壁都市と日本の城下町を並べた対比構図か</t>
+          <t>【構図】中央の赤い縦線で左右2分割。左上に「ヨーロッパ」、右上に「日本」の見出し。左に円形の城壁で囲まれた都市、右に天守を中心とした城下町の俯瞰図。上中央と下に吹き出し。
+【文字】①見出し「ヨーロッパ」5文字・「日本」2文字：黒地に黄色、高さ約10%。②上の吹き出し「なんで壁で囲わないの？」11文字：白地に黒（ヨーロッパ側の問い）。③下の吹き出し「ったく、分かってねぇなぁ…」13文字：白地に赤（日本側の返し）。都市を擬人化した会話劇。
+【色】黒×黄色の見出し、中央の赤線、白い吹き出し。絵は淡い水彩の色。
+【人物の表情】人物なし（都市どうしがしゃべっている設定）。
+【絵の風合い】水彩タッチの鳥瞰図イラスト。</t>
         </is>
       </c>
     </row>
@@ -1088,7 +1120,11 @@
       </c>
       <c r="K12" s="6" t="inlineStr">
         <is>
-          <t>【未確認】インドの地図や人の多さを見せているか／「14億」の数字を入れているか</t>
+          <t>【構図】上下の帯文字で風景をはさむサンドイッチ型。中段は、左に夕日の平野、上に雨雲とヒマラヤ山脈、右にインド亜大陸の立体地図（輪郭が緑に光り、北側の山脈が赤い線）。青い矢印でモンスーンの風が山にぶつかる様子を図解。
+【文字】①上「ヒマラヤが創った『帝国』」12文字：金色グラデーションの立体文字、高さ約17%。②下「インド人口大国の理由」10文字：赤＋白縁、高さ約16%。上で謎をかけ、下で中身を示す。
+【色】青い空・黒い雨雲・金色の夕日・緑の地図の高彩度（HDR調）。
+【人物の表情】人物なし。
+【絵の風合い】AI生成の高彩度な風景イラスト＋3Dの地形図。</t>
         </is>
       </c>
     </row>
@@ -1139,7 +1175,11 @@
       </c>
       <c r="K13" s="6" t="inlineStr">
         <is>
-          <t>【未確認】3つの国の形を並べて見せているか</t>
+          <t>【構図】上半分は暗い紺の世界地図を背景に中央寄せの文字。下半分を3分割し、チリ（オレンジ）・ノルウェー（青）・ベトナム（緑）の地図をそれぞれ光らせて並べる。
+【文字】①「細長い国では／どう暮らしてる？」2行14文字：黄色＋黒縁、中央、高さ約29%。②小見出し「チリ・ノルウェー・ベトナム」13文字：白。
+【色】紺とグレーの地図に、オレンジ・青・緑の3色の発光。
+【人物の表情】人物なし。
+【絵の風合い】デジタル地図のインフォグラフィック風。※倍率1.5倍と低め。問いが「どう暮らしてる？」とゆるく、「なぜ」の矛盾がない。</t>
         </is>
       </c>
     </row>
@@ -1190,7 +1230,11 @@
       </c>
       <c r="K14" s="6" t="inlineStr">
         <is>
-          <t>【未確認】地図上でグリーンランドとデンマークの距離を見せているか</t>
+          <t>【構図】左右2分割。左に衛星写真風のグリーンランド（白い氷床と青い海）、右に北欧の白地図でデンマークを赤く塗る。白い矢印でグリーンランドからデンマークへ結ぶ。
+【文字】①「グリーンランドは／なぜデンマーク領？」2行17文字：白＋「デンマーク領」だけ黄色、黒縁、高さ約30%・幅約70%。②小見出し「いま大国が狙う北極の要衝」12文字：白（時事の関心をつなぐ）。地図上に国名ラベル。
+【色】左は青と白、右はベージュの地図に赤。
+【人物の表情】人物なし。
+【絵の風合い】衛星写真と教科書的な白地図の組み合わせ。</t>
         </is>
       </c>
     </row>
@@ -1241,7 +1285,11 @@
       </c>
       <c r="K15" s="6" t="inlineStr">
         <is>
-          <t>【未確認】問題の15km部分を地図で拡大しているか</t>
+          <t>【構図】東アジアの白地図を全面に使い、ロシア沿海州を赤く塗る。中国から日本海へ向かう赤い破線の矢印が、海の手前で止まる。文字は左上に寄せる。
+【文字】①「なぜ奪われた？」7文字：赤＋白縁、高さ約15%。②「中国を塞ぐ『15km』」11文字：白＋「15km」だけ黄色、黒縁。地名（中国・北朝鮮・韓国・日本海・ロシア）は明朝体の小さいラベル。
+【色】ベージュの陸と水色の海の落ち着いた地図に、赤だけで強調。
+【人物の表情】人物なし。
+【絵の風合い】和紙のような質感の古地図風の白地図。</t>
         </is>
       </c>
     </row>
@@ -1292,7 +1340,11 @@
       </c>
       <c r="K16" s="6" t="inlineStr">
         <is>
-          <t>【未確認】5か国の地図や国旗を並べているか</t>
+          <t>【構図】中央アジアの立体地図を全面に置き、5か国を色分けして赤く光る国境線で囲む。左下に夕日を背にしたラクダの隊商のシルエット（シルクロードの象徴）。
+【文字】①「なぜ5つに分かれた？」10文字：白＋「5つ」だけ黄色、黒縁、高さ約16%。②小見出し「複雑すぎる国境線の謎」10文字：白＋「国境線」黄色、黒帯。国名ラベルは白。
+【色】茶色の背景に、緑・ベージュ・オレンジ・紫の国と、発光する赤い国境線。
+【人物の表情】人物はシルエットのみ。
+【絵の風合い】3D地形図と、夕景の砂漠のAIイラストの組み合わせ。</t>
         </is>
       </c>
     </row>
@@ -1343,7 +1395,11 @@
       </c>
       <c r="K17" s="6" t="inlineStr">
         <is>
-          <t>【未確認】「0.2円」など値段の数字を大きく入れているか／ロシアとアメリカを対比しているか</t>
+          <t>【構図】暗い紺の背景に、左にロシア（赤）、右にアラスカ（金色に発光）と北米（グレー）の地図。中央の金色の矢印に「$7,200,000」と書き、ロシアからアラスカへ「売った」流れを見せる。
+【文字】「アラスカを／ロシアはなぜ売った？」2行13文字：「アラスカ」「ロシア」は黄色、それ以外は白、黒縁、左上、高さ約40%。矢印の中に金額「$7,200,000」。
+【色】紺・赤・金の3色だけ。
+【人物の表情】人物なし。
+【絵の風合い】シンプルなベクターの地図。</t>
         </is>
       </c>
     </row>
@@ -1394,7 +1450,11 @@
       </c>
       <c r="K18" s="6" t="inlineStr">
         <is>
-          <t>【未確認】2国の国旗や地図を並べているか</t>
+          <t>【構図】羊皮紙風の古地図に、オランダ（オレンジ）とベルギー（緑）を塗り、国境を赤く光らせる。左上に大きな問い、右下に札。
+【文字】①「なぜ別の国に／なったのか？」2行12文字：1行目は金色、2行目は白の太い明朝体、高さ約38%。②小見出し「言葉も近い、隣同士なのに…」13文字：白＋「隣同士」黄色、黒帯。③右下の札「オランダとベルギーの謎」11文字：金の縁取り。
+【色】ベージュの羊皮紙に、オレンジ・緑と赤い国境。
+【人物の表情】人物なし。
+【絵の風合い】アンティークの古地図・羊皮紙風。</t>
         </is>
       </c>
     </row>
@@ -1445,7 +1505,11 @@
       </c>
       <c r="K19" s="6" t="inlineStr">
         <is>
-          <t>【未確認】よく似た北欧の国旗を並べて見せているか</t>
+          <t>【構図】北欧の地図だけを全面に置き、ノルウェー（えんじ）・スウェーデン（青）・フィンランド（水色）・デンマーク（赤）を塗り分けて、国名を白文字で入れる。装飾はほぼなし。
+【文字】「なぜ「一つの国」じゃない？」13文字：黄色の太い明朝体、上部1行、高さ約12%・幅約90%。国名ラベルは白。
+【色】紺の海、白い周辺国、北欧4か国の赤〜青系の4色。
+【人物の表情】人物なし。
+【絵の風合い】ごくシンプルなフラットな地図。※30本中で一番はねた（52.5倍）のに、一番シンプルなサムネ。問いの強さで勝っている。</t>
         </is>
       </c>
     </row>
@@ -1496,7 +1560,11 @@
       </c>
       <c r="K20" s="6" t="inlineStr">
         <is>
-          <t>【未確認】半島の地図を2色に塗り分けているか</t>
+          <t>【構図】額縁のように囲んだイベリア半島の地図で、スペイン（赤）とポルトガル（青）の2色だけに塗り分ける。上に1行のタイトル。
+【文字】①上「イベリア半島の「二分割」という歴史的謎」17文字：金色の明朝体、高さ約10%と小さめ。②地図上の国名「スペイン」（金色・大きい）、「ポルトガル」（白）。
+【色】紺の海に赤と青の対比、周りは暗いアンティーク調。
+【人物の表情】人物なし。
+【絵の風合い】フラットな地図を古地図風の暗い額縁に収めた形。※文字は控えめでも30.9倍。2色の対比だけで「なぜ分かれた？」が伝わる。</t>
         </is>
       </c>
     </row>
@@ -1547,7 +1615,11 @@
       </c>
       <c r="K21" s="6" t="inlineStr">
         <is>
-          <t>【未確認】2国の国旗や人物を対立させる構図か</t>
+          <t>【構図】中央にドイツ（黄色に発光）とオーストリア（赤に発光）の地図。左右に両国の国旗と名所（左：ブランデンブルク門の夜景、右：湖畔の町と教会）。稲妻のような亀裂で左右を分ける。
+【文字】①「同じ言語、全く違う国」10文字：黄色＋黒縁、高さ約19%・幅いっぱい。②小見出し「ドイツとオーストリアが『赤の他人』になった理由」22文字：白＋「赤の他人」だけ赤、黒帯。
+【色】黒・黄・赤（両国の国旗の色）で統一し、強い発光。
+【人物の表情】人物なし。
+【絵の風合い】AI生成の高彩度な写実イラストと発光する地図。</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1670,11 @@
       </c>
       <c r="K22" s="6" t="inlineStr">
         <is>
-          <t>【未確認】人物の顔を大きく置いているか／「最期」「53歳」などの文字があるか</t>
+          <t>【構図】中央に人物の胸像（制服姿のゲーリング）、上下を文字の帯ではさむ追伸の定番型。
+【文字】①上「ナチス史上最悪の男」9文字：白、高さ約18%・幅いっぱい。②下「ゲーリングの最期」8文字：赤、高さ約22%。上で人物の「肩書き」、下で「名前＋最期」。
+【色】暗い灰色の背景に、白と赤の2色の文字だけ。
+【人物の表情】正面を見据え、口を結んだ落ち着いた（わずかに笑みのある）顔。
+【絵の風合い】白黒写真をカラー化した肖像写真。背景は暗い灰色〜黒で周囲を暗くした（ビネット）、映画ポスターのような重い雰囲気。文字はかすれのある極太の毛筆・明朝体。</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1725,11 @@
       </c>
       <c r="K23" s="6" t="inlineStr">
         <is>
-          <t>【未確認】若い女性の顔写真を使っているか／「22歳」「悪魔」の文字があるか</t>
+          <t>【構図】中央に若い女性の顔のアップ、上下を文字の帯ではさむ定番型。他の回より背景が明るい（ベージュの壁）ので顔がよく目立つ。
+【文字】①上「ナチス史上最悪の女」9文字：白、高さ約18%。②下「イルマ・グレーゼの最期」11文字：赤、高さ約18%。「男」ではなく「女」にした意外性。
+【色】ベージュの背景に、白と赤の文字。
+【人物の表情】眉をひそめ、カメラをにらむような不機嫌な目つき。「若い女性」と「最悪」の落差を顔で見せる。※チャンネル内で一番の再生数（29.4倍）。
+【絵の風合い】白黒写真をカラー化した肖像写真。背景は暗い灰色〜黒で周囲を暗くした（ビネット）、映画ポスターのような重い雰囲気。文字はかすれのある極太の毛筆・明朝体。</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1780,11 @@
       </c>
       <c r="K24" s="6" t="inlineStr">
         <is>
-          <t>【未確認】人物の顔と「悪魔」「最期」の文字の組み合わせか</t>
+          <t>【構図】中央に人物の胸像、上下を文字の帯ではさむ定番型。背景の左が明るく右が黒い。
+【文字】①上「ナチス史上最悪の男」9文字：白、高さ約18%。②下「ハイドリヒの最期」8文字：赤、高さ約22%。
+【色】白〜黒のグラデーション背景に、白と赤の文字。
+【人物の表情】やや斜めを向き、冷たく見下ろすような目線。
+【絵の風合い】白黒写真をカラー化した肖像写真。背景は暗い灰色〜黒で周囲を暗くした（ビネット）、映画ポスターのような重い雰囲気。文字はかすれのある極太の毛筆・明朝体。</t>
         </is>
       </c>
     </row>
@@ -1751,7 +1835,11 @@
       </c>
       <c r="K25" s="6" t="inlineStr">
         <is>
-          <t>【未確認】晩年の顔か／「44日間」「4500万人」の数字を入れているか</t>
+          <t>【構図】中央に人物の胸像、上下を文字の帯ではさむ定番型。文字が他の回より大きい。
+【文字】①上「残酷すぎる44日間」9文字（「すぎる」だけ小さく）：白、高さ約23%。②下「毛沢東の最期」6文字：赤、高さ約29%。肩書きではなく「期間＋残酷」を上に置いた形。
+【色】暗い背景に、白と赤の文字。
+【人物の表情】正面を向いた、穏やかな薄笑い（「残酷」との落差）。
+【絵の風合い】白黒写真をカラー化した肖像写真。背景は暗い灰色〜黒で周囲を暗くした（ビネット）、映画ポスターのような重い雰囲気。文字はかすれのある極太の毛筆・明朝体。</t>
         </is>
       </c>
     </row>
@@ -1802,7 +1890,11 @@
       </c>
       <c r="K26" s="6" t="inlineStr">
         <is>
-          <t>【未確認】人物の顔とスターリンを並べているか</t>
+          <t>【構図】中央に人物の胸像、上下を文字の帯ではさむ定番型。
+【文字】①上「大量虐殺した悪魔」8文字：白、高さ約22%。②下「ベリヤの最期」6文字：赤、高さ約28%。
+【色】暗い背景に、白と赤の文字。
+【人物の表情】丸眼鏡の男が正面を向き、無表情で冷たい目つき。
+【絵の風合い】白黒写真をカラー化した肖像写真。背景は暗い灰色〜黒で周囲を暗くした（ビネット）、映画ポスターのような重い雰囲気。文字はかすれのある極太の毛筆・明朝体。</t>
         </is>
       </c>
     </row>
@@ -1853,7 +1945,11 @@
       </c>
       <c r="K27" s="6" t="inlineStr">
         <is>
-          <t>【未確認】人物の顔と「ヒトラーに殺された」の文字があるか</t>
+          <t>【構図】中央に制帽姿の人物の横顔、上下を文字の帯ではさむ定番型。左の背景に別の白黒写真がうっすら重なる。
+【文字】①上「ナチス最高の天才」8文字：白、高さ約21%。②下「ロンメルの最期」7文字：赤、高さ約23%。他の回の「最悪」ではなく「最高」の英雄枠。
+【色】白黒寄りの背景に、白と赤の文字。
+【人物の表情】横を向いて遠くを見つめる、険しく引き締まった表情。
+【絵の風合い】白黒写真をカラー化した肖像写真。背景は暗い灰色〜黒で周囲を暗くした（ビネット）、映画ポスターのような重い雰囲気。文字はかすれのある極太の毛筆・明朝体。</t>
         </is>
       </c>
     </row>
@@ -1904,7 +2000,11 @@
       </c>
       <c r="K28" s="6" t="inlineStr">
         <is>
-          <t>【未確認】人物の顔と「500万人」の数字を入れているか</t>
+          <t>【構図】中央に制帽姿の人物、上下を文字の帯ではさむ定番型。左端にハーケンクロイツの腕章が見える。
+【文字】①上「ナチスが最も恐れた男」10文字：白、高さ約18%。②下「アイヒマンの最期」8文字：赤、高さ約21%。
+【色】暗い緑灰色の背景に、白と赤の文字。
+【人物の表情】口元に薄笑いを浮かべ、こちらをにらむような表情。
+【絵の風合い】白黒写真をカラー化した肖像写真。背景は暗い灰色〜黒で周囲を暗くした（ビネット）、映画ポスターのような重い雰囲気。文字はかすれのある極太の毛筆・明朝体。</t>
         </is>
       </c>
     </row>
@@ -1955,7 +2055,11 @@
       </c>
       <c r="K29" s="6" t="inlineStr">
         <is>
-          <t>【未確認】人物の顔と「7日間」「1000万人」の数字があるか</t>
+          <t>【構図】中央に人物の胸像、上下を文字の帯ではさむ定番型。文字がとても大きく、上下で1つの文になっている。
+【文字】①上「スターリンの」6文字：白、高さ約26%。②下「最期の7日間」6文字：赤、高さ約31%（30本中で最大級）。名前＋期間だけの短い文。
+【色】明るめのグレーの背景に、白と赤の文字。
+【人物の表情】口ひげで目を細めた薄笑い（不気味さ）。
+【絵の風合い】白黒写真をカラー化した肖像写真。背景は暗い灰色〜黒で周囲を暗くした（ビネット）、映画ポスターのような重い雰囲気。文字はかすれのある極太の毛筆・明朝体。</t>
         </is>
       </c>
     </row>
@@ -2006,7 +2110,11 @@
       </c>
       <c r="K30" s="6" t="inlineStr">
         <is>
-          <t>【未確認】人物の顔と「逆さ吊り」「10日間」の文字があるか</t>
+          <t>【構図】中央に軍帽・制服のムッソリーニ、その周りを帽子の兵士や側近が囲む集合写真。上下を文字の帯ではさむ。
+【文字】①上「ムッソリーニの」7文字：白、高さ約25%。②下「最期の10日間」7文字：赤、高さ約28%。スターリンの回と同じ「名前の／最期の○日間」型。
+【色】暗い背景にカラー化した写真、白と赤の文字。
+【人物の表情】ムッソリーニはあごを上げて遠くを見る尊大な顔、周りの男たちは険しい顔。
+【絵の風合い】白黒写真をカラー化した肖像写真。背景は暗い灰色〜黒で周囲を暗くした（ビネット）、映画ポスターのような重い雰囲気。文字はかすれのある極太の毛筆・明朝体。</t>
         </is>
       </c>
     </row>
@@ -2057,7 +2165,11 @@
       </c>
       <c r="K31" s="6" t="inlineStr">
         <is>
-          <t>【未確認】ヒトラーの顔と「48時間」の文字があるか</t>
+          <t>【構図】他の9本と違う型。背景を4分割（左上：ヒトラーの顔、右上：女性〈エヴァ〉の白黒写真、左下：紫の稲妻、右下：男の白黒写真）し、四隅に小見出しで動画の中身を予告する。中央に大文字。
+【文字】①中央「ヒトラー」4文字：白＋黒縁。②中央下「最後の48時間」7文字：赤＋白縁、高さ約21%。③四隅の小見出し「2通の遺言書を残す」「突然エヴァと結婚する」「青酸カリで愛犬を毒殺」「ヘルマンを処刑する」（各8〜10文字、白）。
+【色】暗い背景に紫の稲妻、白と赤の文字。
+【人物の表情】ヒトラーは目を見開いた険しい顔、他の人物は白黒の不鮮明な写真。
+【絵の風合い】白黒写真のコラージュに稲妻の効果。チャンネルの初期の回（2025年11月）で、後の「上下帯＋肖像」型に固まる前の形。</t>
         </is>
       </c>
     </row>

--- a/youtube-world-history-research/output/video_analysis_sheet_filled.xlsx
+++ b/youtube-world-history-research/output/video_analysis_sheet_filled.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K31"/>
+  <dimension ref="A1:M31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -461,9 +461,11 @@
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="30" customWidth="1" min="8" max="8"/>
-    <col width="30" customWidth="1" min="9" max="9"/>
-    <col width="30" customWidth="1" min="10" max="10"/>
-    <col width="36" customWidth="1" min="11" max="11"/>
+    <col width="36" customWidth="1" min="9" max="9"/>
+    <col width="60" customWidth="1" min="10" max="10"/>
+    <col width="48" customWidth="1" min="11" max="11"/>
+    <col width="30" customWidth="1" min="12" max="12"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -509,15 +511,25 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>見たら何が得られると約束しているか</t>
+          <t>視聴者は何が欲しいのか</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>どんな感情を動かしているか（驚き・不安・好奇心など）</t>
+          <t>見たら何が得られると約束しているか（サムネ＋タイトル＋概要欄から視聴者が受け取る約束）</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>動画制作者の意図</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>どんな感情を動かしているか（驚き・不安・好奇心など）※コメント未反映</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>サムネの構図・文字数・色・人物の表情</t>
         </is>
@@ -560,15 +572,25 @@
       </c>
       <c r="I2" s="6" t="inlineStr">
         <is>
-          <t>「最強」のモンゴルがヨーロッパで止まった本当の理由（地理・補給・政治事情）がわかる</t>
+          <t>「最強」という前提が崩れる瞬間を見たい。どっちが強いかという番付の話を楽しみたい。</t>
         </is>
       </c>
       <c r="J2" s="6" t="inlineStr">
         <is>
+          <t>サムネ「最強が負けた日」と落馬する騎馬武者で、無敵の軍団が実際に負けた現場を見せると約束し、タイトルで主語がモンゴル、舞台がヨーロッパだと明かす。合わせると「モンゴルを止めた『もっと強い何か』の正体がわかる」と受け取れる。概要欄「最強には最強をぶつけんだよ。」で、答えが地理や偶然ではなく強者どうしの対決だと匂わせ、バトル漫画の対決を見る期待に変えている。</t>
+        </is>
+      </c>
+      <c r="K2" s="6" t="inlineStr">
+        <is>
+          <t>誰もが知る「最強」の看板を借りて、負けた側の話にすることで矛盾を作る。サムネで主語を伏せて「誰が？」と思わせ、タイトルで検索される言葉（モンゴル帝国、ヨーロッパ）を回収する分担。概要欄は漫画のセリフのもじりで、歴史を対戦ものとして楽しむ層に合図している。</t>
+        </is>
+      </c>
+      <c r="L2" s="6" t="inlineStr">
+        <is>
           <t>好奇心（最強なのになぜ？という矛盾）、意外性</t>
         </is>
       </c>
-      <c r="K2" s="6" t="inlineStr">
+      <c r="M2" s="6" t="inlineStr">
         <is>
           <t>【構図】上下2段。上の約3分の1が文字、下の約3分の2が絵。絵は合戦の一場面を引きで切り取ったもので、中央〜右下で3〜4騎の甲冑の騎馬武者が馬ごと崩れ落ちている（落馬・前のめりに倒れる馬）。
 【文字】「最強が負けた日」1行7文字。文字帯は高さの約34%（縁取り込み）、横幅の約95%まで広げ、左右の余白はほぼなし。1文字の高さは画像の約3割（漢字1字＝幅の約16%）。字間は詰めている。「最強」と「負けた」の正反対の言葉をぶつけ、誰の話かは文字で明かさない（タイトル側で「モンゴル」と明かす分担）。
@@ -615,15 +637,25 @@
       </c>
       <c r="I3" s="6" t="inlineStr">
         <is>
-          <t>攻めた側（モンゴル）の目線で見ると、日本の武士がどれほど恐ろしかったかがわかる</t>
+          <t>日本が侵略者を返り討ちにする痛快さ。「神風だけじゃなかった」と知って武士を誇らしく思いたい。教科書の話を別の目線で見直したい。</t>
         </is>
       </c>
       <c r="J3" s="6" t="inlineStr">
         <is>
+          <t>タイトル「立場逆転」「狩られる側に」と、サムネの怯えるモンゴル兵と鬼の形相の武者で、「攻めてきたモンゴル兵が日本でどれだけ怖い目にあったかを追体験できる」と受け取れる。下帯「トラウマ体験すぎる…」で、笑いながら見られる軽さも約束している。概要欄で「神風の力だけで勝負が決まったわけではない」と、通説を正す話もあると示す。</t>
+        </is>
+      </c>
+      <c r="K3" s="6" t="inlineStr">
+        <is>
+          <t>日本人が一番よく知る対外戦争を、相手側の目線に反転させる。恐怖をマンガのセリフで描いてコメディにし、硬い題材の入口を広げる。日本人の誇らしさをくすぐりつつ、概要欄で史実寄りの補正をして「ただの日本すごい動画ではない」という信頼を足している。</t>
+        </is>
+      </c>
+      <c r="L3" s="6" t="inlineStr">
+        <is>
           <t>立場が逆転する痛快さ、日本への誇らしさ、恐怖</t>
         </is>
       </c>
-      <c r="K3" s="6" t="inlineStr">
+      <c r="M3" s="6" t="inlineStr">
         <is>
           <t>【構図】上下の帯文字で絵をはさむサンドイッチ型。中段は左右の対決構図：左に身を寄せ合って縮こまるモンゴル兵5〜6人（狩られる側）、右に刀を振り上げて左へ突進する日本の武者（狩る側）。武者の進行方向（右→左）がモンゴル兵に向かい、視線が「追う側→追われる側」に流れる。
 【文字】4要素で画面の約半分が文字。①上の帯「モンゴル目線で見る元寇」11文字：高さの約16%・幅の約98%、黄色＋黒縁。②左上の吹き出し「怖い怖い怖い怖い怖」9文字（わざと途中で切る）：白い四角に黒文字、高さ約12%・幅約47%。③右の叫び吹き出し「逃がすかおらあぁぁ」約9文字：白いギザギザ吹き出しに赤文字。④下の帯「トラウマ体験すぎる…」10文字：高さの約20%・幅の約95%で一番大きい、赤＋白縁。主役の帯文字は合計21文字。「〜すぎる…」「おらあぁぁ」「怖い」連打など、ネット口語・マンガのセリフ表現で硬い題材をくだけさせている。
@@ -670,15 +702,25 @@
       </c>
       <c r="I4" s="6" t="inlineStr">
         <is>
-          <t>東アジアを荒らした「日本の海賊」の実態と、どれほど厄介だったかがわかる</t>
+          <t>「日本人が海外で恐れられていた」という意外さと、少しの誇らしさ。教科書の単語の中身を、笑いながら知りたい。</t>
         </is>
       </c>
       <c r="J4" s="6" t="inlineStr">
         <is>
+          <t>サムネ「海外から見た倭寇、怖すぎる」と「ただのゴロツキだよ？」「じゃあなんでそんな強ぇんだよ…」の会話で、「被害を受けた側から見た倭寇のヤバさと、ただのゴロツキがなぜ強かったか」がわかると受け取れる。概要欄「こんなやつらが定期的に襲来してくるとか気の毒すぎる。」で、被害側に同情しながら笑って見る視点を指定している。</t>
+        </is>
+      </c>
+      <c r="K4" s="6" t="inlineStr">
+        <is>
+          <t>元寇と同じ「外から見た日本」型の2本目。強さの理由をツッコミの形で伏せ、続きを見る理由を作る。「バケモン」「厄介すぎる」などネットの口語で、怖さを笑いに変えている。</t>
+        </is>
+      </c>
+      <c r="L4" s="6" t="inlineStr">
+        <is>
           <t>恐怖、「日本人がそこまで？」という驚きと少しの誇らしさ</t>
         </is>
       </c>
-      <c r="K4" s="6" t="inlineStr">
+      <c r="M4" s="6" t="inlineStr">
         <is>
           <t>【構図】上の黒帯にタイトル1行、中段は中央の赤い縦線で左右2分割の比較構図、下に横幅いっぱいの大きな吹き出し。左：小舟の上で慌てる大陸側の兵たち、右：小舟で武器を振りかざす倭寇の集団。
 【文字】4要素の会話劇。①上帯「海外から見た倭寇、怖すぎる」13文字：黒帯に黄色、高さ約14%・幅約96%。②左の吹き出し「お前ら何者？」6文字：白地に黒。③右の吹き出し「え、ただのゴロツキだよ？」12文字：黒＋「ただのゴロツキ」だけ赤。④下の大吹き出し「じゃあなんでそんな強ぇんだよ…」15文字：白地に赤、高さ約18%で一番大きい。「問い→とぼけ→ツッコミ」の3段で笑わせる。
@@ -725,15 +767,25 @@
       </c>
       <c r="I5" s="6" t="inlineStr">
         <is>
-          <t>誰もが知るコカ・コーラが、子どもから戦場の兵士まで世界を支配するまでの歴史がわかる</t>
+          <t>身近な商品の意外な裏話を知って、人に話したい。</t>
         </is>
       </c>
       <c r="J5" s="6" t="inlineStr">
         <is>
+          <t>サムネ「コーラの歴史」と笑顔で飲む兵士と女性で、「コーラが世界中で愛されるようになった歴史を楽しく知れる」という穏やかな約束になっている。タイトル「戦場の兵士まで」で戦争との意外な関係を示すが、サムネには問いも驚きもない。概要欄も「缶より瓶の方が美味しいって本当？」と雑談調。</t>
+        </is>
+      </c>
+      <c r="K5" s="6" t="inlineStr">
+        <is>
+          <t>歴史好き以外にも届くテーマで、チャンネルの外に広げる試み。ただ、いつもの「矛盾の問い＋会話のツッコミ」を使わず広告ポスター風にしたため、見たら何がわかるかの約束がぼやけた（1.1倍で30本中最低）。</t>
+        </is>
+      </c>
+      <c r="L5" s="6" t="inlineStr">
+        <is>
           <t>身近なものの意外性、好奇心</t>
         </is>
       </c>
-      <c r="K5" s="6" t="inlineStr">
+      <c r="M5" s="6" t="inlineStr">
         <is>
           <t>【構図】中央にコカ・コーラの瓶を縦いっぱいに大きく置く三分割。左に瓶でコーラを飲む米兵（ヘルメット姿）、右に1920年代風の女性（ヘッドバンド・真珠のネックレス）。背景に古い看板・木箱・炭酸の泡。吹き出しなし。
 【文字】「コーラの歴史」6文字のみ、上部約3割に横幅いっぱい。「コーラ」は赤〜オレンジの燃えるような立体文字、「の歴史」は金色の立体文字。このチャンネルでは珍しく文字が少ない。
@@ -780,15 +832,25 @@
       </c>
       <c r="I6" s="6" t="inlineStr">
         <is>
-          <t>犯罪者が作った国や凡ミスで滅んだ国など、ヤバい国の話を2時間近くまとめて楽しめる</t>
+          <t>「こんな国が本当にあったの？」という奇妙な実話を、まとめて長時間楽しみたい。作業中や寝る前に流したい。</t>
         </is>
       </c>
       <c r="J6" s="6" t="inlineStr">
         <is>
+          <t>サムネ「実在した異常な国11選」と4分割の絵で、「信じられないけど本当にあった国を11個まとめて見られる」と受け取れる。タイトル「犯罪者が建国し、凡ミスで滅亡」で極端な実例を見本として出す。概要欄「私も独立国家作ろうかな。」で、自分でも作れそうと思える軽いノリを示している。</t>
+        </is>
+      </c>
+      <c r="K6" s="6" t="inlineStr">
+        <is>
+          <t>過去の「〇〇な国」回をまとめ直して、長尺で総再生時間を稼ぐ。「11選」で量をはっきり見せ、作業用・寝る前用として選ばれやすくしている。</t>
+        </is>
+      </c>
+      <c r="L6" s="6" t="inlineStr">
+        <is>
           <t>驚き、笑い（くだらなさ）、怖いもの見たさ</t>
         </is>
       </c>
-      <c r="K6" s="6" t="inlineStr">
+      <c r="M6" s="6" t="inlineStr">
         <is>
           <t>【構図】画面を4分割して異なる「国」の絵を並べ（左上：城壁都市の彩色古地図、右上：工場群の俯瞰、左下：煙の上がる町と兵の列、右下：海上の鉄の要塞〈シーランド公国の写真〉）、その中央を大文字が横断する。人物の吹き出しなし。
 【文字】「実在した異常な国」8文字：赤＋白の縁取り＋黒い影、高さ約24%・幅約95%、画面の真ん中。その下に「11選」白＋黒縁。
@@ -835,15 +897,25 @@
       </c>
       <c r="I7" s="6" t="inlineStr">
         <is>
-          <t>死亡率99%の突入役に人が志願した理由（報酬・名誉・制度）がわかる</t>
+          <t>「自分なら絶対無理」なことをした人の心の中をのぞきたい。死と隣り合わせの極限状況を、安全な場所から想像したい。</t>
         </is>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
+          <t>タイトル「致〇率99%」と、サムネ「先頭の兵士って、何考えてたの？」「●ぬよ？」「ですよね。」の会話で、「ほぼ死ぬとわかって突っ込んだ兵士の本音と、そうさせた仕組みがわかる」と受け取れる。概要欄「私はどんな理由があっても先頭にはなりたくないタイプです。」で、視聴者と同じ普通の人の目線で見ると約束している。</t>
+        </is>
+      </c>
+      <c r="K7" s="6" t="inlineStr">
+        <is>
+          <t>「なぜ？」を人の気持ちに向けた問いにする。数字（99%）で極限さを、伏せ字で死を、淡々とした返事でシュールな笑いを作る。作り手が「自分も無理なタイプ」と言うことで、視聴者と同じ側に立っている。</t>
+        </is>
+      </c>
+      <c r="L7" s="6" t="inlineStr">
+        <is>
           <t>恐怖、「なぜそんなことを？」という疑問</t>
         </is>
       </c>
-      <c r="K7" s="6" t="inlineStr">
+      <c r="M7" s="6" t="inlineStr">
         <is>
           <t>【構図】上の黒帯にタイトル、下は黄緑一色の背景に、城壁の上で弓を引く兵（左）と、はしごで城壁を登る兵（右）を対角線上に配置。それぞれに吹き出し。
 【文字】①上帯「先頭の兵士って、何考えてたの？」15文字：黒帯に黄色、高さ約16%・幅いっぱい。②弓兵の吹き出し「●ぬよ？」：赤丸の伏せ字＋赤文字（「死ぬよ？」を想像させる）。③登る兵の吹き出し「ですよね。」：白地に黒。脅しへの冷静な返事でシュールな笑いを作る。
@@ -890,15 +962,25 @@
       </c>
       <c r="I8" s="6" t="inlineStr">
         <is>
-          <t>信じられないほどくだらない理由で国が滅んだ実例を3つ知れる</t>
+          <t>国家という大きなものが、くだらない理由で終わる落差で笑いたい。</t>
         </is>
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
+          <t>サムネ「凡ミスで滅んだ国3選」とタイトル「ビックリするほどしょーもない理由」で、「笑えるほどしょぼい理由で国が終わった実話を3つ見られる」と受け取れる。3つという少なさで、気軽に見られる軽さも約束している。</t>
+        </is>
+      </c>
+      <c r="K8" s="6" t="inlineStr">
+        <is>
+          <t>「〇〇な国」シリーズの最終回（概要欄「とりあえずこれで最後です！」）。シリーズのテンプレート（4分割＋赤い大文字）を使い回し、既存の視聴者に続きものだと分からせる。「滅亡」という重い言葉に「しょーもない」をぶつけて落差を作る。</t>
+        </is>
+      </c>
+      <c r="L8" s="6" t="inlineStr">
+        <is>
           <t>笑い、「国が滅ぶ」と「しょーもない」の落差による驚き</t>
         </is>
       </c>
-      <c r="K8" s="6" t="inlineStr">
+      <c r="M8" s="6" t="inlineStr">
         <is>
           <t>【構図】画面を4分割（左上：海に浮かぶ山の島、右上：工場群の俯瞰、左下：煙の上がる町と兵の列、右下：山あいの木造集落）し、中央を大文字が横断する。「実在した異常な国11選」と同じテンプレート。
 【文字】「凡ミスで滅んだ国」8文字：赤＋白の縁取り、高さ約22%・幅約95%。その下に「3選」白＋黒縁。
@@ -945,15 +1027,25 @@
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
-          <t>最強の兵器のはずの機関銃が、なぜ軍人たちに嫌われていたかがわかる</t>
+          <t>「強いのに嫌われる」理不尽の理由を知って、自分の職場や組織の話に重ねたい。古い組織が新しいものを嫌う「あるある」に共感したい。</t>
         </is>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
+          <t>サムネ「なぜ軍人は機関銃を嫌ったのか？」と不機嫌な将校の「使わねぇよ」「●●だから。」で、「軍人が最強の兵器を拒んだ、意外で人間くさい理由がわかる」と受け取れる。答えは伏せ字で隠す。概要欄「これは現代でもあるある。」で、答えが兵器の性能ではなく組織や人の心理（プライド、慣習）の話だとほのめかし、「今の職場にも通じる話」という約束に広げている。</t>
+        </is>
+      </c>
+      <c r="K9" s="6" t="inlineStr">
+        <is>
+          <t>兵器の話に見せて、中身は「組織が新しい技術を嫌う」という普遍的な人間の話。伏せ字で答えを隠して続きを見させ、概要欄の一言で軍事好き以外の会社員にも自分ごとにさせている。</t>
+        </is>
+      </c>
+      <c r="L9" s="6" t="inlineStr">
+        <is>
           <t>矛盾への好奇心、意外性</t>
         </is>
       </c>
-      <c r="K9" s="6" t="inlineStr">
+      <c r="M9" s="6" t="inlineStr">
         <is>
           <t>【構図】左に縦3行の大きな問い、中央に重機関銃（弾帯・弾薬箱つき）の写真を切り抜いて配置、右端に軍服の将校2人。右下に大きな吹き出し2つ。赤い矢印で文字から機関銃を指す。
 【文字】①「なぜ軍人は／機関銃を／嫌ったのか？」3行15文字：黄色＋黒縁、画面左半分・高さの約半分。②吹き出し「使わねぇよ」5文字：白地に黒。③大吹き出し「●●だから。」：赤丸2つの伏せ字＋赤文字、高さ約25%（答えを隠して続きを見させる）。
@@ -1000,15 +1092,25 @@
       </c>
       <c r="I10" s="6" t="inlineStr">
         <is>
-          <t>騎士が主役だった中世の戦争が、歩兵の台頭でなぜ地獄になったかがわかる</t>
+          <t>騎士道の美しいイメージの裏にある、残酷な現実を知りたい。</t>
         </is>
       </c>
       <c r="J10" s="6" t="inlineStr">
         <is>
+          <t>サムネ「※中世の歩兵、怖すぎ問題」と「こ、降参…」「じゃ●すね？」の会話で、「騎士の名誉のルールが通じない歩兵が、戦場をどう変えたかを見られる」と受け取れる。タイトルの「地獄」で残酷さを予告する。概要欄「戦争にも規律って必要なんだな。。。」で、降参や身代金のルールがなくなった怖さが中身だとわかる。</t>
+        </is>
+      </c>
+      <c r="K10" s="6" t="inlineStr">
+        <is>
+          <t>騎士のロマンを持つ視聴者に、その反対側を見せる。降参が通じない冷たさを2行の会話で見せ、「〇〇問題」というネットの言い回しで軽くして入口を広げている。</t>
+        </is>
+      </c>
+      <c r="L10" s="6" t="inlineStr">
+        <is>
           <t>恐怖、騎士の時代が終わることへのロマン</t>
         </is>
       </c>
-      <c r="K10" s="6" t="inlineStr">
+      <c r="M10" s="6" t="inlineStr">
         <is>
           <t>【構図】上の黒帯にタイトル、中段は左から「倒れた騎士」「斧槍を振りかぶる歩兵（赤い縁取り）」「右に密集した槍兵の隊列」と、勢いが右から左へ流れる配置。吹き出し2つ。
 【文字】①上帯「※中世の歩兵、怖すぎ問題」12文字：黒帯に黄色、高さ約15%・幅いっぱい。②騎士の吹き出し「こ、降参…」。③歩兵の吹き出し「じゃ●すね？」：赤丸の伏せ字＋「す」赤（「殺すね？」を想像させる）。降参を無視する冷酷さを会話で見せる。
@@ -1055,15 +1157,25 @@
       </c>
       <c r="I11" s="6" t="inlineStr">
         <is>
-          <t>世界では当たり前の城塞都市が、なぜ日本では作られなかったかがわかる（日欧比較）</t>
+          <t>日本と海外の違いの理由を知って、「日本ってそういうことか」と自分の国を見直したい。</t>
         </is>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
+          <t>サムネの「ヨーロッパ／日本」の2分割と「なんで壁で囲わないの？」「ったく、分かってねぇなぁ…」で、「日本が壁を作らなかったのには、ちゃんとした理由がある」とわかると受け取れる。タイトル「防御力最強のはずの」「意外な理由」で矛盾を強める。日本側が言い返す構図なので、日本が劣っていたわけではないという安心も約束している。</t>
+        </is>
+      </c>
+      <c r="K11" s="6" t="inlineStr">
+        <is>
+          <t>「世界では当たり前、日本では違う」の比較で、日本人の自分ごと感を作る。都市を擬人化した会話で、日本側に余裕のあるセリフを言わせ、見る前から日本側に肩入れさせている。</t>
+        </is>
+      </c>
+      <c r="L11" s="6" t="inlineStr">
+        <is>
           <t>「言われてみれば確かに」という好奇心、日本についての発見</t>
         </is>
       </c>
-      <c r="K11" s="6" t="inlineStr">
+      <c r="M11" s="6" t="inlineStr">
         <is>
           <t>【構図】中央の赤い縦線で左右2分割。左上に「ヨーロッパ」、右上に「日本」の見出し。左に円形の城壁で囲まれた都市、右に天守を中心とした城下町の俯瞰図。上中央と下に吹き出し。
 【文字】①見出し「ヨーロッパ」5文字・「日本」2文字：黒地に黄色、高さ約10%。②上の吹き出し「なんで壁で囲わないの？」11文字：白地に黒（ヨーロッパ側の問い）。③下の吹き出し「ったく、分かってねぇなぁ…」13文字：白地に赤（日本側の返し）。都市を擬人化した会話劇。
@@ -1110,15 +1222,25 @@
       </c>
       <c r="I12" s="6" t="inlineStr">
         <is>
-          <t>14億人を生んだ地形と、その裏の残酷な歴史がわかる</t>
+          <t>ニュースで知った事実（人口世界一）の背景を知って、世界の見え方を一段深くしたい。自然の大きなスケールに浸りたい。</t>
         </is>
       </c>
       <c r="J12" s="6" t="inlineStr">
         <is>
+          <t>サムネ上の「ヒマラヤが創った『帝国』」で謎をかけ、下の「インド人口大国の理由」で中身を示す。タイトル「最強の地形と残酷な歴史」と合わせて、「人口の多さは地形が作ったという意外な答えと、搾取の歴史がわかる」と受け取れる。概要欄「お茶碗一杯のご飯にも通じる」で、自分の暮らしにつながる話だと示している。</t>
+        </is>
+      </c>
+      <c r="K12" s="6" t="inlineStr">
+        <is>
+          <t>時事（2023年に人口世界一）を入口に、地形という目に見えない原因で答える。高彩度の風景でスケールの大きなドキュメンタリーの空気を作り、大人がゆっくり見る番組として見せている。</t>
+        </is>
+      </c>
+      <c r="L12" s="6" t="inlineStr">
+        <is>
           <t>好奇心、「残酷な歴史」への少しの不安</t>
         </is>
       </c>
-      <c r="K12" s="6" t="inlineStr">
+      <c r="M12" s="6" t="inlineStr">
         <is>
           <t>【構図】上下の帯文字で風景をはさむサンドイッチ型。中段は、左に夕日の平野、上に雨雲とヒマラヤ山脈、右にインド亜大陸の立体地図（輪郭が緑に光り、北側の山脈が赤い線）。青い矢印でモンスーンの風が山にぶつかる様子を図解。
 【文字】①上「ヒマラヤが創った『帝国』」12文字：金色グラデーションの立体文字、高さ約17%。②下「インド人口大国の理由」10文字：赤＋白縁、高さ約16%。上で謎をかけ、下で中身を示す。
@@ -1165,15 +1287,25 @@
       </c>
       <c r="I13" s="6" t="inlineStr">
         <is>
-          <t>チリ・ノルウェー・ベトナムが細長い理由と、3国の意外な共通点がわかる</t>
+          <t>地図を眺めて「変な形」と思った国の事情を知りたい。日本との共通点を見つけたい。</t>
         </is>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
+          <t>サムネ「細長い国ではどう暮らしてる？」と3国の地図で、「細長い国の暮らしの大変さを見られる」と受け取れる。タイトルで「日本より細長い」「過酷な宿命と驚きの共通点」を足す。概要欄で「毎日10時間運転しても端から端まで1週間」など具体的な苦労があると示している。</t>
+        </is>
+      </c>
+      <c r="K13" s="6" t="inlineStr">
+        <is>
+          <t>地図の形という、見てすぐわかる違和感を使う。ただ問いが「どう暮らしてる？」とゆるく、「なぜ」の矛盾がないため、約束が雑学止まりになっている（1.5倍と低め）。</t>
+        </is>
+      </c>
+      <c r="L13" s="6" t="inlineStr">
+        <is>
           <t>驚き、地図を眺める楽しさ</t>
         </is>
       </c>
-      <c r="K13" s="6" t="inlineStr">
+      <c r="M13" s="6" t="inlineStr">
         <is>
           <t>【構図】上半分は暗い紺の世界地図を背景に中央寄せの文字。下半分を3分割し、チリ（オレンジ）・ノルウェー（青）・ベトナム（緑）の地図をそれぞれ光らせて並べる。
 【文字】①「細長い国では／どう暮らしてる？」2行14文字：黄色＋黒縁、中央、高さ約29%。②小見出し「チリ・ノルウェー・ベトナム」13文字：白。
@@ -1220,15 +1352,25 @@
       </c>
       <c r="I14" s="6" t="inlineStr">
         <is>
-          <t>北米にある巨大な島が、なぜ遠いデンマークの領土なのかがわかる</t>
+          <t>ニュース（大国が狙う）で気になった島の事情を、根っこから知って納得したい。</t>
         </is>
       </c>
       <c r="J14" s="6" t="inlineStr">
         <is>
+          <t>サムネ「グリーンランドはなぜデンマーク領？」と地図の矢印で、地図を見た誰もが思う矛盾の答えがわかると受け取れる。サムネ下「いま大国が狙う北極の要衝」で今のニュースにつながる話を、タイトル「嘘と勘違いから始まった数奇な運命」でドラマのある経緯を約束する。概要欄で「史上最大の不動産詐欺」など4つの見どころと、後半の地政学パートを予告している。</t>
+        </is>
+      </c>
+      <c r="K14" s="6" t="inlineStr">
+        <is>
+          <t>時事で名前を聞くようになった島を、昔からの素朴な疑問とセットにする。「大人の歴史物語」という言葉で、落ち着いて聞ける教養番組として見せ、中高年層を狙っている。</t>
+        </is>
+      </c>
+      <c r="L14" s="6" t="inlineStr">
+        <is>
           <t>素朴な疑問が解ける好奇心、「嘘と勘違い」という意外な経緯への興味</t>
         </is>
       </c>
-      <c r="K14" s="6" t="inlineStr">
+      <c r="M14" s="6" t="inlineStr">
         <is>
           <t>【構図】左右2分割。左に衛星写真風のグリーンランド（白い氷床と青い海）、右に北欧の白地図でデンマークを赤く塗る。白い矢印でグリーンランドからデンマークへ結ぶ。
 【文字】①「グリーンランドは／なぜデンマーク領？」2行17文字：白＋「デンマーク領」だけ黄色、黒縁、高さ約30%・幅約70%。②小見出し「いま大国が狙う北極の要衝」12文字：白（時事の関心をつなぐ）。地図上に国名ラベル。
@@ -1275,15 +1417,25 @@
       </c>
       <c r="I15" s="6" t="inlineStr">
         <is>
-          <t>中国が日本海に出られない「15kmの壁」の歴史的な経緯がわかる</t>
+          <t>日本のすぐ隣の安全保障に関わる話を知って、ニュースを自分で読み解けるようになりたい。中国の弱点を知る安心感。</t>
         </is>
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
+          <t>サムネ「なぜ奪われた？」「中国を塞ぐ『15km』」と、途中で止まる矢印の地図で、「大国の中国が日本海に出られない理由と、その土地がロシアに取られた経緯がわかる」と受け取れる。概要欄で「幕末の日本に与えた恐怖」「中国の地政学的な弱点」まで触れると約束している。</t>
+        </is>
+      </c>
+      <c r="K15" s="6" t="inlineStr">
+        <is>
+          <t>日本人が気になる隣国の話を、地図上の小さな数字（15km）で具体的にする。矢印が止まる絵で答えの一部を見せて、「なぜ？」を強くしている。</t>
+        </is>
+      </c>
+      <c r="L15" s="6" t="inlineStr">
+        <is>
           <t>驚き、日本の安全保障に関わることへの関心</t>
         </is>
       </c>
-      <c r="K15" s="6" t="inlineStr">
+      <c r="M15" s="6" t="inlineStr">
         <is>
           <t>【構図】東アジアの白地図を全面に使い、ロシア沿海州を赤く塗る。中国から日本海へ向かう赤い破線の矢印が、海の手前で止まる。文字は左上に寄せる。
 【文字】①「なぜ奪われた？」7文字：赤＋白縁、高さ約15%。②「中国を塞ぐ『15km』」11文字：白＋「15km」だけ黄色、黒縁。地名（中国・北朝鮮・韓国・日本海・ロシア）は明朝体の小さいラベル。
@@ -1330,15 +1482,25 @@
       </c>
       <c r="I16" s="6" t="inlineStr">
         <is>
-          <t>中央アジアが5つの国に分かれた理由がわかる</t>
+          <t>「〜スタン」という国が多いという長年のモヤモヤを解消したい。</t>
         </is>
       </c>
       <c r="J16" s="6" t="inlineStr">
         <is>
+          <t>サムネ「なぜ5つに分かれた？」と光る国境線の地図で、「名前の似た5つの国ができた理由がわかる」と受け取れる。小見出し「複雑すぎる国境線の謎」で、国境線の不自然な形にも答えると示す。概要欄で、大国（イギリスとロシア、ソ連）の思惑が答えだと明かしている。</t>
+        </is>
+      </c>
+      <c r="K16" s="6" t="inlineStr">
+        <is>
+          <t>誰もが一度は思う素朴な疑問を、そのまま問いにする。「5つ」だけ黄色にして数で引っかけ、シルクロードのロマンを絵で足している。</t>
+        </is>
+      </c>
+      <c r="L16" s="6" t="inlineStr">
+        <is>
           <t>素朴な疑問が解ける好奇心</t>
         </is>
       </c>
-      <c r="K16" s="6" t="inlineStr">
+      <c r="M16" s="6" t="inlineStr">
         <is>
           <t>【構図】中央アジアの立体地図を全面に置き、5か国を色分けして赤く光る国境線で囲む。左下に夕日を背にしたラクダの隊商のシルエット（シルクロードの象徴）。
 【文字】①「なぜ5つに分かれた？」10文字：白＋「5つ」だけ黄色、黒縁、高さ約16%。②小見出し「複雑すぎる国境線の謎」10文字：白＋「国境線」黄色、黒帯。国名ラベルは白。
@@ -1385,15 +1547,25 @@
       </c>
       <c r="I17" s="6" t="inlineStr">
         <is>
-          <t>ロシアがアラスカを安値で手放した理由と、その後の皮肉な結末がわかる</t>
+          <t>「歴史上の大損」を見て、もったいないと驚きたい。損をした側の本当の事情を知りたい。</t>
         </is>
       </c>
       <c r="J17" s="6" t="inlineStr">
         <is>
+          <t>サムネ「アラスカをロシアはなぜ売った？」と「$7,200,000」の矢印で、「信じられない安値で売った理由がわかる」と受け取れる。タイトルは「世界最大の宝の山」「坪単価0.2円」で損の大きさをあおり、サムネで正体（アラスカ）を明かす。概要欄で「本当に愚かだったから手放したのか？」と、通説をひっくり返すと約束している。</t>
+        </is>
+      </c>
+      <c r="K17" s="6" t="inlineStr">
+        <is>
+          <t>金額という誰でもわかる物差しで「損」を見せる。タイトルで正体を隠し、サムネで明かす分担。概要欄で「愚かな取引」という通説に反論する構成にして、ただの雑学ではない深さを出している。</t>
+        </is>
+      </c>
+      <c r="L17" s="6" t="inlineStr">
+        <is>
           <t>「もったいない」という驚き、皮肉の面白さ</t>
         </is>
       </c>
-      <c r="K17" s="6" t="inlineStr">
+      <c r="M17" s="6" t="inlineStr">
         <is>
           <t>【構図】暗い紺の背景に、左にロシア（赤）、右にアラスカ（金色に発光）と北米（グレー）の地図。中央の金色の矢印に「$7,200,000」と書き、ロシアからアラスカへ「売った」流れを見せる。
 【文字】「アラスカを／ロシアはなぜ売った？」2行13文字：「アラスカ」「ロシア」は黄色、それ以外は白、黒縁、左上、高さ約40%。矢印の中に金額「$7,200,000」。
@@ -1440,15 +1612,25 @@
       </c>
       <c r="I18" s="6" t="inlineStr">
         <is>
-          <t>双子のように似たオランダとベルギーが、なぜ別の国になったかがわかる</t>
+          <t>似ている2国の違いの理由を知って、ヨーロッパの地図が違って見える体験をしたい。</t>
         </is>
       </c>
       <c r="J18" s="6" t="inlineStr">
         <is>
+          <t>サムネ「なぜ別の国になったのか？」「言葉も近い、隣同士なのに…」と2色の古地図で、「双子のような2国が分かれたドラマを見られる」と受け取れる。タイトル「引き裂かれた歴史」で悲劇性を、概要欄の「一本のオペラ」が独立のきっかけという意外な事実でドラマを約束している。</t>
+        </is>
+      </c>
+      <c r="K18" s="6" t="inlineStr">
+        <is>
+          <t>「似ているのに別」の矛盾の型。古地図の風合いで、大人がゆっくり楽しむ歴史物語として見せている（概要欄のタグに「大人の教養」）。</t>
+        </is>
+      </c>
+      <c r="L18" s="6" t="inlineStr">
+        <is>
           <t>好奇心、「引き裂かれた」というドラマ性</t>
         </is>
       </c>
-      <c r="K18" s="6" t="inlineStr">
+      <c r="M18" s="6" t="inlineStr">
         <is>
           <t>【構図】羊皮紙風の古地図に、オランダ（オレンジ）とベルギー（緑）を塗り、国境を赤く光らせる。左上に大きな問い、右下に札。
 【文字】①「なぜ別の国に／なったのか？」2行12文字：1行目は金色、2行目は白の太い明朝体、高さ約38%。②小見出し「言葉も近い、隣同士なのに…」13文字：白＋「隣同士」黄色、黒帯。③右下の札「オランダとベルギーの謎」11文字：金の縁取り。
@@ -1495,15 +1677,25 @@
       </c>
       <c r="I19" s="6" t="inlineStr">
         <is>
-          <t>国旗も言葉も似ている北欧の国々が、なぜ一つの国にならなかったかがわかる</t>
+          <t>「似ているのになぜ？」の答えを知ってすっきりしたい。平和なイメージの北欧の裏側を知りたい。</t>
         </is>
       </c>
       <c r="J19" s="6" t="inlineStr">
         <is>
+          <t>サムネ「なぜ『一つの国』じゃない？」と塗り分けた北欧の地図だけで、問いがそのまま約束になっている。タイトル「国旗も言葉もほぼ同じなのに」で矛盾を強める。概要欄で「残酷で血塗られた兄弟たちの歴史」「ストックホルムの血浴」と、平和なイメージを裏切る話だと示している。</t>
+        </is>
+      </c>
+      <c r="K19" s="6" t="inlineStr">
+        <is>
+          <t>問いの強さだけで勝負する（30本中最高の52.5倍で、サムネは最もシンプル）。地図を見せれば矛盾が伝わるので、飾りを足していない。</t>
+        </is>
+      </c>
+      <c r="L19" s="6" t="inlineStr">
+        <is>
           <t>好奇心、似ているのに別々という意外性</t>
         </is>
       </c>
-      <c r="K19" s="6" t="inlineStr">
+      <c r="M19" s="6" t="inlineStr">
         <is>
           <t>【構図】北欧の地図だけを全面に置き、ノルウェー（えんじ）・スウェーデン（青）・フィンランド（水色）・デンマーク（赤）を塗り分けて、国名を白文字で入れる。装飾はほぼなし。
 【文字】「なぜ「一つの国」じゃない？」13文字：黄色の太い明朝体、上部1行、高さ約12%・幅約90%。国名ラベルは白。
@@ -1550,15 +1742,25 @@
       </c>
       <c r="I20" s="6" t="inlineStr">
         <is>
-          <t>同じ半島にあるスペインとポルトガルが、なぜ2つに分かれたかがわかる</t>
+          <t>地図を見て感じた違和感（同じ半島なのに2つの国）の答えを知りたい。</t>
         </is>
       </c>
       <c r="J20" s="6" t="inlineStr">
         <is>
+          <t>サムネ「イベリア半島の『二分割』という歴史的謎」と赤と青の地図で、「同じ半島に2つの国がある理由がわかる」と受け取れる。タイトル「一つ屋根の下に二つの家族？」で家族のたとえにして親しみやすくする。概要欄で「大国スペインはなぜ小さなポルトガルを飲み込めなかったのか」と、強い側が勝てなかった謎に絞っている。</t>
+        </is>
+      </c>
+      <c r="K20" s="6" t="inlineStr">
+        <is>
+          <t>2色の対比だけで「分かれている」を一目で見せる。家族のたとえで、国の話を人間関係のドラマに置き換えている。</t>
+        </is>
+      </c>
+      <c r="L20" s="6" t="inlineStr">
+        <is>
           <t>好奇心、「一つ屋根の下の二つの家族」というたとえによる親しみ</t>
         </is>
       </c>
-      <c r="K20" s="6" t="inlineStr">
+      <c r="M20" s="6" t="inlineStr">
         <is>
           <t>【構図】額縁のように囲んだイベリア半島の地図で、スペイン（赤）とポルトガル（青）の2色だけに塗り分ける。上に1行のタイトル。
 【文字】①上「イベリア半島の「二分割」という歴史的謎」17文字：金色の明朝体、高さ約10%と小さめ。②地図上の国名「スペイン」（金色・大きい）、「ポルトガル」（白）。
@@ -1605,15 +1807,25 @@
       </c>
       <c r="I21" s="6" t="inlineStr">
         <is>
-          <t>同じ言語なのに別の国である理由と、2国の愛憎の歴史がわかる</t>
+          <t>同じ言葉を話すのに別の国という矛盾をすっきりさせたい。兄弟げんかのような愛憎ドラマを楽しみたい。</t>
         </is>
       </c>
       <c r="J21" s="6" t="inlineStr">
         <is>
+          <t>サムネ「同じ言語、全く違う国」「『赤の他人』になった理由」と、亀裂で割れた地図で、「兄弟のような2国が他人になるまでの因縁がわかる」と受け取れる。タイトル「複雑すぎる愛憎史」で感情のドラマを約束する。概要欄でハプスブルク家、ビスマルク、ナチスによる併合まで1000年のドラマを予告している。</t>
+        </is>
+      </c>
+      <c r="K21" s="6" t="inlineStr">
+        <is>
+          <t>矛盾の型に「愛憎」という人間関係の言葉を足して、国の歴史を家族ドラマにする。国旗の色と稲妻の亀裂で、対立を絵で見せている。</t>
+        </is>
+      </c>
+      <c r="L21" s="6" t="inlineStr">
+        <is>
           <t>好奇心、愛憎ドラマへの興味</t>
         </is>
       </c>
-      <c r="K21" s="6" t="inlineStr">
+      <c r="M21" s="6" t="inlineStr">
         <is>
           <t>【構図】中央にドイツ（黄色に発光）とオーストリア（赤に発光）の地図。左右に両国の国旗と名所（左：ブランデンブルク門の夜景、右：湖畔の町と教会）。稲妻のような亀裂で左右を分ける。
 【文字】①「同じ言語、全く違う国」10文字：黄色＋黒縁、高さ約19%・幅いっぱい。②小見出し「ドイツとオーストリアが『赤の他人』になった理由」22文字：白＋「赤の他人」だけ赤、黒帯。
@@ -1660,15 +1872,25 @@
       </c>
       <c r="I22" s="6" t="inlineStr">
         <is>
-          <t>ヒトラーの後継者だったゲーリングが、どんな最期を迎えたかがわかる</t>
+          <t>権力の頂点にいた悪人が、最後にどうなったかを見届けたい。悪が報いを受けるのを見て納得したい。</t>
         </is>
       </c>
       <c r="J22" s="6" t="inlineStr">
         <is>
+          <t>サムネ「ナチス史上最悪の男」「ゲーリングの最期」と落ち着いた顔の肖像で、「最悪と呼ばれた男の最後」を見届けられると受け取れる。タイトル「残酷すぎる最期」「ヒトラーの後継者」で、頂点からの転落を約束する。概要欄から、第一次世界大戦の飛行隊の司令官から空軍の最高司令官、そして最期までの生涯を追う構成だとわかる。</t>
+        </is>
+      </c>
+      <c r="K22" s="6" t="inlineStr">
+        <is>
+          <t>「最期」というゴールを先に見せて、生涯全体を見させる。決まった型（上下の帯＋肖像）で、関連動画からシリーズとしてつないでいる。</t>
+        </is>
+      </c>
+      <c r="L22" s="6" t="inlineStr">
+        <is>
           <t>怖いもの見たさ、因果応報への関心</t>
         </is>
       </c>
-      <c r="K22" s="6" t="inlineStr">
+      <c r="M22" s="6" t="inlineStr">
         <is>
           <t>【構図】中央に人物の胸像（制服姿のゲーリング）、上下を文字の帯ではさむ追伸の定番型。
 【文字】①上「ナチス史上最悪の男」9文字：白、高さ約18%・幅いっぱい。②下「ゲーリングの最期」8文字：赤、高さ約22%。上で人物の「肩書き」、下で「名前＋最期」。
@@ -1715,15 +1937,25 @@
       </c>
       <c r="I23" s="6" t="inlineStr">
         <is>
-          <t>22歳で処刑されたナチスの女性看守が、何をして、どう最期を迎えたかがわかる</t>
+          <t>「若い女性がなぜそこまで残酷になれたのか」という、理解できないものへの好奇心。悪人が裁かれる結末を見届けたい。</t>
         </is>
       </c>
       <c r="J23" s="6" t="inlineStr">
         <is>
+          <t>サムネ「ナチス史上最悪の女」と、にらむ若い女性の顔で、「若い女性が最悪と呼ばれた理由とその最期がわかる」と受け取れる。タイトル「22歳で処刑された悪魔」で年齢と結末の衝撃を足す。概要欄で「史上最年少で死刑を執行された女性」「最大3万人の命を管理」と、普通の少女が看守になるまでの経緯も見せると約束している。</t>
+        </is>
+      </c>
+      <c r="K23" s="6" t="inlineStr">
+        <is>
+          <t>いつもの「最悪の男」を「女」に変えて意外性を作る（チャンネル最高の29.4倍）。若い女性の顔と「悪魔」の落差で目を止めさせている。</t>
+        </is>
+      </c>
+      <c r="L23" s="6" t="inlineStr">
+        <is>
           <t>恐怖と嫌悪、「若い女性が」という意外性</t>
         </is>
       </c>
-      <c r="K23" s="6" t="inlineStr">
+      <c r="M23" s="6" t="inlineStr">
         <is>
           <t>【構図】中央に若い女性の顔のアップ、上下を文字の帯ではさむ定番型。他の回より背景が明るい（ベージュの壁）ので顔がよく目立つ。
 【文字】①上「ナチス史上最悪の女」9文字：白、高さ約18%。②下「イルマ・グレーゼの最期」11文字：赤、高さ約18%。「男」ではなく「女」にした意外性。
@@ -1770,15 +2002,25 @@
       </c>
       <c r="I24" s="6" t="inlineStr">
         <is>
-          <t>数百万人の虐殺に関わったハイドリヒの人物像と、その最期がわかる</t>
+          <t>ナチスの中でも特に恐れられた人物の正体を知りたい。悪人が報いを受けるのを見届けたい。</t>
         </is>
       </c>
       <c r="J24" s="6" t="inlineStr">
         <is>
+          <t>サムネ「ナチス史上最悪の男」「ハイドリヒの最期」で、「最悪の男がどう死んだか」を見届けられると受け取れる。タイトル「ナチスが最も恐れた男」で、身内からも恐れられるほどの怖さを約束する。概要欄で「38歳の若さで暗殺」と結末の種類を明かし、ゲーリングやアイヒマンとの関係も見せると示している。</t>
+        </is>
+      </c>
+      <c r="K24" s="6" t="inlineStr">
+        <is>
+          <t>定番の型で、名前を知らない人にも「最悪」の肩書きで興味を持たせる。概要欄で他の回の人物の名前を出し、シリーズ内を回遊させている。</t>
+        </is>
+      </c>
+      <c r="L24" s="6" t="inlineStr">
+        <is>
           <t>恐怖、悪人が裁かれるかどうかへの関心</t>
         </is>
       </c>
-      <c r="K24" s="6" t="inlineStr">
+      <c r="M24" s="6" t="inlineStr">
         <is>
           <t>【構図】中央に人物の胸像、上下を文字の帯ではさむ定番型。背景の左が明るく右が黒い。
 【文字】①上「ナチス史上最悪の男」9文字：白、高さ約18%。②下「ハイドリヒの最期」8文字：赤、高さ約22%。
@@ -1825,15 +2067,25 @@
       </c>
       <c r="I25" s="6" t="inlineStr">
         <is>
-          <t>毛沢東が死ぬまでの44日間に何が起きたかがわかる</t>
+          <t>巨大な権力者の最後の日々に何が起きたかをのぞき見たい。死が隠されたという裏話を知りたい。</t>
         </is>
       </c>
       <c r="J25" s="6" t="inlineStr">
         <is>
+          <t>サムネ「残酷すぎる44日間」「毛沢東の最期」と穏やかな薄笑いの肖像で、「最後の44日間に起きた残酷な出来事を見られる」と受け取れる。タイトル「4500万人を殺した男」で罪の大きさを示す。概要欄で「なぜ彼の死は16時間もの間隠されたのか」と、権力の裏側の謎を約束している。</t>
+        </is>
+      </c>
+      <c r="K25" s="6" t="inlineStr">
+        <is>
+          <t>期間を区切ることで、生涯ではなく最後の数日間の密室劇として見せる。数字（44日間、4500万人）を2つ並べて、重さと具体性を出している。</t>
+        </is>
+      </c>
+      <c r="L25" s="6" t="inlineStr">
+        <is>
           <t>怖いもの見たさ、独裁者の結末への関心</t>
         </is>
       </c>
-      <c r="K25" s="6" t="inlineStr">
+      <c r="M25" s="6" t="inlineStr">
         <is>
           <t>【構図】中央に人物の胸像、上下を文字の帯ではさむ定番型。文字が他の回より大きい。
 【文字】①上「残酷すぎる44日間」9文字（「すぎる」だけ小さく）：白、高さ約23%。②下「毛沢東の最期」6文字：赤、高さ約29%。肩書きではなく「期間＋残酷」を上に置いた形。
@@ -1880,15 +2132,25 @@
       </c>
       <c r="I26" s="6" t="inlineStr">
         <is>
-          <t>スターリンの右腕だった秘密警察長官ベリヤの正体と結末がわかる</t>
+          <t>独裁者の陰にいた「本当に怖い人」の正体を知りたい。仲間に裏切られて終わる悪人の結末を見届けたい。</t>
         </is>
       </c>
       <c r="J26" s="6" t="inlineStr">
         <is>
+          <t>サムネ「大量虐殺した悪魔」「ベリヤの最期」と冷たい目の丸眼鏡の男で、「悪魔と呼ばれた男の正体と最期がわかる」と受け取れる。タイトル「スターリンが絶賛したソ連の秘密警察長官」で、独裁者の右腕という位置づけを示す。概要欄で、仲間に裏切られて銃殺されたと結末を明かしている。</t>
+        </is>
+      </c>
+      <c r="K26" s="6" t="inlineStr">
+        <is>
+          <t>有名なスターリンの名前を借りて、知名度の低い人物を見せる。秘密警察という陰の権力の怖さで引いている。</t>
+        </is>
+      </c>
+      <c r="L26" s="6" t="inlineStr">
+        <is>
           <t>恐怖、権力者の裏側への好奇心</t>
         </is>
       </c>
-      <c r="K26" s="6" t="inlineStr">
+      <c r="M26" s="6" t="inlineStr">
         <is>
           <t>【構図】中央に人物の胸像、上下を文字の帯ではさむ定番型。
 【文字】①上「大量虐殺した悪魔」8文字：白、高さ約22%。②下「ベリヤの最期」6文字：赤、高さ約28%。
@@ -1935,15 +2197,25 @@
       </c>
       <c r="I27" s="6" t="inlineStr">
         <is>
-          <t>「砂漠の狐」と呼ばれた名将ロンメルが、なぜヒトラーに殺されたかがわかる</t>
+          <t>有能な英雄が理不尽に殺される悲劇に心を動かされたい。ナチスの中の「まともな人」を知りたい。</t>
         </is>
       </c>
       <c r="J27" s="6" t="inlineStr">
         <is>
+          <t>サムネ「ナチス最高の天才」「ロンメルの最期」と遠くを見る横顔で、「天才と呼ばれた将軍の悲劇的な最期を見られる」と受け取れる。タイトル「ヒトラーに殺された男」「砂漠の狐」で、味方に殺される理不尽を約束する。概要欄で「敵のチャーチル首相からも賞賛」「暗殺未遂事件への関与を疑われ自害」と、英雄の物語であることを示している。</t>
+        </is>
+      </c>
+      <c r="K27" s="6" t="inlineStr">
+        <is>
+          <t>「最悪」ではなく「最高」の人物で、悪人シリーズの中に悲劇の英雄枠を作る。同じ型のまま、動かす感情の種類（怖さ→同情）だけを変えている。</t>
+        </is>
+      </c>
+      <c r="L27" s="6" t="inlineStr">
+        <is>
           <t>悲劇への同情、英雄が裏切られる理不尽さへの怒り</t>
         </is>
       </c>
-      <c r="K27" s="6" t="inlineStr">
+      <c r="M27" s="6" t="inlineStr">
         <is>
           <t>【構図】中央に制帽姿の人物の横顔、上下を文字の帯ではさむ定番型。左の背景に別の白黒写真がうっすら重なる。
 【文字】①上「ナチス最高の天才」8文字：白、高さ約21%。②下「ロンメルの最期」7文字：赤、高さ約23%。他の回の「最悪」ではなく「最高」の英雄枠。
@@ -1990,15 +2262,25 @@
       </c>
       <c r="I28" s="6" t="inlineStr">
         <is>
-          <t>ユダヤ人移送を指揮したアイヒマンの人物像と、逃亡から処刑までの最期がわかる</t>
+          <t>逃げた悪人が最後に捕まる「正義の結末」を見届けたい。普通に見える人が大量殺人に関わった理由を知りたい。</t>
         </is>
       </c>
       <c r="J28" s="6" t="inlineStr">
         <is>
+          <t>サムネ「ナチスが最も恐れた男」「アイヒマンの最期」と薄笑いの肖像で、「恐れられた男の最期」を見届けられると受け取れる。タイトル「500万人を殺した男」で罪の大きさを示す。概要欄で「アルゼンチンに逃亡した彼に訪れた悲劇」と、逃亡から捕まるまでのサスペンスを約束している。</t>
+        </is>
+      </c>
+      <c r="K28" s="6" t="inlineStr">
+        <is>
+          <t>定番の型。概要欄で「逃亡」という追跡劇の要素を出し、ただの人物紹介ではなく物語として見せている。</t>
+        </is>
+      </c>
+      <c r="L28" s="6" t="inlineStr">
+        <is>
           <t>恐怖、正義が下されるかどうかへの関心</t>
         </is>
       </c>
-      <c r="K28" s="6" t="inlineStr">
+      <c r="M28" s="6" t="inlineStr">
         <is>
           <t>【構図】中央に制帽姿の人物、上下を文字の帯ではさむ定番型。左端にハーケンクロイツの腕章が見える。
 【文字】①上「ナチスが最も恐れた男」10文字：白、高さ約18%。②下「アイヒマンの最期」8文字：赤、高さ約21%。
@@ -2045,15 +2327,25 @@
       </c>
       <c r="I29" s="6" t="inlineStr">
         <is>
-          <t>スターリンが倒れてから死ぬまでの7日間に何が起きたかがわかる</t>
+          <t>恐れられた独裁者が、最後は誰にも助けられずに死んでいく皮肉を見届けたい。</t>
         </is>
       </c>
       <c r="J29" s="6" t="inlineStr">
         <is>
+          <t>サムネ「スターリンの／最期の7日間」の大きな文字で、「独裁者の最後の1週間に何が起きたかを見られる」と受け取れる。タイトル「1000万人を殺した男」で罪の大きさを足す。概要欄で「医師が呼ばれるまでに13時間もの空白」「側近たちの思惑とは？」と、側近に見捨てられた密室劇を約束している。</t>
+        </is>
+      </c>
+      <c r="K29" s="6" t="inlineStr">
+        <is>
+          <t>知名度が一番高い人物なので、文字を名前と期間だけにして最大の大きさで見せる。概要欄の「13時間の空白」で、陰謀めいた謎を足している。</t>
+        </is>
+      </c>
+      <c r="L29" s="6" t="inlineStr">
+        <is>
           <t>怖いもの見たさ、独裁者が見捨てられる皮肉</t>
         </is>
       </c>
-      <c r="K29" s="6" t="inlineStr">
+      <c r="M29" s="6" t="inlineStr">
         <is>
           <t>【構図】中央に人物の胸像、上下を文字の帯ではさむ定番型。文字がとても大きく、上下で1つの文になっている。
 【文字】①上「スターリンの」6文字：白、高さ約26%。②下「最期の7日間」6文字：赤、高さ約31%（30本中で最大級）。名前＋期間だけの短い文。
@@ -2100,15 +2392,25 @@
       </c>
       <c r="I30" s="6" t="inlineStr">
         <is>
-          <t>ムッソリーニが逆さ吊りで公開処刑されるまでの10日間がわかる</t>
+          <t>独裁者が民衆に裁かれる劇的な結末を見届けたい。</t>
         </is>
       </c>
       <c r="J30" s="6" t="inlineStr">
         <is>
+          <t>サムネ「ムッソリーニの／最期の10日間」と側近に囲まれた尊大な顔で、「最後の10日間の転落を見られる」と受け取れる。タイトル「逆さ吊りで公開処刑」で、結末の衝撃的な場面を先に明かす。概要欄で「法を無視した私刑と正義が物議を醸す」と、見た後に考えさせる問いも置いている。</t>
+        </is>
+      </c>
+      <c r="K30" s="6" t="inlineStr">
+        <is>
+          <t>結末（逆さ吊り）を先に明かし、「そこに至るまで」を見させる。スターリン回と同じ「〇〇の／最期の〇日間」型で、シリーズの見た目をそろえている。</t>
+        </is>
+      </c>
+      <c r="L30" s="6" t="inlineStr">
+        <is>
           <t>衝撃、怖いもの見たさ</t>
         </is>
       </c>
-      <c r="K30" s="6" t="inlineStr">
+      <c r="M30" s="6" t="inlineStr">
         <is>
           <t>【構図】中央に軍帽・制服のムッソリーニ、その周りを帽子の兵士や側近が囲む集合写真。上下を文字の帯ではさむ。
 【文字】①上「ムッソリーニの」7文字：白、高さ約25%。②下「最期の10日間」7文字：赤、高さ約28%。スターリンの回と同じ「名前の／最期の○日間」型。
@@ -2155,15 +2457,25 @@
       </c>
       <c r="I31" s="6" t="inlineStr">
         <is>
-          <t>ヒトラーが死ぬまでの最後の48時間に、地下壕で何が起きていたかがわかる</t>
+          <t>誰もが知る独裁者の、まだ知らない最後の場面を知りたい。</t>
         </is>
       </c>
       <c r="J31" s="6" t="inlineStr">
         <is>
+          <t>サムネ「ヒトラー最後の48時間」と四隅の「2通の遺言書を残す」「突然エヴァと結婚する」「青酸カリで愛犬を毒殺」「ヘルマンを処刑する」で、「地下壕の最後の2日間に起きた奇妙な出来事を具体的に見られる」と受け取れる。見どころを4つ先に見せる約束で、概要欄も同じ見どころを並べている。</t>
+        </is>
+      </c>
+      <c r="K31" s="6" t="inlineStr">
+        <is>
+          <t>一番知名度の高い人物で、チャンネルの入口を作った初期の回。見どころを四隅に並べて「知らない話がある」と示す。後の回では、これを上下の帯＋肖像の型に絞り込んでいる。</t>
+        </is>
+      </c>
+      <c r="L31" s="6" t="inlineStr">
+        <is>
           <t>怖いもの見たさ、緊迫感</t>
         </is>
       </c>
-      <c r="K31" s="6" t="inlineStr">
+      <c r="M31" s="6" t="inlineStr">
         <is>
           <t>【構図】他の9本と違う型。背景を4分割（左上：ヒトラーの顔、右上：女性〈エヴァ〉の白黒写真、左下：紫の稲妻、右下：男の白黒写真）し、四隅に小見出しで動画の中身を予告する。中央に大文字。
 【文字】①中央「ヒトラー」4文字：白＋黒縁。②中央下「最後の48時間」7文字：赤＋白縁、高さ約21%。③四隅の小見出し「2通の遺言書を残す」「突然エヴァと結婚する」「青酸カリで愛犬を毒殺」「ヘルマンを処刑する」（各8〜10文字、白）。

--- a/youtube-world-history-research/output/video_analysis_sheet_filled.xlsx
+++ b/youtube-world-history-research/output/video_analysis_sheet_filled.xlsx
@@ -531,7 +531,7 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>サムネの構図・文字数・色・人物の表情</t>
+          <t>サムネの構図・文字数・色・人物の表情・フォント</t>
         </is>
       </c>
     </row>
@@ -596,7 +596,8 @@
 【文字】「最強が負けた日」1行7文字。文字帯は高さの約34%（縁取り込み）、横幅の約95%まで広げ、左右の余白はほぼなし。1文字の高さは画像の約3割（漢字1字＝幅の約16%）。字間は詰めている。「最強」と「負けた」の正反対の言葉をぶつけ、誰の話かは文字で明かさない（タイトル側で「モンゴル」と明かす分担）。
 【色】背景は茶色・くすんだ金・暗い緑の古画トーンで全体に暗め。目立つ色は2つだけ：文字の黄色（太いゴシック体＋黒の縁取り）と、人物を囲む赤い縁取り。
 【人物の表情】顔は小さく表情はほぼ読めない。のけぞる体・投げ出された手足・崩れる馬など、体の動きで「負けた瞬間」を見せている。
-【絵の風合い】中世の戦記を描いた写本・絵巻の挿絵風。ペルシア細密画（ミニアチュール）風の可能性が高い（平らな金茶色の背景、点々と描いた草、立体感の少ない線描）。</t>
+【絵の風合い】中世の戦記を描いた写本・絵巻の挿絵風。ペルシア細密画（ミニアチュール）風の可能性が高い（平らな金茶色の背景、点々と描いた草、立体感の少ない線描）。
+【フォント】極太ゴシック体（候補：源ノ角ゴシック Heavy／Noto Sans JP Black）を黄色＋太い黒縁で1行。字間をほぼ詰め、文字の大小差は付けない。飾りのない太いゴシックで「見出し・ニュース速報」のような強さを出している。</t>
         </is>
       </c>
     </row>
@@ -661,7 +662,8 @@
 【文字】4要素で画面の約半分が文字。①上の帯「モンゴル目線で見る元寇」11文字：高さの約16%・幅の約98%、黄色＋黒縁。②左上の吹き出し「怖い怖い怖い怖い怖」9文字（わざと途中で切る）：白い四角に黒文字、高さ約12%・幅約47%。③右の叫び吹き出し「逃がすかおらあぁぁ」約9文字：白いギザギザ吹き出しに赤文字。④下の帯「トラウマ体験すぎる…」10文字：高さの約20%・幅の約95%で一番大きい、赤＋白縁。主役の帯文字は合計21文字。「〜すぎる…」「おらあぁぁ」「怖い」連打など、ネット口語・マンガのセリフ表現で硬い題材をくだけさせている。
 【色】背景は褐色・セピアの古画トーン。文字は上が黄色・下が赤の強い2色を上下に分け、白い吹き出しが間をつなぐ。モンゴル兵は黄土色・オレンジ系で一塊に、武者は青・赤・金など色数が多くこちらが目立つ。
 【人物の表情】モンゴル兵：目を見開き口を開け、頭を抱える・身をすくめる誇張された恐怖顔（ややコミカル）。武者：目をむき歯をむき出しにした鬼の形相で叫ぶ。文字を読まなくても「怖がる側／襲う側」が一瞬でわかる。
-【絵の風合い】右の武者は江戸の武者絵（浮世絵・錦絵）風（歌川国芳のような躍動感）。左のモンゴル兵は古い合戦絵巻の人物をマンガ的に誇張した描き方。</t>
+【絵の風合い】右の武者は江戸の武者絵（浮世絵・錦絵）風（歌川国芳のような躍動感）。左のモンゴル兵は古い合戦絵巻の人物をマンガ的に誇張した描き方。
+【フォント】上下の帯は極太ゴシック体（候補：源ノ角ゴシック Heavy／Noto Sans JP Black）（上：黄＋黒縁、下：赤＋白縁）。下帯は「トラウマ体験」を大きく、「すぎる…」を小さくして語尾を軽くする。吹き出しは太めのゴシック体で、「逃がすかおらあぁぁ」は赤字で小さい「ぁ」を混ぜて叫びを表す。全部ゴシックで、マンガのセリフのような軽さ。</t>
         </is>
       </c>
     </row>
@@ -726,7 +728,8 @@
 【文字】4要素の会話劇。①上帯「海外から見た倭寇、怖すぎる」13文字：黒帯に黄色、高さ約14%・幅約96%。②左の吹き出し「お前ら何者？」6文字：白地に黒。③右の吹き出し「え、ただのゴロツキだよ？」12文字：黒＋「ただのゴロツキ」だけ赤。④下の大吹き出し「じゃあなんでそんな強ぇんだよ…」15文字：白地に赤、高さ約18%で一番大きい。「問い→とぼけ→ツッコミ」の3段で笑わせる。
 【色】黒帯×黄色、中央の赤線、白い吹き出しに赤文字。絵は青い海と黄土・赤の衣服。
 【人物の表情】左の兵は目と口を開けた驚き・恐怖の顔。右の倭寇は余裕のニヤけ顔で、強さと軽さの落差を見せる。
-【絵の風合い】中国・日本の古い絵巻（倭寇図巻のような合戦絵巻）風の線描に彩色したイラスト。</t>
+【絵の風合い】中国・日本の古い絵巻（倭寇図巻のような合戦絵巻）風の線描に彩色したイラスト。
+【フォント】上帯は極太ゴシック体（候補：源ノ角ゴシック Heavy／Noto Sans JP Black）（黄）。吹き出しは太ゴシック体の黒字で、下の大吹き出しだけ赤の極太ゴシック。「強ぇ」の小さい「ぇ」でくだけた口調を文字でも見せる。</t>
         </is>
       </c>
     </row>
@@ -791,7 +794,8 @@
 【文字】「コーラの歴史」6文字のみ、上部約3割に横幅いっぱい。「コーラ」は赤〜オレンジの燃えるような立体文字、「の歴史」は金色の立体文字。このチャンネルでは珍しく文字が少ない。
 【色】全体がコーラの琥珀色・茶色と赤・金でまとまっている。
 【人物の表情】兵士も女性も笑顔で瓶から飲んでいる（楽しさ・親しみ）。
-【絵の風合い】1940年代アメリカのヴィンテージ広告ポスター風の写実イラスト（AI生成らしい質感）。※再生数÷登録者数は1.1倍で30本中最低。いつもの「会話劇＋ツッコミ」型を外した回でもある。</t>
+【絵の風合い】1940年代アメリカのヴィンテージ広告ポスター風の写実イラスト（AI生成らしい質感）。※再生数÷登録者数は1.1倍で30本中最低。いつもの「会話劇＋ツッコミ」型を外した回でもある。
+【フォント】「コーラ」は極太の毛筆体（筆のかすれ・はらいが残る楷書〜行書。候補：衡山毛筆フォント系）に、赤〜オレンジのグラデーションと立体の厚み・光沢を付けた加工。「の歴史」は金色の立体の毛筆体。このチャンネルで唯一の「広告・映画タイトル風の加工文字」で、いつものゴシックの会話劇から外れている。</t>
         </is>
       </c>
     </row>
@@ -856,7 +860,8 @@
 【文字】「実在した異常な国」8文字：赤＋白の縁取り＋黒い影、高さ約24%・幅約95%、画面の真ん中。その下に「11選」白＋黒縁。
 【色】4枚の絵はそれぞれ緑・茶・青の別トーンで、中央の赤い大文字が一番目立つ。
 【人物の表情】人物はほぼなし（左下に小さな兵の列のみ）。
-【絵の風合い】中世の彩色地図・版画風イラストと写真のコラージュ。「凡ミスで滅んだ国3選」と同じテンプレート。</t>
+【絵の風合い】中世の彩色地図・版画風イラストと写真のコラージュ。「凡ミスで滅んだ国3選」と同じテンプレート。
+【フォント】「実在した異常な国」は極太の毛筆体（筆のかすれ・はらいが残る楷書〜行書。候補：衡山毛筆フォント系）（赤＋白の縁取り＋黒い影）。「11選」は極太ゴシック体（候補：源ノ角ゴシック Heavy／Noto Sans JP Black）（白＋黒縁）。題名は毛筆で重く、数字はゴシックで読みやすく、と書体を分けている。</t>
         </is>
       </c>
     </row>
@@ -921,7 +926,8 @@
 【文字】①上帯「先頭の兵士って、何考えてたの？」15文字：黒帯に黄色、高さ約16%・幅いっぱい。②弓兵の吹き出し「●ぬよ？」：赤丸の伏せ字＋赤文字（「死ぬよ？」を想像させる）。③登る兵の吹き出し「ですよね。」：白地に黒。脅しへの冷静な返事でシュールな笑いを作る。
 【色】黒帯×黄色、背景の黄緑ベタがとても目立つ。白い城壁と赤い服、赤い伏せ字。
 【人物の表情】弓兵は狙いを定める真顔、登る兵は無表情で淡々。表情は控えめで、吹き出しのセリフで感情を作っている。
-【絵の風合い】鉛筆の線画に水彩で色をつけた、図鑑・教科書の挿絵のような手描き風イラスト。背景だけ単色のベタ塗り。</t>
+【絵の風合い】鉛筆の線画に水彩で色をつけた、図鑑・教科書の挿絵のような手描き風イラスト。背景だけ単色のベタ塗り。
+【フォント】上帯は極太ゴシック体（候補：源ノ角ゴシック Heavy／Noto Sans JP Black）（黄）。吹き出しは太ゴシック体で、「●ぬよ？」だけ赤。帯と吹き出しを同じゴシック系でそろえている。</t>
         </is>
       </c>
     </row>
@@ -986,7 +992,8 @@
 【文字】「凡ミスで滅んだ国」8文字：赤＋白の縁取り、高さ約22%・幅約95%。その下に「3選」白＋黒縁。
 【色】4枚の絵は青・茶・緑の別トーン、中央の赤い大文字が一番目立つ。
 【人物の表情】人物はほぼなし。
-【絵の風合い】古い彩色版画・油絵風の風景イラスト（AI生成らしい質感）。</t>
+【絵の風合い】古い彩色版画・油絵風の風景イラスト（AI生成らしい質感）。
+【フォント】「凡ミスで滅んだ国」は極太の毛筆体（筆のかすれ・はらいが残る楷書〜行書。候補：衡山毛筆フォント系）（赤＋白縁）。「3選」は極太ゴシック体（候補：源ノ角ゴシック Heavy／Noto Sans JP Black）（白＋黒縁）。「実在した異常な国11選」と同じ書体の組み合わせ。</t>
         </is>
       </c>
     </row>
@@ -1051,7 +1058,8 @@
 【文字】①「なぜ軍人は／機関銃を／嫌ったのか？」3行15文字：黄色＋黒縁、画面左半分・高さの約半分。②吹き出し「使わねぇよ」5文字：白地に黒。③大吹き出し「●●だから。」：赤丸2つの伏せ字＋赤文字、高さ約25%（答えを隠して続きを見させる）。
 【色】エメラルドグリーンのベタ背景（放射状の模様入り）、黄色の文字、赤い矢印・伏せ字。
 【人物の表情】将校たちは口ひげで、機関銃を見下ろす不機嫌・ふてぶてしい顔。
-【絵の風合い】機関銃は写真の切り抜き、将校は19世紀の新聞挿絵・風刺画風のイラスト。</t>
+【絵の風合い】機関銃は写真の切り抜き、将校は19世紀の新聞挿絵・風刺画風のイラスト。
+【フォント】左の問いは極太ゴシック体（候補：源ノ角ゴシック Heavy／Noto Sans JP Black）（黄＋黒縁）、3行とも同じ大きさ。吹き出しは太ゴシック体、「●●だから。」は赤の極太ゴシックで一番大きい。</t>
         </is>
       </c>
     </row>
@@ -1116,7 +1124,8 @@
 【文字】①上帯「※中世の歩兵、怖すぎ問題」12文字：黒帯に黄色、高さ約15%・幅いっぱい。②騎士の吹き出し「こ、降参…」。③歩兵の吹き出し「じゃ●すね？」：赤丸の伏せ字＋「す」赤（「殺すね？」を想像させる）。降参を無視する冷酷さを会話で見せる。
 【色】淡い緑のベタ背景、鎧の金・青、歩兵を囲む赤い縁取り、赤い伏せ字。
 【人物の表情】騎士は力なく倒れて顔をそむける、歩兵は無表情で淡々と斧を振り下ろす（冷酷さ）。
-【絵の風合い】中世ヨーロッパの彩飾写本の挿絵（ミニアチュール）風。</t>
+【絵の風合い】中世ヨーロッパの彩飾写本の挿絵（ミニアチュール）風。
+【フォント】上帯は極太ゴシック体（候補：源ノ角ゴシック Heavy／Noto Sans JP Black）（黄）。吹き出しは太ゴシック体で、「す」だけ赤。帯の「※」は、ネットの注意書きをまねた記号。</t>
         </is>
       </c>
     </row>
@@ -1181,7 +1190,8 @@
 【文字】①見出し「ヨーロッパ」5文字・「日本」2文字：黒地に黄色、高さ約10%。②上の吹き出し「なんで壁で囲わないの？」11文字：白地に黒（ヨーロッパ側の問い）。③下の吹き出し「ったく、分かってねぇなぁ…」13文字：白地に赤（日本側の返し）。都市を擬人化した会話劇。
 【色】黒×黄色の見出し、中央の赤線、白い吹き出し。絵は淡い水彩の色。
 【人物の表情】人物なし（都市どうしがしゃべっている設定）。
-【絵の風合い】水彩タッチの鳥瞰図イラスト。</t>
+【絵の風合い】水彩タッチの鳥瞰図イラスト。
+【フォント】見出し「ヨーロッパ」「日本」は極太ゴシック体（候補：源ノ角ゴシック Heavy／Noto Sans JP Black）（黄）。吹き出しは太ゴシック体で、下の返しだけ赤。小さい「ぇ」「ぁ」でくだけた口調を出す。</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1256,8 @@
 【文字】①上「ヒマラヤが創った『帝国』」12文字：金色グラデーションの立体文字、高さ約17%。②下「インド人口大国の理由」10文字：赤＋白縁、高さ約16%。上で謎をかけ、下で中身を示す。
 【色】青い空・黒い雨雲・金色の夕日・緑の地図の高彩度（HDR調）。
 【人物の表情】人物なし。
-【絵の風合い】AI生成の高彩度な風景イラスト＋3Dの地形図。</t>
+【絵の風合い】AI生成の高彩度な風景イラスト＋3Dの地形図。
+【フォント】上は極太ゴシック体（候補：源ノ角ゴシック Heavy／Noto Sans JP Black）に金色のグラデーション＋立体の厚み（ベベル加工）、下は赤の極太ゴシック体＋白縁でやや斜体。どちらもゴシックだが、上は「豪華・壮大」、下は「答えの強調」と加工で役割を分けている。</t>
         </is>
       </c>
     </row>
@@ -1311,7 +1322,8 @@
 【文字】①「細長い国では／どう暮らしてる？」2行14文字：黄色＋黒縁、中央、高さ約29%。②小見出し「チリ・ノルウェー・ベトナム」13文字：白。
 【色】紺とグレーの地図に、オレンジ・青・緑の3色の発光。
 【人物の表情】人物なし。
-【絵の風合い】デジタル地図のインフォグラフィック風。※倍率1.5倍と低め。問いが「どう暮らしてる？」とゆるく、「なぜ」の矛盾がない。</t>
+【絵の風合い】デジタル地図のインフォグラフィック風。※倍率1.5倍と低め。問いが「どう暮らしてる？」とゆるく、「なぜ」の矛盾がない。
+【フォント】問いは極太ゴシック体（候補：源ノ角ゴシック Heavy／Noto Sans JP Black）（黄＋黒縁）、2行。小見出しは太ゴシック体の白で小さめ。加工はほぼなし。</t>
         </is>
       </c>
     </row>
@@ -1376,7 +1388,8 @@
 【文字】①「グリーンランドは／なぜデンマーク領？」2行17文字：白＋「デンマーク領」だけ黄色、黒縁、高さ約30%・幅約70%。②小見出し「いま大国が狙う北極の要衝」12文字：白（時事の関心をつなぐ）。地図上に国名ラベル。
 【色】左は青と白、右はベージュの地図に赤。
 【人物の表情】人物なし。
-【絵の風合い】衛星写真と教科書的な白地図の組み合わせ。</t>
+【絵の風合い】衛星写真と教科書的な白地図の組み合わせ。
+【フォント】問いは極太ゴシック体（候補：源ノ角ゴシック Heavy／Noto Sans JP Black）（白＋「デンマーク領」だけ黄、黒縁＋影）。小見出しと地図の国名は細めのゴシック体。</t>
         </is>
       </c>
     </row>
@@ -1441,7 +1454,8 @@
 【文字】①「なぜ奪われた？」7文字：赤＋白縁、高さ約15%。②「中国を塞ぐ『15km』」11文字：白＋「15km」だけ黄色、黒縁。地名（中国・北朝鮮・韓国・日本海・ロシア）は明朝体の小さいラベル。
 【色】ベージュの陸と水色の海の落ち着いた地図に、赤だけで強調。
 【人物の表情】人物なし。
-【絵の風合い】和紙のような質感の古地図風の白地図。</t>
+【絵の風合い】和紙のような質感の古地図風の白地図。
+【フォント】「なぜ奪われた？」は赤の極太ゴシック体（候補：源ノ角ゴシック Heavy／Noto Sans JP Black）＋白縁、「中国を塞ぐ『15km』」は白の極太ゴシック。地図の地名（中国・日本海など）だけ明朝体で、古地図らしさを出している。見出し＝ゴシック、地図のラベル＝明朝と分けている。</t>
         </is>
       </c>
     </row>
@@ -1506,7 +1520,8 @@
 【文字】①「なぜ5つに分かれた？」10文字：白＋「5つ」だけ黄色、黒縁、高さ約16%。②小見出し「複雑すぎる国境線の謎」10文字：白＋「国境線」黄色、黒帯。国名ラベルは白。
 【色】茶色の背景に、緑・ベージュ・オレンジ・紫の国と、発光する赤い国境線。
 【人物の表情】人物はシルエットのみ。
-【絵の風合い】3D地形図と、夕景の砂漠のAIイラストの組み合わせ。</t>
+【絵の風合い】3D地形図と、夕景の砂漠のAIイラストの組み合わせ。
+【フォント】問いは極太ゴシック体（候補：源ノ角ゴシック Heavy／Noto Sans JP Black）（白＋「5つ」だけ黄、黒縁）。小見出しは黒帯に太ゴシック体の白。国名ラベルは中くらいの太さのゴシック体。</t>
         </is>
       </c>
     </row>
@@ -1571,7 +1586,8 @@
 【文字】「アラスカを／ロシアはなぜ売った？」2行13文字：「アラスカ」「ロシア」は黄色、それ以外は白、黒縁、左上、高さ約40%。矢印の中に金額「$7,200,000」。
 【色】紺・赤・金の3色だけ。
 【人物の表情】人物なし。
-【絵の風合い】シンプルなベクターの地図。</t>
+【絵の風合い】シンプルなベクターの地図。
+【フォント】問いは極太ゴシック体（候補：源ノ角ゴシック Heavy／Noto Sans JP Black）（「アラスカ」「ロシア」は黄、他は白）。金額「$7,200,000」は欧文の太いサンセリフ体。</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1652,8 @@
 【文字】①「なぜ別の国に／なったのか？」2行12文字：1行目は金色、2行目は白の太い明朝体、高さ約38%。②小見出し「言葉も近い、隣同士なのに…」13文字：白＋「隣同士」黄色、黒帯。③右下の札「オランダとベルギーの謎」11文字：金の縁取り。
 【色】ベージュの羊皮紙に、オレンジ・緑と赤い国境。
 【人物の表情】人物なし。
-【絵の風合い】アンティークの古地図・羊皮紙風。</t>
+【絵の風合い】アンティークの古地図・羊皮紙風。
+【フォント】問いは極太明朝体（候補：源ノ明朝 Heavy／Noto Serif JP Black）（1行目は金色、2行目は白）で、古地図・羊皮紙の絵と合わせている。小見出しは黒帯に太ゴシック体、右下の札は明朝体、地図の国名は極太ゴシック体。</t>
         </is>
       </c>
     </row>
@@ -1701,7 +1718,8 @@
 【文字】「なぜ「一つの国」じゃない？」13文字：黄色の太い明朝体、上部1行、高さ約12%・幅約90%。国名ラベルは白。
 【色】紺の海、白い周辺国、北欧4か国の赤〜青系の4色。
 【人物の表情】人物なし。
-【絵の風合い】ごくシンプルなフラットな地図。※30本中で一番はねた（52.5倍）のに、一番シンプルなサムネ。問いの強さで勝っている。</t>
+【絵の風合い】ごくシンプルなフラットな地図。※30本中で一番はねた（52.5倍）のに、一番シンプルなサムネ。問いの強さで勝っている。
+【フォント】問いは極太明朝体（候補：源ノ明朝 Heavy／Noto Serif JP Black）（黄、1行）。国名ラベルは白の太ゴシック体。明朝の問いと地図だけの、いちばん飾りの少ない組み合わせ。</t>
         </is>
       </c>
     </row>
@@ -1766,7 +1784,8 @@
 【文字】①上「イベリア半島の「二分割」という歴史的謎」17文字：金色の明朝体、高さ約10%と小さめ。②地図上の国名「スペイン」（金色・大きい）、「ポルトガル」（白）。
 【色】紺の海に赤と青の対比、周りは暗いアンティーク調。
 【人物の表情】人物なし。
-【絵の風合い】フラットな地図を古地図風の暗い額縁に収めた形。※文字は控えめでも30.9倍。2色の対比だけで「なぜ分かれた？」が伝わる。</t>
+【絵の風合い】フラットな地図を古地図風の暗い額縁に収めた形。※文字は控えめでも30.9倍。2色の対比だけで「なぜ分かれた？」が伝わる。
+【フォント】上の題は金色の極太明朝体（候補：源ノ明朝 Heavy／Noto Serif JP Black）で小さめ。地図上の「スペイン」は金色の立体の極太ゴシック体、「ポルトガル」は白の太ゴシック体で小さめ。大きさの差で「大きい国と小さい国」を表している。</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1850,8 @@
 【文字】①「同じ言語、全く違う国」10文字：黄色＋黒縁、高さ約19%・幅いっぱい。②小見出し「ドイツとオーストリアが『赤の他人』になった理由」22文字：白＋「赤の他人」だけ赤、黒帯。
 【色】黒・黄・赤（両国の国旗の色）で統一し、強い発光。
 【人物の表情】人物なし。
-【絵の風合い】AI生成の高彩度な写実イラストと発光する地図。</t>
+【絵の風合い】AI生成の高彩度な写実イラストと発光する地図。
+【フォント】「同じ言語、全く違う国」は極太ゴシック体（候補：源ノ角ゴシック Heavy／Noto Sans JP Black）に黄〜金のグラデーション＋黒縁。小見出しは黒帯に太ゴシック体の白、「赤の他人」だけ赤。国名ラベルは極太ゴシック体。</t>
         </is>
       </c>
     </row>
@@ -1896,7 +1916,8 @@
 【文字】①上「ナチス史上最悪の男」9文字：白、高さ約18%・幅いっぱい。②下「ゲーリングの最期」8文字：赤、高さ約22%。上で人物の「肩書き」、下で「名前＋最期」。
 【色】暗い灰色の背景に、白と赤の2色の文字だけ。
 【人物の表情】正面を見据え、口を結んだ落ち着いた（わずかに笑みのある）顔。
-【絵の風合い】白黒写真をカラー化した肖像写真。背景は暗い灰色〜黒で周囲を暗くした（ビネット）、映画ポスターのような重い雰囲気。文字はかすれのある極太の毛筆・明朝体。</t>
+【絵の風合い】白黒写真をカラー化した肖像写真。背景は暗い灰色〜黒で周囲を暗くした（ビネット）、映画ポスターのような重い雰囲気。文字はかすれのある極太の明朝体。
+【フォント】上下とも極太明朝体（候補：源ノ明朝 Heavy／Noto Serif JP Black）に、かすれ（ざらついた質感）を重ねた加工。縁取りは付けず、文字の周りを黒くぼかして浮かせる。1行の中で、ひらがな（「の」など）を一回り小さくし、名前・漢字・数字を大きくしている（文字の大小差＝ジャンプ率で、読ませたい語を先に目に入れる）。映画ポスターやドキュメンタリーの題字の雰囲気で、「重い実話」だと伝える書体。</t>
         </is>
       </c>
     </row>
@@ -1961,7 +1982,8 @@
 【文字】①上「ナチス史上最悪の女」9文字：白、高さ約18%。②下「イルマ・グレーゼの最期」11文字：赤、高さ約18%。「男」ではなく「女」にした意外性。
 【色】ベージュの背景に、白と赤の文字。
 【人物の表情】眉をひそめ、カメラをにらむような不機嫌な目つき。「若い女性」と「最悪」の落差を顔で見せる。※チャンネル内で一番の再生数（29.4倍）。
-【絵の風合い】白黒写真をカラー化した肖像写真。背景は暗い灰色〜黒で周囲を暗くした（ビネット）、映画ポスターのような重い雰囲気。文字はかすれのある極太の毛筆・明朝体。</t>
+【絵の風合い】白黒写真をカラー化した肖像写真。背景は暗い灰色〜黒で周囲を暗くした（ビネット）、映画ポスターのような重い雰囲気。文字はかすれのある極太の明朝体。
+【フォント】上下とも極太明朝体（候補：源ノ明朝 Heavy／Noto Serif JP Black）に、かすれ（ざらついた質感）を重ねた加工。縁取りは付けず、文字の周りを黒くぼかして浮かせる。1行の中で、ひらがな（「の」など）を一回り小さくし、名前・漢字・数字を大きくしている（文字の大小差＝ジャンプ率で、読ませたい語を先に目に入れる）。映画ポスターやドキュメンタリーの題字の雰囲気で、「重い実話」だと伝える書体。</t>
         </is>
       </c>
     </row>
@@ -2026,7 +2048,8 @@
 【文字】①上「ナチス史上最悪の男」9文字：白、高さ約18%。②下「ハイドリヒの最期」8文字：赤、高さ約22%。
 【色】白〜黒のグラデーション背景に、白と赤の文字。
 【人物の表情】やや斜めを向き、冷たく見下ろすような目線。
-【絵の風合い】白黒写真をカラー化した肖像写真。背景は暗い灰色〜黒で周囲を暗くした（ビネット）、映画ポスターのような重い雰囲気。文字はかすれのある極太の毛筆・明朝体。</t>
+【絵の風合い】白黒写真をカラー化した肖像写真。背景は暗い灰色〜黒で周囲を暗くした（ビネット）、映画ポスターのような重い雰囲気。文字はかすれのある極太の明朝体。
+【フォント】上下とも極太明朝体（候補：源ノ明朝 Heavy／Noto Serif JP Black）に、かすれ（ざらついた質感）を重ねた加工。縁取りは付けず、文字の周りを黒くぼかして浮かせる。1行の中で、ひらがな（「の」など）を一回り小さくし、名前・漢字・数字を大きくしている（文字の大小差＝ジャンプ率で、読ませたい語を先に目に入れる）。映画ポスターやドキュメンタリーの題字の雰囲気で、「重い実話」だと伝える書体。</t>
         </is>
       </c>
     </row>
@@ -2091,7 +2114,8 @@
 【文字】①上「残酷すぎる44日間」9文字（「すぎる」だけ小さく）：白、高さ約23%。②下「毛沢東の最期」6文字：赤、高さ約29%。肩書きではなく「期間＋残酷」を上に置いた形。
 【色】暗い背景に、白と赤の文字。
 【人物の表情】正面を向いた、穏やかな薄笑い（「残酷」との落差）。
-【絵の風合い】白黒写真をカラー化した肖像写真。背景は暗い灰色〜黒で周囲を暗くした（ビネット）、映画ポスターのような重い雰囲気。文字はかすれのある極太の毛筆・明朝体。</t>
+【絵の風合い】白黒写真をカラー化した肖像写真。背景は暗い灰色〜黒で周囲を暗くした（ビネット）、映画ポスターのような重い雰囲気。文字はかすれのある極太の明朝体。
+【フォント】上下とも極太明朝体（候補：源ノ明朝 Heavy／Noto Serif JP Black）に、かすれ（ざらついた質感）を重ねた加工。縁取りは付けず、文字の周りを黒くぼかして浮かせる。1行の中で、ひらがな（「の」など）を一回り小さくし、名前・漢字・数字を大きくしている（文字の大小差＝ジャンプ率で、読ませたい語を先に目に入れる）。映画ポスターやドキュメンタリーの題字の雰囲気で、「重い実話」だと伝える書体。この回は上の「すぎる」も小さくしている。</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2180,8 @@
 【文字】①上「大量虐殺した悪魔」8文字：白、高さ約22%。②下「ベリヤの最期」6文字：赤、高さ約28%。
 【色】暗い背景に、白と赤の文字。
 【人物の表情】丸眼鏡の男が正面を向き、無表情で冷たい目つき。
-【絵の風合い】白黒写真をカラー化した肖像写真。背景は暗い灰色〜黒で周囲を暗くした（ビネット）、映画ポスターのような重い雰囲気。文字はかすれのある極太の毛筆・明朝体。</t>
+【絵の風合い】白黒写真をカラー化した肖像写真。背景は暗い灰色〜黒で周囲を暗くした（ビネット）、映画ポスターのような重い雰囲気。文字はかすれのある極太の明朝体。
+【フォント】上下とも極太明朝体（候補：源ノ明朝 Heavy／Noto Serif JP Black）に、かすれ（ざらついた質感）を重ねた加工。縁取りは付けず、文字の周りを黒くぼかして浮かせる。1行の中で、ひらがな（「の」など）を一回り小さくし、名前・漢字・数字を大きくしている（文字の大小差＝ジャンプ率で、読ませたい語を先に目に入れる）。映画ポスターやドキュメンタリーの題字の雰囲気で、「重い実話」だと伝える書体。</t>
         </is>
       </c>
     </row>
@@ -2221,7 +2246,8 @@
 【文字】①上「ナチス最高の天才」8文字：白、高さ約21%。②下「ロンメルの最期」7文字：赤、高さ約23%。他の回の「最悪」ではなく「最高」の英雄枠。
 【色】白黒寄りの背景に、白と赤の文字。
 【人物の表情】横を向いて遠くを見つめる、険しく引き締まった表情。
-【絵の風合い】白黒写真をカラー化した肖像写真。背景は暗い灰色〜黒で周囲を暗くした（ビネット）、映画ポスターのような重い雰囲気。文字はかすれのある極太の毛筆・明朝体。</t>
+【絵の風合い】白黒写真をカラー化した肖像写真。背景は暗い灰色〜黒で周囲を暗くした（ビネット）、映画ポスターのような重い雰囲気。文字はかすれのある極太の明朝体。
+【フォント】上下とも極太明朝体（候補：源ノ明朝 Heavy／Noto Serif JP Black）に、かすれ（ざらついた質感）を重ねた加工。縁取りは付けず、文字の周りを黒くぼかして浮かせる。1行の中で、ひらがな（「の」など）を一回り小さくし、名前・漢字・数字を大きくしている（文字の大小差＝ジャンプ率で、読ませたい語を先に目に入れる）。映画ポスターやドキュメンタリーの題字の雰囲気で、「重い実話」だと伝える書体。</t>
         </is>
       </c>
     </row>
@@ -2286,7 +2312,8 @@
 【文字】①上「ナチスが最も恐れた男」10文字：白、高さ約18%。②下「アイヒマンの最期」8文字：赤、高さ約21%。
 【色】暗い緑灰色の背景に、白と赤の文字。
 【人物の表情】口元に薄笑いを浮かべ、こちらをにらむような表情。
-【絵の風合い】白黒写真をカラー化した肖像写真。背景は暗い灰色〜黒で周囲を暗くした（ビネット）、映画ポスターのような重い雰囲気。文字はかすれのある極太の毛筆・明朝体。</t>
+【絵の風合い】白黒写真をカラー化した肖像写真。背景は暗い灰色〜黒で周囲を暗くした（ビネット）、映画ポスターのような重い雰囲気。文字はかすれのある極太の明朝体。
+【フォント】上下とも極太明朝体（候補：源ノ明朝 Heavy／Noto Serif JP Black）に、かすれ（ざらついた質感）を重ねた加工。縁取りは付けず、文字の周りを黒くぼかして浮かせる。1行の中で、ひらがな（「の」など）を一回り小さくし、名前・漢字・数字を大きくしている（文字の大小差＝ジャンプ率で、読ませたい語を先に目に入れる）。映画ポスターやドキュメンタリーの題字の雰囲気で、「重い実話」だと伝える書体。この回は上の「が」「も」「れた」も小さくしている。</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2378,8 @@
 【文字】①上「スターリンの」6文字：白、高さ約26%。②下「最期の7日間」6文字：赤、高さ約31%（30本中で最大級）。名前＋期間だけの短い文。
 【色】明るめのグレーの背景に、白と赤の文字。
 【人物の表情】口ひげで目を細めた薄笑い（不気味さ）。
-【絵の風合い】白黒写真をカラー化した肖像写真。背景は暗い灰色〜黒で周囲を暗くした（ビネット）、映画ポスターのような重い雰囲気。文字はかすれのある極太の毛筆・明朝体。</t>
+【絵の風合い】白黒写真をカラー化した肖像写真。背景は暗い灰色〜黒で周囲を暗くした（ビネット）、映画ポスターのような重い雰囲気。文字はかすれのある極太の明朝体。
+【フォント】上下とも極太明朝体（候補：源ノ明朝 Heavy／Noto Serif JP Black）に、かすれ（ざらついた質感）を重ねた加工。縁取りは付けず、文字の周りを黒くぼかして浮かせる。1行の中で、ひらがな（「の」など）を一回り小さくし、名前・漢字・数字を大きくしている（文字の大小差＝ジャンプ率で、読ませたい語を先に目に入れる）。映画ポスターやドキュメンタリーの題字の雰囲気で、「重い実話」だと伝える書体。</t>
         </is>
       </c>
     </row>
@@ -2416,7 +2444,8 @@
 【文字】①上「ムッソリーニの」7文字：白、高さ約25%。②下「最期の10日間」7文字：赤、高さ約28%。スターリンの回と同じ「名前の／最期の○日間」型。
 【色】暗い背景にカラー化した写真、白と赤の文字。
 【人物の表情】ムッソリーニはあごを上げて遠くを見る尊大な顔、周りの男たちは険しい顔。
-【絵の風合い】白黒写真をカラー化した肖像写真。背景は暗い灰色〜黒で周囲を暗くした（ビネット）、映画ポスターのような重い雰囲気。文字はかすれのある極太の毛筆・明朝体。</t>
+【絵の風合い】白黒写真をカラー化した肖像写真。背景は暗い灰色〜黒で周囲を暗くした（ビネット）、映画ポスターのような重い雰囲気。文字はかすれのある極太の明朝体。
+【フォント】上下とも極太明朝体（候補：源ノ明朝 Heavy／Noto Serif JP Black）に、かすれ（ざらついた質感）を重ねた加工。縁取りは付けず、文字の周りを黒くぼかして浮かせる。1行の中で、ひらがな（「の」など）を一回り小さくし、名前・漢字・数字を大きくしている（文字の大小差＝ジャンプ率で、読ませたい語を先に目に入れる）。映画ポスターやドキュメンタリーの題字の雰囲気で、「重い実話」だと伝える書体。「ッ」も小さい。</t>
         </is>
       </c>
     </row>
@@ -2481,7 +2510,8 @@
 【文字】①中央「ヒトラー」4文字：白＋黒縁。②中央下「最後の48時間」7文字：赤＋白縁、高さ約21%。③四隅の小見出し「2通の遺言書を残す」「突然エヴァと結婚する」「青酸カリで愛犬を毒殺」「ヘルマンを処刑する」（各8〜10文字、白）。
 【色】暗い背景に紫の稲妻、白と赤の文字。
 【人物の表情】ヒトラーは目を見開いた険しい顔、他の人物は白黒の不鮮明な写真。
-【絵の風合い】白黒写真のコラージュに稲妻の効果。チャンネルの初期の回（2025年11月）で、後の「上下帯＋肖像」型に固まる前の形。</t>
+【絵の風合い】白黒写真のコラージュに稲妻の効果。チャンネルの初期の回（2025年11月）で、後の「上下帯＋肖像」型に固まる前の形。
+【フォント】「ヒトラー」は白の極太明朝体（候補：源ノ明朝 Heavy／Noto Serif JP Black）＋黒縁、「最後の48時間」は赤の極太明朝体に白縁と立体の厚みを付けた加工。四隅の小見出しは白の太明朝体。後の回とちがって縁取りや立体加工があり、かすれ加工はない。</t>
         </is>
       </c>
     </row>

--- a/youtube-world-history-research/output/video_analysis_sheet_filled.xlsx
+++ b/youtube-world-history-research/output/video_analysis_sheet_filled.xlsx
@@ -453,52 +453,52 @@
   <dimension ref="A1:M31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="44" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="30" customWidth="1" min="8" max="8"/>
-    <col width="36" customWidth="1" min="9" max="9"/>
-    <col width="60" customWidth="1" min="10" max="10"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
+    <col width="60" customWidth="1" min="9" max="9"/>
+    <col width="40" customWidth="1" min="10" max="10"/>
     <col width="48" customWidth="1" min="11" max="11"/>
-    <col width="30" customWidth="1" min="12" max="12"/>
+    <col width="60" customWidth="1" min="12" max="12"/>
     <col width="60" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>動画タイトル</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>動画URL</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>再生数（10/15時点）</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>チャンネル名</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>チャンネルURL</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>登録者数（10/8〜9時点）</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>動画タイトル</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>動画URL</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>再生数（10/15時点）</t>
-        </is>
-      </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
           <t>再生数÷登録者数</t>
@@ -511,22 +511,22 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>見たら何が得られると約束しているか（サムネ＋タイトル＋概要欄から視聴者が受け取る約束）</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>視聴者は何が欲しいのか</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>見たら何が得られると約束しているか（サムネ＋タイトル＋概要欄から視聴者が受け取る約束）</t>
-        </is>
-      </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>動画制作者の意図</t>
+          <t>動画制作者の意図はなにか</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>どんな感情を動かしているか（驚き・不安・好奇心など）※コメント未反映</t>
+          <t>どんな感情を動かしているか（コメント反映・10/15取得）</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
@@ -538,56 +538,58 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>なぜ最強だったはずのモンゴル帝国は ヨーロッパを侵略できなかったのか？【歴史解説】</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=y0cwR7ttIaY</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="n">
+        <v>549553</v>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
           <t>世界史裏探訪</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>https://www.youtube.com/@sekaishi_ura</t>
         </is>
       </c>
-      <c r="C2" s="4" t="n">
+      <c r="F2" s="4" t="n">
         <v>263000</v>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>なぜ最強だったはずのモンゴル帝国は ヨーロッパを侵略できなかったのか？【歴史解説】</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=y0cwR7ttIaY</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="n">
-        <v>549553</v>
       </c>
       <c r="G2" s="5" t="n">
         <v>2.1</v>
       </c>
       <c r="H2" s="6" t="inlineStr">
         <is>
-          <t>モンゴル帝国の強さは知っているが、その限界は知らない歴史・戦争好きの大人</t>
+          <t>モンゴル＝最強というイメージを持つ歴史・戦争好きの大人。コメントでは「鎌倉武士の話だろと思ったら違った」という声があり、元寇の回から流れてきた視聴者も多い。地理や戦術の補足を書く中級者も集まっている。</t>
         </is>
       </c>
       <c r="I2" s="6" t="inlineStr">
         <is>
-          <t>「最強」という前提が崩れる瞬間を見たい。どっちが強いかという番付の話を楽しみたい。</t>
+          <t>サムネ「最強が負けた日」と落馬する騎馬武者で「無敵の軍団が負けた現場」を見せ、タイトルで主語がモンゴル、舞台がヨーロッパだと明かす。合わせると「モンゴルを止めたもっと強い何か（と理由）がわかる」と受け取れる。概要欄「最強には最強をぶつけんだよ。」で、強者どうしの対決を見る期待に変える。
+【コメントから】マムルーク朝の偽装退却に「鳥肌」という声があり、対決の約束は果たされている。地理や補給の補足が多く、答えの「なぜ」にはまだ語りたい余地が残る。</t>
         </is>
       </c>
       <c r="J2" s="6" t="inlineStr">
         <is>
-          <t>サムネ「最強が負けた日」と落馬する騎馬武者で、無敵の軍団が実際に負けた現場を見せると約束し、タイトルで主語がモンゴル、舞台がヨーロッパだと明かす。合わせると「モンゴルを止めた『もっと強い何か』の正体がわかる」と受け取れる。概要欄「最強には最強をぶつけんだよ。」で、答えが地理や偶然ではなく強者どうしの対決だと匂わせ、バトル漫画の対決を見る期待に変えている。</t>
+          <t>「最強」という前提が崩れる瞬間を見たい。強者どうしの対決を、バトル漫画のように楽しみたい。そのうえで「結局、草原でしか勝てなかった」という構造をつかみ、自分でも人に語れる見方を手に入れたい（最多いいねのコメントは、まさにその見方を語っている）。</t>
         </is>
       </c>
       <c r="K2" s="6" t="inlineStr">
         <is>
-          <t>誰もが知る「最強」の看板を借りて、負けた側の話にすることで矛盾を作る。サムネで主語を伏せて「誰が？」と思わせ、タイトルで検索される言葉（モンゴル帝国、ヨーロッパ）を回収する分担。概要欄は漫画のセリフのもじりで、歴史を対戦ものとして楽しむ層に合図している。</t>
+          <t>誰もが知る「最強」の看板を借りて、負けた側の話にすることで矛盾を作る。サムネでは主語を伏せて「誰が？」と思わせ、タイトルで検索される言葉を回収する分担。元寇の回が大きく伸びたあとに出し、同じモンゴルで続けて見てもらう狙いもあると推測。</t>
         </is>
       </c>
       <c r="L2" s="6" t="inlineStr">
         <is>
-          <t>好奇心（最強なのになぜ？という矛盾）、意外性</t>
+          <t>【コメントに出た感情】納得と、知識を足したい気持ち。最多いいねは「モンゴルが拡大できたのは草原地帯だけ」という地理の補足。「マムルーク朝がすごいのか元がエグいのか」「偽装退却をやり返すのが鳥肌」など、強者どうしの対決への興奮もある。「鎌倉武士だろと思ったら違った」と、元寇の続きとして見た人も多い。
+【黙っている多数について】「最強がなぜ負けた？」という矛盾への好奇心で見て、地理という答えに納得して終わる人が多いと推測。コメント率0.67/1000は裏探訪では低め。</t>
         </is>
       </c>
       <c r="M2" s="6" t="inlineStr">
@@ -604,56 +606,58 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>【立場逆転】侵略しに来たのに狩られる側に…モンゴル目線で見る元寇の恐怖【歴史解説】</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=t_Kje4VAKiE</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="n">
+        <v>1299382</v>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
           <t>世界史裏探訪</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>https://www.youtube.com/@sekaishi_ura</t>
         </is>
       </c>
-      <c r="C3" s="4" t="n">
+      <c r="F3" s="4" t="n">
         <v>263000</v>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>【立場逆転】侵略しに来たのに狩られる側に…モンゴル目線で見る元寇の恐怖【歴史解説】</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=t_Kje4VAKiE</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="n">
-        <v>1299382</v>
       </c>
       <c r="G3" s="5" t="n">
         <v>4.9</v>
       </c>
       <c r="H3" s="6" t="inlineStr">
         <is>
-          <t>元寇を「神風で勝った」程度にしか知らない日本人全般</t>
+          <t>学校で「台風（神風）で勝った」と習った日本人全般。コメント最多（4,015いいね）は「本当にひどい歴史教育だった」で、通説に不満や疑問を持っていた人に強く届いている。鎌倉武士のめちゃくちゃぶりを面白がるネット文化に慣れた層も多い。</t>
         </is>
       </c>
       <c r="I3" s="6" t="inlineStr">
         <is>
-          <t>日本が侵略者を返り討ちにする痛快さ。「神風だけじゃなかった」と知って武士を誇らしく思いたい。教科書の話を別の目線で見直したい。</t>
+          <t>タイトル「立場逆転」「狩られる側に」と、サムネの怯えるモンゴル兵と鬼の形相の武者で、「攻めてきた側が日本でどれだけ怖い目にあったかを、笑いながら追体験できる」と受け取れる。概要欄で「神風だけで勝負が決まったわけではない」と、通説を正すことも約束している。
+【コメントから】「元軍がうちの大将の首を掲げたら、逆に取り返そうと襲ってきた」などの逸話への反応が多く、追体験と通説の訂正の両方が果たされている。</t>
         </is>
       </c>
       <c r="J3" s="6" t="inlineStr">
         <is>
-          <t>タイトル「立場逆転」「狩られる側に」と、サムネの怯えるモンゴル兵と鬼の形相の武者で、「攻めてきたモンゴル兵が日本でどれだけ怖い目にあったかを追体験できる」と受け取れる。下帯「トラウマ体験すぎる…」で、笑いながら見られる軽さも約束している。概要欄で「神風の力だけで勝負が決まったわけではない」と、通説を正す話もあると示す。</t>
+          <t>教科書で習った「台風のおかげ」という負け惜しみのような話を、「武士が実際に強かった」という話で上書きしたい。日本人として誇らしく思いたいし、お互いが相手を蛮族だと思っていたという構図で笑いたい。</t>
         </is>
       </c>
       <c r="K3" s="6" t="inlineStr">
         <is>
-          <t>日本人が一番よく知る対外戦争を、相手側の目線に反転させる。恐怖をマンガのセリフで描いてコメディにし、硬い題材の入口を広げる。日本人の誇らしさをくすぐりつつ、概要欄で史実寄りの補正をして「ただの日本すごい動画ではない」という信頼を足している。</t>
+          <t>日本人が一番よく知る対外戦争を、相手側の目線に反転させる。恐怖をマンガのセリフで描いてコメディにし、硬い題材の入口を広げる。通説への不満という、視聴者がもともと抱えていた感情を正面から拾った（130万再生でコメント2,336件）。</t>
         </is>
       </c>
       <c r="L3" s="6" t="inlineStr">
         <is>
-          <t>立場が逆転する痛快さ、日本への誇らしさ、恐怖</t>
+          <t>【コメントに出た感情】①教科書への不満と、通説がひっくり返る快感（最多4,015いいね「台風でかろうじて勝てたと習った。ひどい歴史教育だった」）。②お互いが相手を蛮族だと思っていた、という笑い（「なんだコイツら…こわ」）。③鎌倉武士の常識外れぶりを面白がる（「世紀末モヒカン」）。
+【黙っている多数について】日本人としての誇らしさと、コメディとしての笑いで見ていると推測。いいね率1.27%、コメント率1.79/1000と、裏探訪の中でも反応が強い回。</t>
         </is>
       </c>
       <c r="M3" s="6" t="inlineStr">
@@ -670,56 +674,58 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>【恐怖】日本のバケモン海賊「倭寇」、さすがに厄介すぎる【歴史解説】</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=62_F5SjtZCM</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>741800</v>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>世界史裏探訪</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>https://www.youtube.com/@sekaishi_ura</t>
         </is>
       </c>
-      <c r="C4" s="4" t="n">
+      <c r="F4" s="4" t="n">
         <v>263000</v>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>【恐怖】日本のバケモン海賊「倭寇」、さすがに厄介すぎる【歴史解説】</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=62_F5SjtZCM</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="n">
-        <v>741800</v>
       </c>
       <c r="G4" s="5" t="n">
         <v>2.8</v>
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
-          <t>倭寇を教科書の単語でしか知らない日本人の歴史好き</t>
+          <t>倭寇を教科書の単語でしか知らない日本人。コメントでは、近隣国の人が日本人を名乗って悪事を働くという今の話に結びつける層が上位を占めた。元寇の仕返しという見方をする、歴史のつながりが好きな層もいる。</t>
         </is>
       </c>
       <c r="I4" s="6" t="inlineStr">
         <is>
-          <t>「日本人が海外で恐れられていた」という意外さと、少しの誇らしさ。教科書の単語の中身を、笑いながら知りたい。</t>
+          <t>サムネ「海外から見た倭寇、怖すぎる」と「ただのゴロツキだよ？」「じゃあなんでそんな強ぇんだよ…」の会話で、「被害を受けた側から見た倭寇のヤバさと、ゴロツキがなぜ強かったか」がわかると受け取れる。概要欄「気の毒すぎる」で、被害側に同情しながら笑って見る視点を指定している。
+【コメントから】「賊にしては戦術が天才すぎる」と、強さの理由の約束は果たされている。ただ、上位のコメントは中身より「後期倭寇は日本人ではなかった」という話題に向かった。</t>
         </is>
       </c>
       <c r="J4" s="6" t="inlineStr">
         <is>
-          <t>サムネ「海外から見た倭寇、怖すぎる」と「ただのゴロツキだよ？」「じゃあなんでそんな強ぇんだよ…」の会話で、「被害を受けた側から見た倭寇のヤバさと、ただのゴロツキがなぜ強かったか」がわかると受け取れる。概要欄「こんなやつらが定期的に襲来してくるとか気の毒すぎる。」で、被害側に同情しながら笑って見る視点を指定している。</t>
+          <t>「日本人が海外で恐れられていた」という意外さを楽しみたい。そのうえで「後期の倭寇は日本人ではなかった」という事実を知り、今の近隣国への感情のはけ口にしたい人も多い（上位2つのコメント）。</t>
         </is>
       </c>
       <c r="K4" s="6" t="inlineStr">
         <is>
-          <t>元寇と同じ「外から見た日本」型の2本目。強さの理由をツッコミの形で伏せ、続きを見る理由を作る。「バケモン」「厄介すぎる」などネットの口語で、怖さを笑いに変えている。</t>
+          <t>元寇と同じ「外から見た日本」型の2本目。強さの理由をツッコミの形で伏せ、続きを見る理由を作る。結果として、近隣国への感情という強い反応を呼ぶ題材になった。この型は伸びるが、コメント欄が荒れやすい副作用もある。</t>
         </is>
       </c>
       <c r="L4" s="6" t="inlineStr">
         <is>
-          <t>恐怖、「日本人がそこまで？」という驚きと少しの誇らしさ</t>
+          <t>【コメントに出た感情】予想した「恐怖」よりも、現代の対立感情への接続が強い。上位2つ（約1,500いいね）は「悪いことをする時は日本人と名乗る」は昔からの伝統だった、という皮肉。元寇の仕返しだったという見方、「賊にしては戦術が天才すぎる」という感心も多い。
+【黙っている多数について】日本人が恐れられていたという意外さと少しの誇らしさで見ていると推測。コメント欄は近隣国への感情が出やすく、熱心層の偏りが特に大きい回。</t>
         </is>
       </c>
       <c r="M4" s="6" t="inlineStr">
@@ -736,56 +742,58 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>街角の子供から戦場の兵士まで...世界を支配したコカ・コーラの歴史【歴史解説】</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=e-i5fvSbPM0</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>278564</v>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
           <t>世界史裏探訪</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>https://www.youtube.com/@sekaishi_ura</t>
         </is>
       </c>
-      <c r="C5" s="4" t="n">
+      <c r="F5" s="4" t="n">
         <v>263000</v>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>街角の子供から戦場の兵士まで...世界を支配したコカ・コーラの歴史【歴史解説】</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=e-i5fvSbPM0</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="n">
-        <v>278564</v>
       </c>
       <c r="G5" s="5" t="n">
         <v>1.1</v>
       </c>
       <c r="H5" s="6" t="inlineStr">
         <is>
-          <t>歴史好きに限らない一般層。身近な商品の裏話が好きな人</t>
+          <t>歴史好きに限らない一般層。コメントは「ちょうどコーラを飲んでいた」「瓶が一番うまい」「ペプシマン」など、飲み物の思い出や雑学の話が中心で、普段の視聴者より軽い層に届いている。</t>
         </is>
       </c>
       <c r="I5" s="6" t="inlineStr">
         <is>
-          <t>身近な商品の意外な裏話を知って、人に話したい。</t>
+          <t>サムネ「コーラの歴史」と笑顔で飲む兵士と女性で、「コーラが世界中で愛されるようになった歴史を楽しく知れる」という穏やかな約束。タイトル「戦場の兵士まで」で戦争との意外な関係を示すが、サムネには問いも驚きもない。
+【コメントから】「ファンタはナチス下のドイツで生まれた」という補足が最多いいねで、動画の外の雑学の方が盛り上がった。約束が穏やかなぶん、期待も満足も小さめ。</t>
         </is>
       </c>
       <c r="J5" s="6" t="inlineStr">
         <is>
-          <t>サムネ「コーラの歴史」と笑顔で飲む兵士と女性で、「コーラが世界中で愛されるようになった歴史を楽しく知れる」という穏やかな約束になっている。タイトル「戦場の兵士まで」で戦争との意外な関係を示すが、サムネには問いも驚きもない。概要欄も「缶より瓶の方が美味しいって本当？」と雑談調。</t>
+          <t>身近な商品の意外な裏話を知って、人に話したい。思い出話をしたい。強い「なぜ？」は持っていない。</t>
         </is>
       </c>
       <c r="K5" s="6" t="inlineStr">
         <is>
-          <t>歴史好き以外にも届くテーマで、チャンネルの外に広げる試み。ただ、いつもの「矛盾の問い＋会話のツッコミ」を使わず広告ポスター風にしたため、見たら何がわかるかの約束がぼやけた（1.1倍で30本中最低）。</t>
+          <t>歴史好き以外にも届く題材で、チャンネルの外に広げる試み。ただ、いつもの「矛盾の問い＋会話のツッコミ」を使わず広告ポスター風にしたため、見る理由が弱くなった（1.1倍で30本中最低）。いいね率1.75%は高く、見た人の満足度は低くないので、入口（サムネと問い）の問題と推測。</t>
         </is>
       </c>
       <c r="L5" s="6" t="inlineStr">
         <is>
-          <t>身近なものの意外性、好奇心</t>
+          <t>【コメントに出た感情】歴史への驚きより、自分の体験や雑学を話したい気持ち。「ファンタはナチス下のドイツで生まれた」の補足（720いいね）、「ちょうどコーラを飲んでいた」「瓶が一番うまい」「ペプシマン」など、飲み物の思い出話が中心。
+【黙っている多数について】身近な商品の雑学として軽く見た人が多いと推測。感情の山がなく、驚きや緊張を動かせていない（1.1倍で30本中最低）。いいね率1.75%は高く、見た人の満足度は低くない。</t>
         </is>
       </c>
       <c r="M5" s="6" t="inlineStr">
@@ -802,56 +810,58 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>【総集編】犯罪者が建国し、凡ミスで滅亡...歴史上存在したヤバすぎる国たち【歴史解説】</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=_CE6EZ7nBWY</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>409355</v>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
           <t>世界史裏探訪</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>https://www.youtube.com/@sekaishi_ura</t>
         </is>
       </c>
-      <c r="C6" s="4" t="n">
+      <c r="F6" s="4" t="n">
         <v>263000</v>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>【総集編】犯罪者が建国し、凡ミスで滅亡...歴史上存在したヤバすぎる国たち【歴史解説】</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=_CE6EZ7nBWY</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="n">
-        <v>409355</v>
       </c>
       <c r="G6" s="5" t="n">
         <v>1.6</v>
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>作業中や寝る前に長く流したい歴史好き。チャンネルの既存視聴者</t>
+          <t>チャンネルの既存ファン。コメントの大半が、動画内の呼びかけ「ニッチナテーマダイスキタフガイ」を名乗る自己紹介で、仲間内の遊びを楽しむ常連が中心。「眠れない夜のお供」「繰り返し再生している」と、作業用・睡眠用に流す人もいる。</t>
         </is>
       </c>
       <c r="I6" s="6" t="inlineStr">
         <is>
-          <t>「こんな国が本当にあったの？」という奇妙な実話を、まとめて長時間楽しみたい。作業中や寝る前に流したい。</t>
+          <t>サムネ「実在した異常な国11選」と4分割の絵で、「信じられないけど本当にあった国を11個まとめて見られる」と受け取れる。概要欄「私も独立国家作ろうかな。」で、自分でも作れそうと思える軽いノリを約束している。
+【コメントから】「私も建国できる気がしてきました」が最多で、軽いノリの約束がそのまま返ってきている。</t>
         </is>
       </c>
       <c r="J6" s="6" t="inlineStr">
         <is>
-          <t>サムネ「実在した異常な国11選」と4分割の絵で、「信じられないけど本当にあった国を11個まとめて見られる」と受け取れる。タイトル「犯罪者が建国し、凡ミスで滅亡」で極端な実例を見本として出す。概要欄「私も独立国家作ろうかな。」で、自分でも作れそうと思える軽いノリを示している。</t>
+          <t>好きなチャンネルの世界に長く浸りたい。仲間内のノリで一緒に遊びたい。寝る前や作業中に安心して流せるものがほしい。</t>
         </is>
       </c>
       <c r="K6" s="6" t="inlineStr">
         <is>
-          <t>過去の「〇〇な国」回をまとめ直して、長尺で総再生時間を稼ぐ。「11選」で量をはっきり見せ、作業用・寝る前用として選ばれやすくしている。</t>
+          <t>過去の「〇〇な国」回をまとめ直して、長尺で総再生時間を稼ぐ。視聴者に呼び名を付けて呼びかけ、コメント欄を仲間意識の場にしている。新規よりも既存ファンを濃くする動画。</t>
         </is>
       </c>
       <c r="L6" s="6" t="inlineStr">
         <is>
-          <t>驚き、笑い（くだらなさ）、怖いもの見たさ</t>
+          <t>【コメントに出た感情】チャンネルへの仲間意識。動画内の呼びかけ「ニッチナテーマダイスキタフガイ」を名乗る自己紹介コメントが大量にあり、「私も建国できる気がしてきました」「建国通信講座はここですか」と大喜利で遊んでいる。「眠れない夜のお供」「繰り返し再生している」と、作業用・睡眠用で使う声もある。
+【黙っている多数について】驚きより、長く流して楽しむ安心感。コメント率0.32/1000と低く、総集編は既存ファンが静かに流す動画と推測。</t>
         </is>
       </c>
       <c r="M6" s="6" t="inlineStr">
@@ -868,56 +878,58 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>【致〇率99%】敵陣に最初に突入する兵士のモチベーションは何だったのか？【歴史解説】</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=lOGdA7_YDe0</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>3214321</v>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>世界史裏探訪</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>https://www.youtube.com/@sekaishi_ura</t>
         </is>
       </c>
-      <c r="C7" s="4" t="n">
+      <c r="F7" s="4" t="n">
         <v>263000</v>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>【致〇率99%】敵陣に最初に突入する兵士のモチベーションは何だったのか？【歴史解説】</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=lOGdA7_YDe0</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="n">
-        <v>3214321</v>
       </c>
       <c r="G7" s="5" t="n">
         <v>12.2</v>
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>戦争・軍事ものが好きな男性中心。歴史ファン以外まで広い層</t>
+          <t>戦争や軍事が好きな人に限らず、「人はなぜ命を懸けられるのか」に興味がある大人まで広い層（321万再生で30本中最多）。コメントには、曽祖父の従軍体験、ご先祖が一番槍だったという家族の話を書く人、中国の兵法の補足を書く人もいる。</t>
         </is>
       </c>
       <c r="I7" s="6" t="inlineStr">
         <is>
-          <t>「自分なら絶対無理」なことをした人の心の中をのぞきたい。死と隣り合わせの極限状況を、安全な場所から想像したい。</t>
+          <t>タイトル「致〇率99%」と、サムネ「先頭の兵士って、何考えてたの？」「●ぬよ？」「ですよね。」の会話で、「ほぼ死ぬとわかって突っ込んだ兵士の本音と、そうさせた仕組みがわかる」と受け取れる。概要欄「私はどんな理由があっても先頭にはなりたくないタイプです。」で、普通の人の目線で見ると約束している。
+【コメントから】「名誉の仕組みは渡す側の損失がほぼない、よく考えられたシステム」が6,347いいねで最多。仕組みがわかるという約束は、強く果たされている。</t>
         </is>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>タイトル「致〇率99%」と、サムネ「先頭の兵士って、何考えてたの？」「●ぬよ？」「ですよね。」の会話で、「ほぼ死ぬとわかって突っ込んだ兵士の本音と、そうさせた仕組みがわかる」と受け取れる。概要欄「私はどんな理由があっても先頭にはなりたくないタイプです。」で、視聴者と同じ普通の人の目線で見ると約束している。</t>
+          <t>「自分なら絶対無理」なことをした人の心の中をのぞきたい。そして、その答えを「名誉・報酬・酒・懲罰」という人間の仕組みとして理解し、今の社会や自分の家族の歴史に重ねたい。</t>
         </is>
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
-          <t>「なぜ？」を人の気持ちに向けた問いにする。数字（99%）で極限さを、伏せ字で死を、淡々とした返事でシュールな笑いを作る。作り手が「自分も無理なタイプ」と言うことで、視聴者と同じ側に立っている。</t>
+          <t>「なぜ？」を人の気持ちに向けた問いにする。数字（99%）で極限さを、伏せ字で死を、淡々とした返事でシュールな笑いを作る。「サムネの吸引力が強すぎて逆らえなかった」（1,823いいね）というコメントがあり、会話劇サムネの狙いが最も当たった回。</t>
         </is>
       </c>
       <c r="L7" s="6" t="inlineStr">
         <is>
-          <t>恐怖、「なぜそんなことを？」という疑問</t>
+          <t>【コメントに出た感情】人間の仕組みへの感心と、重さへの共感。最多6,347いいねは「名誉の仕組みは渡す側の損失がほぼない、よく考えられたシステム」。「当時は生きること自体が辛かったから」という想像、「曽祖父が前線で」という家族の話、「見ていたら気分が沈んだ。戦争はいかん」もある。「サムネの吸引力が強すぎて逆らえなかった」（1,823いいね）は、サムネの会話劇が入口になった証拠。
+【黙っている多数について】「自分なら絶対無理」という極限への好奇心で見て、最後は少し重くなる。321万再生で30本中最多。</t>
         </is>
       </c>
       <c r="M7" s="6" t="inlineStr">
@@ -934,56 +946,58 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>ビックリするほどしょーもない理由で滅亡した国３選【歴史解説】</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=EXsFtJWLtLw</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>414461</v>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
           <t>世界史裏探訪</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="E8" s="3" t="inlineStr">
         <is>
           <t>https://www.youtube.com/@sekaishi_ura</t>
         </is>
       </c>
-      <c r="C8" s="4" t="n">
+      <c r="F8" s="4" t="n">
         <v>263000</v>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>ビックリするほどしょーもない理由で滅亡した国３選【歴史解説】</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=EXsFtJWLtLw</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="n">
-        <v>414461</v>
       </c>
       <c r="G8" s="5" t="n">
         <v>1.6</v>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>気軽に歴史の雑学を楽しみたい層</t>
+          <t>チャンネルの「〇〇な国」シリーズを見てきた常連と、気軽な雑学好き。コメントには「ビザンツの鍵閉め忘れを挙げると思っていた」と、定番ネタを知っている歴史好きもいる。</t>
         </is>
       </c>
       <c r="I8" s="6" t="inlineStr">
         <is>
-          <t>国家という大きなものが、くだらない理由で終わる落差で笑いたい。</t>
+          <t>サムネ「凡ミスで滅んだ国3選」とタイトル「ビックリするほどしょーもない理由」で、「笑えるほどしょぼい理由で国が終わった実話を3つ見られる」と受け取れる。
+【コメントから】「みんなとお酒が飲めないから独立撤回」に「萌えすぎる」が最多で、笑いの約束は果たされている。一方で「ペルロヤ共和国は凡ミスではなく詰んでいて可哀想」という声もあり、3本のうち1本は約束と中身がずれている。</t>
         </is>
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
-          <t>サムネ「凡ミスで滅んだ国3選」とタイトル「ビックリするほどしょーもない理由」で、「笑えるほどしょぼい理由で国が終わった実話を3つ見られる」と受け取れる。3つという少なさで、気軽に見られる軽さも約束している。</t>
+          <t>国家という大きなものがくだらない理由で終わる落差で笑いたい。かわいげのある人間くささを見たい。</t>
         </is>
       </c>
       <c r="K8" s="6" t="inlineStr">
         <is>
-          <t>「〇〇な国」シリーズの最終回（概要欄「とりあえずこれで最後です！」）。シリーズのテンプレート（4分割＋赤い大文字）を使い回し、既存の視聴者に続きものだと分からせる。「滅亡」という重い言葉に「しょーもない」をぶつけて落差を作る。</t>
+          <t>シリーズ最終回（概要欄「とりあえずこれで最後です！」）として、同じテンプレートで続きものだと分からせる。「滅亡」という重い言葉に「しょーもない」をぶつけて落差を作る。</t>
         </is>
       </c>
       <c r="L8" s="6" t="inlineStr">
         <is>
-          <t>笑い、「国が滅ぶ」と「しょーもない」の落差による驚き</t>
+          <t>【コメントに出た感情】笑いと、かわいさへの萌え。最多は「みんなとお酒が飲めないから独立撤回、は萌えすぎる」。「ビザンツ帝国、鍵閉め忘れ」のネタも多い。一方で「ペルロヤ共和国は詰んでいて可哀想」と、同情の声もある。
+【黙っている多数について】国の滅亡と「しょーもない」の落差で、気軽に笑って見ていると推測。いいね率1.25%で満足度は高い。</t>
         </is>
       </c>
       <c r="M8" s="6" t="inlineStr">
@@ -1000,56 +1014,58 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>なぜ攻撃力最強のはずの機関銃は、軍人たちから嫌われまくっていたのか？【歴史解説】</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=oqU0VDyQiUE</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>317807</v>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
           <t>世界史裏探訪</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="E9" s="3" t="inlineStr">
         <is>
           <t>https://www.youtube.com/@sekaishi_ura</t>
         </is>
       </c>
-      <c r="C9" s="4" t="n">
+      <c r="F9" s="4" t="n">
         <v>263000</v>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>なぜ攻撃力最強のはずの機関銃は、軍人たちから嫌われまくっていたのか？【歴史解説】</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=oqU0VDyQiUE</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="n">
-        <v>317807</v>
       </c>
       <c r="G9" s="5" t="n">
         <v>1.2</v>
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>兵器・軍事史が好きな層</t>
+          <t>兵器や軍事史が好きな人と、組織で働く大人。コメント率3.01/1000は30本中最高で、「今のドローンも卑怯者と言われる」「精神論は日本だけじゃなかった」と、今の組織や技術に重ねて語りたい人が集まった。補給や水冷式について反論する詳しい人も多い。</t>
         </is>
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
-          <t>「強いのに嫌われる」理不尽の理由を知って、自分の職場や組織の話に重ねたい。古い組織が新しいものを嫌う「あるある」に共感したい。</t>
+          <t>サムネ「なぜ軍人は機関銃を嫌ったのか？」と、不機嫌な将校の「使わねぇよ」「●●だから。」で、「軍人が最強の兵器を拒んだ、意外で人間くさい理由がわかる」と受け取れる。概要欄「これは現代でもあるある。」で、「今の職場にも通じる話」という約束に広げている。
+【コメントから】今の組織に重ねるコメントが上位に並び、「現代でもあるある」の約束は果たされている。補給の問題など、動画が触れきれていない理由を足す人も多い。</t>
         </is>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>サムネ「なぜ軍人は機関銃を嫌ったのか？」と不機嫌な将校の「使わねぇよ」「●●だから。」で、「軍人が最強の兵器を拒んだ、意外で人間くさい理由がわかる」と受け取れる。答えは伏せ字で隠す。概要欄「これは現代でもあるある。」で、答えが兵器の性能ではなく組織や人の心理（プライド、慣習）の話だとほのめかし、「今の職場にも通じる話」という約束に広げている。</t>
+          <t>「強いのに嫌われる」理不尽の理由を知り、自分の職場や組織で新しいものが嫌われる「あるある」に重ねて納得したい。そして、それを人に語りたい（議論が最も活発な回）。</t>
         </is>
       </c>
       <c r="K9" s="6" t="inlineStr">
         <is>
-          <t>兵器の話に見せて、中身は「組織が新しい技術を嫌う」という普遍的な人間の話。伏せ字で答えを隠して続きを見させ、概要欄の一言で軍事好き以外の会社員にも自分ごとにさせている。</t>
+          <t>兵器の話に見せて、中身は「組織が新しい技術を嫌う」という普遍的な話。伏せ字で答えを隠して続きを見させ、概要欄の一言で軍事好き以外にも自分ごとにさせる。結果として、30本で一番語りたくなる動画になった。</t>
         </is>
       </c>
       <c r="L9" s="6" t="inlineStr">
         <is>
-          <t>矛盾への好奇心、意外性</t>
+          <t>【コメントに出た感情】現代や自分の組織への接続と議論。コメント率3.01/1000は30本中最高。「誰か一人が使えば均衡は崩れる」「軍人の精神論は日本だけじゃなかった」「今のドローンも卑怯者と言われる」「蛮族にはこれでも使っとけ、という差別意識がリアル」など、概要欄の「これは現代でもあるある。」どおり、今の話に重ねる人が多い。補給や水冷式など、詳しい人の反論も多い。
+【黙っている多数について】「強いのに嫌われる」理不尽への好奇心と、組織あるあるへの苦笑いで見ていると推測。</t>
         </is>
       </c>
       <c r="M9" s="6" t="inlineStr">
@@ -1066,56 +1082,58 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>「歩兵」が中世ヨーロッパの戦場を”地獄”に変えたと言われる理由【歴史解説】</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=mMzDpd9NA38</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>1516503</v>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>世界史裏探訪</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="E10" s="3" t="inlineStr">
         <is>
           <t>https://www.youtube.com/@sekaishi_ura</t>
         </is>
       </c>
-      <c r="C10" s="4" t="n">
+      <c r="F10" s="4" t="n">
         <v>263000</v>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>「歩兵」が中世ヨーロッパの戦場を”地獄”に変えたと言われる理由【歴史解説】</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=mMzDpd9NA38</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="n">
-        <v>1516503</v>
       </c>
       <c r="G10" s="5" t="n">
         <v>5.8</v>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>中世ヨーロッパ・騎士・戦争が好きな層</t>
+          <t>中世ヨーロッパ・騎士・戦術が好きな人。コメントでは「前置きが短い・テンポが良い・情報量が多い」「参考文献があってありがたい」と、作りの丁寧さを評価する人が目立ち、ゆっくり解説に飽きた中級者が多い。日本の騎馬から足軽への変化に重ねる人もいる。</t>
         </is>
       </c>
       <c r="I10" s="6" t="inlineStr">
         <is>
-          <t>騎士道の美しいイメージの裏にある、残酷な現実を知りたい。</t>
+          <t>サムネ「※中世の歩兵、怖すぎ問題」と「こ、降参…」「じゃ●すね？」の会話で、「騎士の名誉のルールが通じない歩兵が、戦場をどう変えたかを見られる」と受け取れる。概要欄「戦争にも規律って必要なんだな。。。」で、降参や身代金のルールがなくなった怖さが中身だとわかる。
+【コメントから】「槍を構えて騎士の突撃を受けるのはものすごい勇気」など、現場の怖さを想像するコメントが最多で、約束は果たされている。</t>
         </is>
       </c>
       <c r="J10" s="6" t="inlineStr">
         <is>
-          <t>サムネ「※中世の歩兵、怖すぎ問題」と「こ、降参…」「じゃ●すね？」の会話で、「騎士の名誉のルールが通じない歩兵が、戦場をどう変えたかを見られる」と受け取れる。タイトルの「地獄」で残酷さを予告する。概要欄「戦争にも規律って必要なんだな。。。」で、降参や身代金のルールがなくなった怖さが中身だとわかる。</t>
+          <t>騎士道の美しいイメージの裏にある、残酷な現実を知りたい。それを、テンポよく、出典つきの信頼できる形で知りたい。</t>
         </is>
       </c>
       <c r="K10" s="6" t="inlineStr">
         <is>
-          <t>騎士のロマンを持つ視聴者に、その反対側を見せる。降参が通じない冷たさを2行の会話で見せ、「〇〇問題」というネットの言い回しで軽くして入口を広げている。</t>
+          <t>騎士のロマンを持つ視聴者に、その反対側を見せる。降参が通じない冷たさを2行の会話で見せ、ネットの言い回しで軽くする。参考文献を概要欄に載せ、信頼で差をつけている。</t>
         </is>
       </c>
       <c r="L10" s="6" t="inlineStr">
         <is>
-          <t>恐怖、騎士の時代が終わることへのロマン</t>
+          <t>【コメントに出た感情】知的な満足と、チャンネルへの信頼。「槍で騎士の突撃を受けるのはものすごい勇気」という想像のほかに、「前置きが短い・テンポが良い・情報量が多い」（517いいね）、「参考文献を書いてくれてありがたい」（326いいね）など、作り方を褒める声が目立つ。日本の騎馬から足軽への変化と重ねる人も多い。
+【黙っている多数について】残酷さへの怖いもの見たさで入り、作りの丁寧さで最後まで見ていると推測。152万再生でいいね率0.85%。</t>
         </is>
       </c>
       <c r="M10" s="6" t="inlineStr">
@@ -1132,56 +1150,58 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>防御力最強のはずの「城塞都市」が日本で採用されなかった意外な理由【歴史解説】</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=ebAl58P2JRc</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>3164917</v>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
           <t>世界史裏探訪</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="E11" s="3" t="inlineStr">
         <is>
           <t>https://www.youtube.com/@sekaishi_ura</t>
         </is>
       </c>
-      <c r="C11" s="4" t="n">
+      <c r="F11" s="4" t="n">
         <v>263000</v>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>防御力最強のはずの「城塞都市」が日本で採用されなかった意外な理由【歴史解説】</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=ebAl58P2JRc</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="n">
-        <v>3164917</v>
       </c>
       <c r="G11" s="5" t="n">
         <v>12</v>
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>日本と海外の比較が好きな、日本人の歴史好き全般</t>
+          <t>日本と海外の比較が好きな日本人全般（316万再生）。コメント最多は「ちょうど築城するところだったので参考になりました」（12,622いいね）で、大喜利で参加したい層が大きい。城や建築、地形に詳しい人の補足も多く、「コメント欄に識者がいて勉強になる」と、コメント欄まで楽しむ人もいる。</t>
         </is>
       </c>
       <c r="I11" s="6" t="inlineStr">
         <is>
-          <t>日本と海外の違いの理由を知って、「日本ってそういうことか」と自分の国を見直したい。</t>
+          <t>サムネの「ヨーロッパ／日本」の2分割と「なんで壁で囲わないの？」「ったく、分かってねぇなぁ…」で、「日本が壁を作らなかったのには、ちゃんとした理由がある」とわかると受け取れる。日本側が言い返す構図なので、日本が劣っていたわけではないという安心も約束している。
+【コメントから】「兵農分離と刀狩、その動機まで考えたことなかった。腑に落ちた」など、納得のコメントが多く、約束は果たされている。</t>
         </is>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>サムネの「ヨーロッパ／日本」の2分割と「なんで壁で囲わないの？」「ったく、分かってねぇなぁ…」で、「日本が壁を作らなかったのには、ちゃんとした理由がある」とわかると受け取れる。タイトル「防御力最強のはずの」「意外な理由」で矛盾を強める。日本側が言い返す構図なので、日本が劣っていたわけではないという安心も約束している。</t>
+          <t>日本と海外の違いの理由を知って、「日本ってそういうことか」と自分の国を見直したい。そして、大喜利やトリビアでコメント欄に参加したい。</t>
         </is>
       </c>
       <c r="K11" s="6" t="inlineStr">
         <is>
-          <t>「世界では当たり前、日本では違う」の比較で、日本人の自分ごと感を作る。都市を擬人化した会話で、日本側に余裕のあるセリフを言わせ、見る前から日本側に肩入れさせている。</t>
+          <t>「世界では当たり前、日本では違う」比較で、日本人の自分ごと感を作る。都市を擬人化した会話で日本側に余裕のあるセリフを言わせ、見る前から日本側に肩入れさせる。参考文献の掲載で「最近の動画は信用できない」という不信にも応えている。</t>
         </is>
       </c>
       <c r="L11" s="6" t="inlineStr">
         <is>
-          <t>「言われてみれば確かに」という好奇心、日本についての発見</t>
+          <t>【コメントに出た感情】大喜利の楽しさと、日本を見直す納得。最多12,622いいねは「ちょうど築城するところだったので参考になりました」で、このチャンネルの定番の遊びが最大の反応を集めた。日本の家は通気性重視、靴を脱ぐ文化、「姫路城はタワーディフェンス型」など、自分の知っている日本と結びつける声が多い。「参考文献があるのが神」「コメント欄に識者がいて勉強になる」と、信頼も強い。
+【黙っている多数について】「日本が劣っていたわけではない」と安心して納得できることが一番の価値と推測。316万再生、いいね率1.18%。</t>
         </is>
       </c>
       <c r="M11" s="6" t="inlineStr">
@@ -1198,56 +1218,58 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>なぜインドは「人口世界一」になったのか？14億人を生んだ最強の地形と残酷な歴史</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=sky5rp3O0fg</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v>14759</v>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
           <t>おもしろ世界史ラボ</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="E12" s="3" t="inlineStr">
         <is>
           <t>https://www.youtube.com/@%E3%81%8A%E3%82%82%E3%81%97%E3%82%8D%E4%B8%96%E7%95%8C%E5%8F%B2%E3%83%A9%E3%83%9C</t>
         </is>
       </c>
-      <c r="C12" s="4" t="n">
+      <c r="F12" s="4" t="n">
         <v>7160</v>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>なぜインドは「人口世界一」になったのか？14億人を生んだ最強の地形と残酷な歴史</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=sky5rp3O0fg</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="n">
-        <v>14759</v>
       </c>
       <c r="G12" s="5" t="n">
         <v>2.1</v>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>ニュースで「インドが人口世界一」と聞いた大人</t>
+          <t>ニュースで「インドが人口世界一」と聞いた大人。コメントは4件しかなく、どんな人が見ているかはほとんど読み取れない。</t>
         </is>
       </c>
       <c r="I12" s="6" t="inlineStr">
         <is>
-          <t>ニュースで知った事実（人口世界一）の背景を知って、世界の見え方を一段深くしたい。自然の大きなスケールに浸りたい。</t>
+          <t>サムネ上の「ヒマラヤが創った『帝国』」で謎をかけ、下の「インド人口大国の理由」で中身を示す。タイトル「最強の地形と残酷な歴史」と合わせて、「人口の多さは地形が作ったという意外な答えと、搾取の歴史がわかる」と受け取れる。
+【コメントから】「要約：稲作が人口爆発の主要因」というコメントがあり、答えは伝わっている。ただ反応自体が少ない。</t>
         </is>
       </c>
       <c r="J12" s="6" t="inlineStr">
         <is>
-          <t>サムネ上の「ヒマラヤが創った『帝国』」で謎をかけ、下の「インド人口大国の理由」で中身を示す。タイトル「最強の地形と残酷な歴史」と合わせて、「人口の多さは地形が作ったという意外な答えと、搾取の歴史がわかる」と受け取れる。概要欄「お茶碗一杯のご飯にも通じる」で、自分の暮らしにつながる話だと示している。</t>
+          <t>ニュースで知った事実の背景を、短く知りたい。</t>
         </is>
       </c>
       <c r="K12" s="6" t="inlineStr">
         <is>
-          <t>時事（2023年に人口世界一）を入口に、地形という目に見えない原因で答える。高彩度の風景でスケールの大きなドキュメンタリーの空気を作り、大人がゆっくり見る番組として見せている。</t>
+          <t>時事を入口に、地形という目に見えない原因で答える。高彩度の風景で大きなスケールを見せたが、「なぜ？」の矛盾が他の回より弱く、約1.5万再生にとどまっている。</t>
         </is>
       </c>
       <c r="L12" s="6" t="inlineStr">
         <is>
-          <t>好奇心、「残酷な歴史」への少しの不安</t>
+          <t>【コメントに出た感情】コメントが4件しかなく、感情は読み取れない（「勉強になりました」「要約：稲作が人口爆発の主要因」）。
+【黙っている多数について】約1.5万再生でいいね率0.43%と反応は薄い。地形の雄大さより、「なぜ？」の答えを短く知りたい人が多いと推測。</t>
         </is>
       </c>
       <c r="M12" s="6" t="inlineStr">
@@ -1264,56 +1286,58 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>【驚愕の地理】日本より細長い国が存在した！？チリ・ノルウェー・ベトナムが抱える過酷な宿命と驚きの共通点</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=_rEy7JfXiKE</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="n">
+        <v>10723</v>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>おもしろ世界史ラボ</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="E13" s="3" t="inlineStr">
         <is>
           <t>https://www.youtube.com/@%E3%81%8A%E3%82%82%E3%81%97%E3%82%8D%E4%B8%96%E7%95%8C%E5%8F%B2%E3%83%A9%E3%83%9C</t>
         </is>
       </c>
-      <c r="C13" s="4" t="n">
+      <c r="F13" s="4" t="n">
         <v>7160</v>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>【驚愕の地理】日本より細長い国が存在した！？チリ・ノルウェー・ベトナムが抱える過酷な宿命と驚きの共通点</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=_rEy7JfXiKE</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="n">
-        <v>10723</v>
       </c>
       <c r="G13" s="5" t="n">
         <v>1.5</v>
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>地図や地理の雑学が好きな人</t>
+          <t>地図や地理の雑学が好きな人。コメント5件のうち2件はAI制作への不満で、AI動画に厳しい目を持つ人も来ている。</t>
         </is>
       </c>
       <c r="I13" s="6" t="inlineStr">
         <is>
-          <t>地図を眺めて「変な形」と思った国の事情を知りたい。日本との共通点を見つけたい。</t>
+          <t>サムネ「細長い国ではどう暮らしてる？」と3国の地図で、「細長い国の暮らしの大変さを見られる」と受け取れる。概要欄で具体的な苦労（運転しても端から端まで1週間など）を予告している。
+【コメントから】「こういうの見たかった」「気楽に見られる」という声はあるが、「台本か動画のどちらかはそれなりの質に」と、中身の物足りなさも指摘されている。</t>
         </is>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>サムネ「細長い国ではどう暮らしてる？」と3国の地図で、「細長い国の暮らしの大変さを見られる」と受け取れる。タイトルで「日本より細長い」「過酷な宿命と驚きの共通点」を足す。概要欄で「毎日10時間運転しても端から端まで1週間」など具体的な苦労があると示している。</t>
+          <t>地図を眺めて「変な形」と思った国の事情を、気楽に知りたい。</t>
         </is>
       </c>
       <c r="K13" s="6" t="inlineStr">
         <is>
-          <t>地図の形という、見てすぐわかる違和感を使う。ただ問いが「どう暮らしてる？」とゆるく、「なぜ」の矛盾がないため、約束が雑学止まりになっている（1.5倍と低め）。</t>
+          <t>地図の形という、見てすぐわかる違和感を使う。ただ問いがゆるく「なぜ」の矛盾がないため、雑学止まりになっている（1.5倍）。AI制作への不満が出たのは、問いの弱さで中身の薄さが目立ったためと推測。</t>
         </is>
       </c>
       <c r="L13" s="6" t="inlineStr">
         <is>
-          <t>驚き、地図を眺める楽しさ</t>
+          <t>【コメントに出た感情】コメント5件。「こういうの見たかった」「気楽に見られる」という好意と、「AIばかりで見る気が失せる」「台本か動画のどちらかはそれなりの質に」というAI制作への不満が半々。
+【黙っている多数について】雑学としてゆるく見ている。問いがゆるく、強い感情は動いていないと推測（1.5倍）。</t>
         </is>
       </c>
       <c r="M13" s="6" t="inlineStr">
@@ -1330,56 +1354,58 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>【大人の歴史物語】なぜ北米の巨大な島「グリーンランド」は、遠く離れたデンマーク領なのか？ 〜嘘と勘違いから始まった数奇な運命〜</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=b8Hy-06K0mY</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>43346</v>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
           <t>おもしろ世界史ラボ</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="E14" s="3" t="inlineStr">
         <is>
           <t>https://www.youtube.com/@%E3%81%8A%E3%82%82%E3%81%97%E3%82%8D%E4%B8%96%E7%95%8C%E5%8F%B2%E3%83%A9%E3%83%9C</t>
         </is>
       </c>
-      <c r="C14" s="4" t="n">
+      <c r="F14" s="4" t="n">
         <v>7160</v>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>【大人の歴史物語】なぜ北米の巨大な島「グリーンランド」は、遠く離れたデンマーク領なのか？ 〜嘘と勘違いから始まった数奇な運命〜</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=b8Hy-06K0mY</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="n">
-        <v>43346</v>
       </c>
       <c r="G14" s="5" t="n">
         <v>6.1</v>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>時事ニュースでグリーンランドの名前を聞いた大人。地図を見て疑問に思ったことがある人</t>
+          <t>時事ニュースでグリーンランドの名前を聞いた大人。コメントはトランプ政権の動きに触れるものが半分で、時事から来た人が中心と見られる。</t>
         </is>
       </c>
       <c r="I14" s="6" t="inlineStr">
         <is>
-          <t>ニュース（大国が狙う）で気になった島の事情を、根っこから知って納得したい。</t>
+          <t>サムネ「グリーンランドはなぜデンマーク領？」と地図の矢印で、地図を見た誰もが思う矛盾の答えがわかると受け取れる。サムネ下「いま大国が狙う北極の要衝」で今のニュースへのつながりを、タイトルでドラマのある経緯を約束する。
+【コメントから】「国境は地理より外交と偶然で決まる」と納得の声はあるが、4件しかない。4.3万再生でコメント率0.09/1000と30本中最も静か。</t>
         </is>
       </c>
       <c r="J14" s="6" t="inlineStr">
         <is>
-          <t>サムネ「グリーンランドはなぜデンマーク領？」と地図の矢印で、地図を見た誰もが思う矛盾の答えがわかると受け取れる。サムネ下「いま大国が狙う北極の要衝」で今のニュースにつながる話を、タイトル「嘘と勘違いから始まった数奇な運命」でドラマのある経緯を約束する。概要欄で「史上最大の不動産詐欺」など4つの見どころと、後半の地政学パートを予告している。</t>
+          <t>ニュースで気になった島の事情を、根っこから知って納得したい。</t>
         </is>
       </c>
       <c r="K14" s="6" t="inlineStr">
         <is>
-          <t>時事で名前を聞くようになった島を、昔からの素朴な疑問とセットにする。「大人の歴史物語」という言葉で、落ち着いて聞ける教養番組として見せ、中高年層を狙っている。</t>
+          <t>時事で名前を聞くようになった島を、昔からの素朴な疑問とセットにする。「大人の歴史物語」の言葉で落ち着いた教養番組として見せ、中高年層を狙っている。</t>
         </is>
       </c>
       <c r="L14" s="6" t="inlineStr">
         <is>
-          <t>素朴な疑問が解ける好奇心、「嘘と勘違い」という意外な経緯への興味</t>
+          <t>【コメントに出た感情】コメント4件。「国境は地理より外交と偶然で決まる」という納得と、トランプ政権の動きへの関心。上位2件は文体（「…🤔」「😳」で終わる要約調）が似ている。
+【黙っている多数について】4.3万再生でコメント率0.09/1000と、30本中で最も静か。時事への関心で入り、静かに見て終わる人が多いと推測。</t>
         </is>
       </c>
       <c r="M14" s="6" t="inlineStr">
@@ -1396,56 +1422,58 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>【地政学と歴史】中国はなぜ日本海に出られないのか？ロシアに奪われた「15kmの壁」の真実</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=0fQNhKQyVcg</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>9957</v>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
           <t>おもしろ世界史ラボ</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="E15" s="3" t="inlineStr">
         <is>
           <t>https://www.youtube.com/@%E3%81%8A%E3%82%82%E3%81%97%E3%82%8D%E4%B8%96%E7%95%8C%E5%8F%B2%E3%83%A9%E3%83%9C</t>
         </is>
       </c>
-      <c r="C15" s="4" t="n">
+      <c r="F15" s="4" t="n">
         <v>7160</v>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>【地政学と歴史】中国はなぜ日本海に出られないのか？ロシアに奪われた「15kmの壁」の真実</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=0fQNhKQyVcg</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="n">
-        <v>9957</v>
       </c>
       <c r="G15" s="5" t="n">
         <v>1.4</v>
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
-          <t>地政学や国際ニュースに関心がある日本人</t>
+          <t>地政学や国際ニュースに関心がある日本人。コメントでは「清は中国ではない」「北京条約は1860年では」と、年代や用語に厳しい歴史好きと、中国やロシアに強い感情を持つ層が目立つ。</t>
         </is>
       </c>
       <c r="I15" s="6" t="inlineStr">
         <is>
-          <t>日本のすぐ隣の安全保障に関わる話を知って、ニュースを自分で読み解けるようになりたい。中国の弱点を知る安心感。</t>
+          <t>サムネ「なぜ奪われた？」「中国を塞ぐ『15km』」と、途中で止まる矢印の地図で、「大国の中国が日本海に出られない理由と、その土地がロシアに取られた経緯がわかる」と受け取れる。
+【コメントから】年代の誤りへの批判が複数あり、「AIで作った動画はくだらん」という声も出た。約束した中身の正確さが信頼を落としている。</t>
         </is>
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
-          <t>サムネ「なぜ奪われた？」「中国を塞ぐ『15km』」と、途中で止まる矢印の地図で、「大国の中国が日本海に出られない理由と、その土地がロシアに取られた経緯がわかる」と受け取れる。概要欄で「幕末の日本に与えた恐怖」「中国の地政学的な弱点」まで触れると約束している。</t>
+          <t>日本のすぐ隣の安全保障の話を知って、ニュースを自分で読み解きたい。中国の弱点を知って安心したい。</t>
         </is>
       </c>
       <c r="K15" s="6" t="inlineStr">
         <is>
-          <t>日本人が気になる隣国の話を、地図上の小さな数字（15km）で具体的にする。矢印が止まる絵で答えの一部を見せて、「なぜ？」を強くしている。</t>
+          <t>日本人が気になる隣国の話を、地図上の小さな数字（15km）で具体的にする。矢印が止まる絵で答えの一部を見せて「なぜ？」を強くする。ただ、政治的に敏感な題材は、誤りがあると厳しく突かれる。</t>
         </is>
       </c>
       <c r="L15" s="6" t="inlineStr">
         <is>
-          <t>驚き、日本の安全保障に関わることへの関心</t>
+          <t>【コメントに出た感情】安全保障への安心と、誤りへの厳しい指摘。「中国の侵略を止めているのがロシアと北朝鮮という皮肉」が最多。一方で「北京条約は1860年では」「年代がメタメタ」「清は中国ではない」と、年代や用語の誤りへの批判、「AIで作った動画はくだらん」という声が目立つ。
+【黙っている多数について】日本の隣国の話への関心で見ている。コメント率1.61/1000はラボで最高で、誤りや政治的な話題が議論を呼んだ回。</t>
         </is>
       </c>
       <c r="M15" s="6" t="inlineStr">
@@ -1462,56 +1490,58 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>なぜ中央アジアは「5つのスタン」に分かれたのか？【シルクロードの真実】</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=L1HApBYXYaw</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="n">
+        <v>145756</v>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>おもしろ世界史ラボ</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="E16" s="3" t="inlineStr">
         <is>
           <t>https://www.youtube.com/@%E3%81%8A%E3%82%82%E3%81%97%E3%82%8D%E4%B8%96%E7%95%8C%E5%8F%B2%E3%83%A9%E3%83%9C</t>
         </is>
       </c>
-      <c r="C16" s="4" t="n">
+      <c r="F16" s="4" t="n">
         <v>7160</v>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>なぜ中央アジアは「5つのスタン」に分かれたのか？【シルクロードの真実】</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=L1HApBYXYaw</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="n">
-        <v>145756</v>
       </c>
       <c r="G16" s="5" t="n">
         <v>20.4</v>
       </c>
       <c r="H16" s="6" t="inlineStr">
         <is>
-          <t>「〜スタン」という国が多いことを不思議に思ったことがある人</t>
+          <t>「〜スタン」が多いことを不思議に思ったことがある人。コメントには、ウイグルやバスマチ運動の補足を書く詳しい人もいる。「生成AI動画と怪しんで見たが、内容が濃かった」と、AI動画を疑いながら見た人もいる。</t>
         </is>
       </c>
       <c r="I16" s="6" t="inlineStr">
         <is>
-          <t>「〜スタン」という国が多いという長年のモヤモヤを解消したい。</t>
+          <t>サムネ「なぜ5つに分かれた？」と光る国境線の地図で、「名前の似た5つの国ができた理由がわかる」と受け取れる。小見出し「複雑すぎる国境線の謎」で、国境線の形にも答えると示す。
+【コメントから】「抵抗運動を防ぐためにあえて5つに分けた」という補足があり、答えへの関心は高い。「空白のないナレーションは不愉快」と、読み上げへの不満もある。</t>
         </is>
       </c>
       <c r="J16" s="6" t="inlineStr">
         <is>
-          <t>サムネ「なぜ5つに分かれた？」と光る国境線の地図で、「名前の似た5つの国ができた理由がわかる」と受け取れる。小見出し「複雑すぎる国境線の謎」で、国境線の不自然な形にも答えると示す。概要欄で、大国（イギリスとロシア、ソ連）の思惑が答えだと明かしている。</t>
+          <t>長年のモヤモヤ（なぜ〜スタンが多いのか）を、一度ですっきり解消したい。</t>
         </is>
       </c>
       <c r="K16" s="6" t="inlineStr">
         <is>
-          <t>誰もが一度は思う素朴な疑問を、そのまま問いにする。「5つ」だけ黄色にして数で引っかけ、シルクロードのロマンを絵で足している。</t>
+          <t>誰もが一度は思う素朴な疑問を、そのまま問いにする。「5つ」だけ黄色にして数で引っかけ、シルクロードのロマンを絵で足す。</t>
         </is>
       </c>
       <c r="L16" s="6" t="inlineStr">
         <is>
-          <t>素朴な疑問が解ける好奇心</t>
+          <t>【コメントに出た感情】知識を足したい気持ちと、モヤモヤの解消。「ウイグルも入るべき」「抵抗運動を防ぐために5つに分けた」などの補足が中心。「生成AI動画と怪しんで見たが、読み上げも自然で内容も濃かった」という評価と、「空白のないナレーションは不愉快」という不満が両方ある。
+【黙っている多数について】「〜スタンが多いのはなぜ」という長年の疑問が解ける満足で見ていると推測（14.6万再生）。</t>
         </is>
       </c>
       <c r="M16" s="6" t="inlineStr">
@@ -1528,56 +1558,58 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>ロシア最大の痛恨…なぜ「世界最大の宝の山」を手放したのか？坪単価0.2円で売られたアラスカの悲劇と歴史の皮肉</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=YgU5vvbNHFc</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="n">
+        <v>117755</v>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
           <t>おもしろ世界史ラボ</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="E17" s="3" t="inlineStr">
         <is>
           <t>https://www.youtube.com/@%E3%81%8A%E3%82%82%E3%81%97%E3%82%8D%E4%B8%96%E7%95%8C%E5%8F%B2%E3%83%A9%E3%83%9C</t>
         </is>
       </c>
-      <c r="C17" s="4" t="n">
+      <c r="F17" s="4" t="n">
         <v>7160</v>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>ロシア最大の痛恨…なぜ「世界最大の宝の山」を手放したのか？坪単価0.2円で売られたアラスカの悲劇と歴史の皮肉</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=YgU5vvbNHFc</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="n">
-        <v>117755</v>
       </c>
       <c r="G17" s="5" t="n">
         <v>16.4</v>
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
-          <t>歴史や地政学の「損得」の話が好きな人</t>
+          <t>歴史や地政学の「損得」の話が好きな人。コメントでは「当時の判断は妥当だった」と、通説を見直す冷静な見方をする人が多い。</t>
         </is>
       </c>
       <c r="I17" s="6" t="inlineStr">
         <is>
-          <t>「歴史上の大損」を見て、もったいないと驚きたい。損をした側の本当の事情を知りたい。</t>
+          <t>サムネ「アラスカをロシアはなぜ売った？」と「$7,200,000」の矢印で、「信じられない安値で売った理由がわかる」と受け取れる。概要欄で「本当に愚かだったから手放したのか？」と、通説をひっくり返すと約束している。
+【コメントから】最多の「宝の山を捨てたというより、守れない土地を手放しただけ」は、概要欄の問いにそのまま答えている。約束は果たされているが、「語尾が無音化して聞きにくい」「トランジションが多すぎる」と作りへの不満がある（いいね率0.24%）。</t>
         </is>
       </c>
       <c r="J17" s="6" t="inlineStr">
         <is>
-          <t>サムネ「アラスカをロシアはなぜ売った？」と「$7,200,000」の矢印で、「信じられない安値で売った理由がわかる」と受け取れる。タイトルは「世界最大の宝の山」「坪単価0.2円」で損の大きさをあおり、サムネで正体（アラスカ）を明かす。概要欄で「本当に愚かだったから手放したのか？」と、通説をひっくり返すと約束している。</t>
+          <t>「大損」への驚きで入り、損をした側の本当の事情を知って、通説を見直したい。</t>
         </is>
       </c>
       <c r="K17" s="6" t="inlineStr">
         <is>
-          <t>金額という誰でもわかる物差しで「損」を見せる。タイトルで正体を隠し、サムネで明かす分担。概要欄で「愚かな取引」という通説に反論する構成にして、ただの雑学ではない深さを出している。</t>
+          <t>金額という誰でもわかる物差しで「損」を見せる。タイトルで正体を隠し、サムネで明かす分担。通説に反論する構成で深さを出したが、音声や編集の質が満足度を下げている。</t>
         </is>
       </c>
       <c r="L17" s="6" t="inlineStr">
         <is>
-          <t>「もったいない」という驚き、皮肉の面白さ</t>
+          <t>【コメントに出た感情】通説への納得。最多は「宝の山を捨てたというより、守れない土地を手放しただけ」で、概要欄の「本当に愚かだったのか？」という問いにそのまま答えている。「語尾が無音化して聞きにくい」「トランジションが多すぎる」と、作りへの不満もある。
+【黙っている多数について】「大損」への驚きで入り、事情がわかって納得すると推測。いいね率0.24%で、満足度は高くない。</t>
         </is>
       </c>
       <c r="M17" s="6" t="inlineStr">
@@ -1594,56 +1626,58 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>一見すると双子なのに…オランダとベルギーはなぜ「別の国」になったのか？【引き裂かれた歴史】</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=WTxwe4d4qXM</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="n">
+        <v>231422</v>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
           <t>おもしろ世界史ラボ</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="E18" s="3" t="inlineStr">
         <is>
           <t>https://www.youtube.com/@%E3%81%8A%E3%82%82%E3%81%97%E3%82%8D%E4%B8%96%E7%95%8C%E5%8F%B2%E3%83%A9%E3%83%9C</t>
         </is>
       </c>
-      <c r="C18" s="4" t="n">
+      <c r="F18" s="4" t="n">
         <v>7160</v>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>一見すると双子なのに…オランダとベルギーはなぜ「別の国」になったのか？【引き裂かれた歴史】</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=WTxwe4d4qXM</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="n">
-        <v>231422</v>
       </c>
       <c r="G18" s="5" t="n">
         <v>32.3</v>
       </c>
       <c r="H18" s="6" t="inlineStr">
         <is>
-          <t>似ている国の違いが気になる人、ヨーロッパ旅行が好きな人</t>
+          <t>似ている国の違いが気になる大人、ヨーロッパ旅行やサッカーが好きな人。コメントは丁寧な文体が多く、「オランダ人家族に聞いてもわからなかった」「サッカーを52年応援してきた」と、年配でヨーロッパに縁のある層が中心と見られる。</t>
         </is>
       </c>
       <c r="I18" s="6" t="inlineStr">
         <is>
-          <t>似ている2国の違いの理由を知って、ヨーロッパの地図が違って見える体験をしたい。</t>
+          <t>サムネ「なぜ別の国になったのか？」「言葉も近い、隣同士なのに…」と2色の古地図で、「双子のような2国が分かれたドラマを見られる」と受け取れる。概要欄で「一本のオペラ」が独立のきっかけという意外な事実を予告している。
+【コメントから】「鎖国の日本がオランダとだけ交易した理由がわかった」など、知識がつながった喜びが多く、約束は果たされている。</t>
         </is>
       </c>
       <c r="J18" s="6" t="inlineStr">
         <is>
-          <t>サムネ「なぜ別の国になったのか？」「言葉も近い、隣同士なのに…」と2色の古地図で、「双子のような2国が分かれたドラマを見られる」と受け取れる。タイトル「引き裂かれた歴史」で悲劇性を、概要欄の「一本のオペラ」が独立のきっかけという意外な事実でドラマを約束している。</t>
+          <t>似ている2国の違いの理由を知って、自分の旅行や経験、知っていたことと結びつけたい。</t>
         </is>
       </c>
       <c r="K18" s="6" t="inlineStr">
         <is>
-          <t>「似ているのに別」の矛盾の型。古地図の風合いで、大人がゆっくり楽しむ歴史物語として見せている（概要欄のタグに「大人の教養」）。</t>
+          <t>「似ているのに別」の矛盾の型。古地図の風合いと「大人の教養」の言葉で、年配層がゆっくり楽しむ歴史物語として見せている。</t>
         </is>
       </c>
       <c r="L18" s="6" t="inlineStr">
         <is>
-          <t>好奇心、「引き裂かれた」というドラマ性</t>
+          <t>【コメントに出た感情】知識がつながる気持ちよさと、旅行や体験の記憶。「国境は民族より政治で決まる」という感想、「鎖国の日本がオランダとだけ交易した理由がわかった」「オランダ人家族に聞いてもわからなかった経緯がわかった」「サッカーを52年応援してきた」など、自分の経験と結びつける声が多い。年配と思われる丁寧なコメントが目立つ。
+【黙っている多数について】大人の教養として、落ち着いて見ている人が多いと推測。</t>
         </is>
       </c>
       <c r="M18" s="6" t="inlineStr">
@@ -1660,56 +1694,58 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>国旗も言葉もほぼ同じなのに…北欧が「一つの国」になれなかった理由</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=rJqy3SXia3Y</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="n">
+        <v>376231</v>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
           <t>おもしろ世界史ラボ</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="E19" s="3" t="inlineStr">
         <is>
           <t>https://www.youtube.com/@%E3%81%8A%E3%82%82%E3%81%97%E3%82%8D%E4%B8%96%E7%95%8C%E5%8F%B2%E3%83%A9%E3%83%9C</t>
         </is>
       </c>
-      <c r="C19" s="4" t="n">
+      <c r="F19" s="4" t="n">
         <v>7160</v>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>国旗も言葉もほぼ同じなのに…北欧が「一つの国」になれなかった理由</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=rJqy3SXia3Y</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="n">
-        <v>376231</v>
       </c>
       <c r="G19" s="5" t="n">
         <v>52.5</v>
       </c>
       <c r="H19" s="6" t="inlineStr">
         <is>
-          <t>北欧が好きな人、ヨーロッパに興味がある大人</t>
+          <t>北欧やヨーロッパに興味がある大人。コメントでは「フィンランドは民族も言葉も違う」「アイスランドが抜けている」と、地理や民族に詳しい人の指摘が上位を占めた。「北欧はほぼ一つの国だと思っていた」という素直な初心者もいる。</t>
         </is>
       </c>
       <c r="I19" s="6" t="inlineStr">
         <is>
-          <t>「似ているのになぜ？」の答えを知ってすっきりしたい。平和なイメージの北欧の裏側を知りたい。</t>
+          <t>サムネ「なぜ『一つの国』じゃない？」と、4か国を塗り分けた北欧の地図で、問いがそのまま約束になっている。タイトル「国旗も言葉もほぼ同じなのに」で矛盾を強める。
+【コメントから】サムネに描いたフィンランドが、本編にほとんど出てこないという指摘が多い。地図で約束した4か国の話が3か国の話になり、約束と中身がずれている。それでも30本中最高の52.5倍で、入口の強さが中身のずれを上回った。</t>
         </is>
       </c>
       <c r="J19" s="6" t="inlineStr">
         <is>
-          <t>サムネ「なぜ『一つの国』じゃない？」と塗り分けた北欧の地図だけで、問いがそのまま約束になっている。タイトル「国旗も言葉もほぼ同じなのに」で矛盾を強める。概要欄で「残酷で血塗られた兄弟たちの歴史」「ストックホルムの血浴」と、平和なイメージを裏切る話だと示している。</t>
+          <t>「似ているのになぜ？」の矛盾を、すっきり解きたい。平和なイメージの北欧の裏側を知りたい。</t>
         </is>
       </c>
       <c r="K19" s="6" t="inlineStr">
         <is>
-          <t>問いの強さだけで勝負する（30本中最高の52.5倍で、サムネは最もシンプル）。地図を見せれば矛盾が伝わるので、飾りを足していない。</t>
+          <t>問いの強さだけで勝負する。地図を見せれば矛盾が伝わるので、飾りを足さない。ただ、サムネの地図と本編の範囲を合わせていなかったことが、詳しい人の不満になった。</t>
         </is>
       </c>
       <c r="L19" s="6" t="inlineStr">
         <is>
-          <t>好奇心、似ているのに別々という意外性</t>
+          <t>【コメントに出た感情】知識の訂正と補足が中心。上位5件のうち4件が「フィンランドは民族も言葉も違う」「フィンランドがほとんど出てこない」「アイスランドが抜けている」という指摘。「北欧はほぼ一つの国だと思っていた。全然違って面白い」という素直な驚きもある。
+【黙っている多数について】「似ているのになぜ？」という矛盾がすっきり解ける満足で見ていると推測。30本中最高の52.5倍で、コメントの指摘は再生の伸びを止めていない。</t>
         </is>
       </c>
       <c r="M19" s="6" t="inlineStr">
@@ -1726,46 +1762,47 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>一つ屋根の下に二つの家族？イベリア半島が「２つに分かれた」歴史の裏側</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=dkrkDvQjz-4</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="n">
+        <v>221200</v>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
           <t>おもしろ世界史ラボ</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="E20" s="3" t="inlineStr">
         <is>
           <t>https://www.youtube.com/@%E3%81%8A%E3%82%82%E3%81%97%E3%82%8D%E4%B8%96%E7%95%8C%E5%8F%B2%E3%83%A9%E3%83%9C</t>
         </is>
       </c>
-      <c r="C20" s="4" t="n">
+      <c r="F20" s="4" t="n">
         <v>7160</v>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>一つ屋根の下に二つの家族？イベリア半島が「２つに分かれた」歴史の裏側</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=dkrkDvQjz-4</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="n">
-        <v>221200</v>
       </c>
       <c r="G20" s="5" t="n">
         <v>30.9</v>
       </c>
       <c r="H20" s="6" t="inlineStr">
         <is>
-          <t>スペインやポルトガルに興味がある人</t>
+          <t>スペインやポルトガルに興味がある大人。コメントには、スペイン国内の多様性を補足する詳しい人や、旅行の思い出を書く年配の人が多い。「でかい字幕助かる」という声もあり、文字の大きさを気にする年代も見ている。</t>
         </is>
       </c>
       <c r="I20" s="6" t="inlineStr">
         <is>
-          <t>地図を見て感じた違和感（同じ半島なのに2つの国）の答えを知りたい。</t>
+          <t>サムネ「イベリア半島の『二分割』という歴史的謎」と赤と青の地図で、「同じ半島に2つの国がある理由がわかる」と受け取れる。概要欄で「大国スペインはなぜ小さなポルトガルを飲み込めなかったのか」と、強い側が勝てなかった謎に絞っている。
+【コメントから】「スペイン自体が多様すぎて統合が難しい」という補足が最多で、視聴者は答えをもう一段深く知りたがっている。</t>
         </is>
       </c>
       <c r="J20" s="6" t="inlineStr">
         <is>
-          <t>サムネ「イベリア半島の『二分割』という歴史的謎」と赤と青の地図で、「同じ半島に2つの国がある理由がわかる」と受け取れる。タイトル「一つ屋根の下に二つの家族？」で家族のたとえにして親しみやすくする。概要欄で「大国スペインはなぜ小さなポルトガルを飲み込めなかったのか」と、強い側が勝てなかった謎に絞っている。</t>
+          <t>地図を見て感じた違和感の答えを知りたい。旅行で見たものと歴史を結びつけたい。</t>
         </is>
       </c>
       <c r="K20" s="6" t="inlineStr">
@@ -1775,7 +1812,8 @@
       </c>
       <c r="L20" s="6" t="inlineStr">
         <is>
-          <t>好奇心、「一つ屋根の下の二つの家族」というたとえによる親しみ</t>
+          <t>【コメントに出た感情】知識を足したい気持ちと、旅行の記憶。最多は「スペイン自体が多様すぎて統合が難しい」という補足。「でかい字幕助かる」という見やすさへの評価、「生成AIで一本作ってみたやつか？」「AIだけでそれなりに再生とコメントがつく時代になった」という制作方法への反応もある。
+【黙っている多数について】地図の違和感が解ける満足と推測。</t>
         </is>
       </c>
       <c r="M20" s="6" t="inlineStr">
@@ -1792,46 +1830,47 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>同じ言語なのに、なぜ別の国？ドイツとオーストリアの複雑すぎる愛憎史</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=MIE3-uo--r4</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="n">
+        <v>174273</v>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
           <t>おもしろ世界史ラボ</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="E21" s="3" t="inlineStr">
         <is>
           <t>https://www.youtube.com/@%E3%81%8A%E3%82%82%E3%81%97%E3%82%8D%E4%B8%96%E7%95%8C%E5%8F%B2%E3%83%A9%E3%83%9C</t>
         </is>
       </c>
-      <c r="C21" s="4" t="n">
+      <c r="F21" s="4" t="n">
         <v>7160</v>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>同じ言語なのに、なぜ別の国？ドイツとオーストリアの複雑すぎる愛憎史</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=MIE3-uo--r4</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="n">
-        <v>174273</v>
       </c>
       <c r="G21" s="5" t="n">
         <v>24.3</v>
       </c>
       <c r="H21" s="6" t="inlineStr">
         <is>
-          <t>ドイツとオーストリアの違いが気になる人、ヨーロッパ史が好きな人</t>
+          <t>ドイツやオーストリアに住んだこと・行ったことがある人、ヨーロッパ史が好きな人。コメントは「南ドイツに住んでいるが」「毎年オーストリアを訪問している」と、実体験のある人が多い。</t>
         </is>
       </c>
       <c r="I21" s="6" t="inlineStr">
         <is>
-          <t>同じ言葉を話すのに別の国という矛盾をすっきりさせたい。兄弟げんかのような愛憎ドラマを楽しみたい。</t>
+          <t>サムネ「同じ言語、全く違う国」「『赤の他人』になった理由」と、亀裂で割れた地図で、「兄弟のような2国が他人になるまでの因縁がわかる」と受け取れる。タイトル「複雑すぎる愛憎史」で感情のドラマを約束する。
+【コメントから】「兄弟にしては遠く、他人にしては近い…親戚ですね」が最多で、「赤の他人」という言葉への言い直しが起きている。じゃがいもの呼び方の説明が足りないという声もある。</t>
         </is>
       </c>
       <c r="J21" s="6" t="inlineStr">
         <is>
-          <t>サムネ「同じ言語、全く違う国」「『赤の他人』になった理由」と、亀裂で割れた地図で、「兄弟のような2国が他人になるまでの因縁がわかる」と受け取れる。タイトル「複雑すぎる愛憎史」で感情のドラマを約束する。概要欄でハプスブルク家、ビスマルク、ナチスによる併合まで1000年のドラマを予告している。</t>
+          <t>同じ言葉なのに別の国という矛盾をすっきりさせたい。自分の体験と照らし合わせて「やっぱりそうか」と思いたい。</t>
         </is>
       </c>
       <c r="K21" s="6" t="inlineStr">
@@ -1841,7 +1880,8 @@
       </c>
       <c r="L21" s="6" t="inlineStr">
         <is>
-          <t>好奇心、愛憎ドラマへの興味</t>
+          <t>【コメントに出た感情】自分の体験や知識で語りたい気持ち。「兄弟にしては遠く、他人にしては近い…親戚ですね」が最多。「南ドイツに住んでいるが北ドイツの方が違う国に感じる」「毎年オーストリアを訪問している」など、住んだ・行った経験の話が多い。
+【黙っている多数について】愛憎ドラマとしてより、「同じ言葉なのになぜ？」の納得で見ていると推測。</t>
         </is>
       </c>
       <c r="M21" s="6" t="inlineStr">
@@ -1858,56 +1898,58 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>ヘルマン・ゲーリング｜残酷すぎる最期。53歳で死去したヒトラーの後継者【第二次世界大戦】</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=BtAGQokhyUE</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="n">
+        <v>81175</v>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>追伸、戦場から失礼します。</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="E22" s="3" t="inlineStr">
         <is>
           <t>https://www.youtube.com/@hello-senjo</t>
         </is>
       </c>
-      <c r="C22" s="4" t="n">
+      <c r="F22" s="4" t="n">
         <v>19600</v>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>ヘルマン・ゲーリング｜残酷すぎる最期。53歳で死去したヒトラーの後継者【第二次世界大戦】</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=BtAGQokhyUE</t>
-        </is>
-      </c>
-      <c r="F22" s="4" t="n">
-        <v>81175</v>
       </c>
       <c r="G22" s="5" t="n">
         <v>4.1</v>
       </c>
       <c r="H22" s="6" t="inlineStr">
         <is>
-          <t>第二次世界大戦やナチスに興味がある層</t>
+          <t>第二次世界大戦やナチスの人物に興味がある層。コメントには「いつも動画を楽しみにしている」という常連と、ゲーリングの空軍での功績を語る詳しい人がいる。</t>
         </is>
       </c>
       <c r="I22" s="6" t="inlineStr">
         <is>
-          <t>権力の頂点にいた悪人が、最後にどうなったかを見届けたい。悪が報いを受けるのを見て納得したい。</t>
+          <t>サムネ「ナチス史上最悪の男」「ゲーリングの最期」と落ち着いた顔の肖像で、「最悪と呼ばれた男の最後」を見届けられると受け取れる。タイトル「ヒトラーの後継者」で頂点からの転落を約束する。
+【コメントから】「ナチスには最悪はゴロゴロいる」「最悪と呼ぶほどでもない」と、肩書きへの異論が出ている。「最悪」の約束が、詳しい人には大げさに映った。</t>
         </is>
       </c>
       <c r="J22" s="6" t="inlineStr">
         <is>
-          <t>サムネ「ナチス史上最悪の男」「ゲーリングの最期」と落ち着いた顔の肖像で、「最悪と呼ばれた男の最後」を見届けられると受け取れる。タイトル「残酷すぎる最期」「ヒトラーの後継者」で、頂点からの転落を約束する。概要欄から、第一次世界大戦の飛行隊の司令官から空軍の最高司令官、そして最期までの生涯を追う構成だとわかる。</t>
+          <t>権力の頂点にいた人物が最後にどうなったかを見届けたい。ヒトラー以外のナチスの人物を知りたい（「ヒトラーばかりに目がいきがち」というコメント）。</t>
         </is>
       </c>
       <c r="K22" s="6" t="inlineStr">
         <is>
-          <t>「最期」というゴールを先に見せて、生涯全体を見させる。決まった型（上下の帯＋肖像）で、関連動画からシリーズとしてつないでいる。</t>
+          <t>「最期」というゴールを先に見せて、生涯全体を見させる。決まった型（上下の帯＋肖像）で、関連動画からシリーズとしてつなぐ。</t>
         </is>
       </c>
       <c r="L22" s="6" t="inlineStr">
         <is>
-          <t>怖いもの見たさ、因果応報への関心</t>
+          <t>【コメントに出た感情】人物評価の議論。「ヒトラーに騙された」「ナチスには最悪はゴロゴロいる。ゲーリングはただのジャンキー」「最悪と呼ぶほどでもない」と、肩書き「最悪の男」への賛否が出ている。「いつも動画を楽しみにしている」という常連の声もある。
+【黙っている多数について】8.1万再生、コメント率0.37/1000と静か。怖いもの見たさで来て、人物を知って終わると推測。</t>
         </is>
       </c>
       <c r="M22" s="6" t="inlineStr">
@@ -1924,56 +1966,58 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>イルマ・グレーゼ｜22歳で処刑された悪魔。ナチスが最も恐れた女の残酷すぎる最期【第二次世界大戦】</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=XBXVSbh4w1k</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="n">
+        <v>576986</v>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
           <t>追伸、戦場から失礼します。</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="E23" s="3" t="inlineStr">
         <is>
           <t>https://www.youtube.com/@hello-senjo</t>
         </is>
       </c>
-      <c r="C23" s="4" t="n">
+      <c r="F23" s="4" t="n">
         <v>19600</v>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>イルマ・グレーゼ｜22歳で処刑された悪魔。ナチスが最も恐れた女の残酷すぎる最期【第二次世界大戦】</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=XBXVSbh4w1k</t>
-        </is>
-      </c>
-      <c r="F23" s="4" t="n">
-        <v>576986</v>
       </c>
       <c r="G23" s="5" t="n">
         <v>29.4</v>
       </c>
       <c r="H23" s="6" t="inlineStr">
         <is>
-          <t>第二次世界大戦・ナチスに興味がある層、「悪女」や事件ものが好きな層</t>
+          <t>ナチスや戦争に興味がある層に加え、「悪女」「事件」ものが好きな層。コメントは顔への反応と、人間の本性を考える声が中心で、歴史の詳しさより人間そのものに関心がある人が多い（57.7万再生でチャンネル最多）。</t>
         </is>
       </c>
       <c r="I23" s="6" t="inlineStr">
         <is>
-          <t>「若い女性がなぜそこまで残酷になれたのか」という、理解できないものへの好奇心。悪人が裁かれる結末を見届けたい。</t>
+          <t>サムネ「ナチス史上最悪の女」と、にらむ若い女性の顔で、「若い女性が最悪と呼ばれた理由とその最期がわかる」と受け取れる。タイトル「22歳で処刑された悪魔」で年齢と結末の衝撃を足す。
+【コメントから】「20代の顔じゃない」「目つきが普通の女の子ではない」と、サムネの顔への反応が上位を占める。「誰でもその立場になれば同じことをする」「自分ならどうなるか考えさせられる」と、約束以上に人間について考える動画になっている。</t>
         </is>
       </c>
       <c r="J23" s="6" t="inlineStr">
         <is>
-          <t>サムネ「ナチス史上最悪の女」と、にらむ若い女性の顔で、「若い女性が最悪と呼ばれた理由とその最期がわかる」と受け取れる。タイトル「22歳で処刑された悪魔」で年齢と結末の衝撃を足す。概要欄で「史上最年少で死刑を執行された女性」「最大3万人の命を管理」と、普通の少女が看守になるまでの経緯も見せると約束している。</t>
+          <t>「若い女性がなぜそこまで残酷になれたのか」という、理解できないものを理解したい。そして「自分も同じ環境ならそうなるのか」を確かめたい。</t>
         </is>
       </c>
       <c r="K23" s="6" t="inlineStr">
         <is>
-          <t>いつもの「最悪の男」を「女」に変えて意外性を作る（チャンネル最高の29.4倍）。若い女性の顔と「悪魔」の落差で目を止めさせている。</t>
+          <t>いつもの「最悪の男」を「女」に変えて意外性を作る（29.4倍）。若い女性の顔と「悪魔」の落差で目を止めさせる。顔そのものがコメントの話題になり、サムネの写真選びが一番効いた回。</t>
         </is>
       </c>
       <c r="L23" s="6" t="inlineStr">
         <is>
-          <t>恐怖と嫌悪、「若い女性が」という意外性</t>
+          <t>【コメントに出た感情】顔への衝撃と、人間の本性への問い。「20代の顔じゃない」（537いいね）、「目つきが普通の女の子ではない」（500いいね）、「どう育てたらこんな眼光に」など、サムネの顔に反応したコメントが上位を占める。一方で「誰でもその立場になれば同じことをする」「自分も同じ境遇ならどうなるか、考えさせられる」と、環境と人間について考える声も多い。
+【黙っている多数について】「若い女性がなぜ」という理解できないものへの好奇心。チャンネル最高の29.4倍で、サムネの顔がその入口になっている。</t>
         </is>
       </c>
       <c r="M23" s="6" t="inlineStr">
@@ -1990,56 +2034,58 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>ラインハルト・ハイドリヒ｜数百万人を虐殺した悪魔。ナチスが最も恐れた男の残酷すぎる最期【第二次世界大戦】</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=K4AcedCAqj4</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="n">
+        <v>147795</v>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
           <t>追伸、戦場から失礼します。</t>
         </is>
       </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="E24" s="3" t="inlineStr">
         <is>
           <t>https://www.youtube.com/@hello-senjo</t>
         </is>
       </c>
-      <c r="C24" s="4" t="n">
+      <c r="F24" s="4" t="n">
         <v>19600</v>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>ラインハルト・ハイドリヒ｜数百万人を虐殺した悪魔。ナチスが最も恐れた男の残酷すぎる最期【第二次世界大戦】</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=K4AcedCAqj4</t>
-        </is>
-      </c>
-      <c r="F24" s="4" t="n">
-        <v>147795</v>
       </c>
       <c r="G24" s="5" t="n">
         <v>7.5</v>
       </c>
       <c r="H24" s="6" t="inlineStr">
         <is>
-          <t>第二次世界大戦・ナチスに興味がある層</t>
+          <t>ナチスの体制や組織に関心がある層。コメントでは「冷徹な事務手続きとして虐殺をシステム化した」と、仕組みとして理解したい人が目立つ。</t>
         </is>
       </c>
       <c r="I24" s="6" t="inlineStr">
         <is>
-          <t>ナチスの中でも特に恐れられた人物の正体を知りたい。悪人が報いを受けるのを見届けたい。</t>
+          <t>サムネ「ナチス史上最悪の男」「ハイドリヒの最期」で、「最悪の男がどう死んだか」を見届けられると受け取れる。概要欄で「38歳の若さで暗殺」と結末の種類を明かしている。
+【コメントから】「有能すぎる」「この能力をいい方向に生かせなかったのか」と、優秀さと悪が結びつく怖さへの反応が多く、最期よりも人物像の方が刺さっている。</t>
         </is>
       </c>
       <c r="J24" s="6" t="inlineStr">
         <is>
-          <t>サムネ「ナチス史上最悪の男」「ハイドリヒの最期」で、「最悪の男がどう死んだか」を見届けられると受け取れる。タイトル「ナチスが最も恐れた男」で、身内からも恐れられるほどの怖さを約束する。概要欄で「38歳の若さで暗殺」と結末の種類を明かし、ゲーリングやアイヒマンとの関係も見せると示している。</t>
+          <t>ナチスの中でも特に恐れられた人物の正体を知りたい。「優秀な人間が悪に向かう怖さ」を理解したい。</t>
         </is>
       </c>
       <c r="K24" s="6" t="inlineStr">
         <is>
-          <t>定番の型で、名前を知らない人にも「最悪」の肩書きで興味を持たせる。概要欄で他の回の人物の名前を出し、シリーズ内を回遊させている。</t>
+          <t>定番の型で、名前を知らない人にも「最悪」の肩書きで興味を持たせる。概要欄で他の回の人物を出し、シリーズ内を回遊させる。</t>
         </is>
       </c>
       <c r="L24" s="6" t="inlineStr">
         <is>
-          <t>恐怖、悪人が裁かれるかどうかへの関心</t>
+          <t>【コメントに出た感情】恐怖と、能力への複雑な感心。最多は「感情ではなく冷徹な事務手続きとして虐殺をシステム化した」（85いいね）。「有能すぎる」「天才だよ」「この能力をいい方向に生かせなかったのか」と、優秀さと悪が結びつく怖さに反応している。
+【黙っている多数について】ナチスの中でも名前を知らない人物を、「最悪」の肩書きで知る入口として見ていると推測。</t>
         </is>
       </c>
       <c r="M24" s="6" t="inlineStr">
@@ -2056,56 +2102,58 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>毛沢東の最期！4500万人を殺した男の残酷すぎる44日間【第二次世界大戦】</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=UdZXaobRj_U</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="n">
+        <v>184827</v>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
           <t>追伸、戦場から失礼します。</t>
         </is>
       </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="E25" s="3" t="inlineStr">
         <is>
           <t>https://www.youtube.com/@hello-senjo</t>
         </is>
       </c>
-      <c r="C25" s="4" t="n">
+      <c r="F25" s="4" t="n">
         <v>19600</v>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>毛沢東の最期！4500万人を殺した男の残酷すぎる44日間【第二次世界大戦】</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=UdZXaobRj_U</t>
-        </is>
-      </c>
-      <c r="F25" s="4" t="n">
-        <v>184827</v>
       </c>
       <c r="G25" s="5" t="n">
         <v>9.4</v>
       </c>
       <c r="H25" s="6" t="inlineStr">
         <is>
-          <t>近現代史・独裁者に興味がある層</t>
+          <t>近現代史や独裁者に興味がある層。コメントは「史上最悪」「地獄に堕ちてほしい」という強い断罪と、今の中国への感情を重ねる層が上位を占め、コメント率1.89/1000は追伸で最高。</t>
         </is>
       </c>
       <c r="I25" s="6" t="inlineStr">
         <is>
-          <t>巨大な権力者の最後の日々に何が起きたかをのぞき見たい。死が隠されたという裏話を知りたい。</t>
+          <t>サムネ「残酷すぎる44日間」「毛沢東の最期」と穏やかな薄笑いの肖像で、「最後の44日間に起きた残酷な出来事を見られる」と受け取れる。概要欄で「なぜ彼の死は16時間も隠されたのか」と、権力の裏側の謎を約束している。
+【コメントから】「16時間の空白って意外と少ない」「4人組の運命はそうだったのか、勉強になった」と、裏側の謎の約束には反応がある。ただ多くは中身より人物への断罪。</t>
         </is>
       </c>
       <c r="J25" s="6" t="inlineStr">
         <is>
-          <t>サムネ「残酷すぎる44日間」「毛沢東の最期」と穏やかな薄笑いの肖像で、「最後の44日間に起きた残酷な出来事を見られる」と受け取れる。タイトル「4500万人を殺した男」で罪の大きさを示す。概要欄で「なぜ彼の死は16時間もの間隠されたのか」と、権力の裏側の謎を約束している。</t>
+          <t>独裁者の最後の日々をのぞき見たい。数千万人を死なせた人物が罰を受けたのか確かめ、断罪したい。</t>
         </is>
       </c>
       <c r="K25" s="6" t="inlineStr">
         <is>
-          <t>期間を区切ることで、生涯ではなく最後の数日間の密室劇として見せる。数字（44日間、4500万人）を2つ並べて、重さと具体性を出している。</t>
+          <t>期間を区切ることで、生涯ではなく最後の数日間の密室劇として見せる。数字（44日間、4500万人）を並べて重さを出す。今の中国への感情を呼ぶ題材で、コメント欄は怒りで盛り上がる。</t>
         </is>
       </c>
       <c r="L25" s="6" t="inlineStr">
         <is>
-          <t>怖いもの見たさ、独裁者の結末への関心</t>
+          <t>【コメントに出た感情】強い断罪と怒り。上位はほぼ「英雄ではなく史上最悪」「人類最大の殺人者」「ベッドの上で死ねるなんて」「地獄に堕ちていてほしい」。現代の中国への感情に結びつけるコメントも多い。コメント率1.89/1000は追伸で最高。
+【黙っている多数について】独裁者の最後の日々をのぞき見たい好奇心と、因果応報を確かめたい気持ちと推測。コメント欄は政治的な怒りが強く、熱心層の偏りが特に大きい。</t>
         </is>
       </c>
       <c r="M25" s="6" t="inlineStr">
@@ -2122,56 +2170,58 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>ラヴレンチー・ベリヤ｜数百万人を虐殺した悪魔。スターリンが絶賛したソ連の秘密警察長官【第二次世界大戦】</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=6KhwEtMg3-M</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="n">
+        <v>108893</v>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
           <t>追伸、戦場から失礼します。</t>
         </is>
       </c>
-      <c r="B26" s="3" t="inlineStr">
+      <c r="E26" s="3" t="inlineStr">
         <is>
           <t>https://www.youtube.com/@hello-senjo</t>
         </is>
       </c>
-      <c r="C26" s="4" t="n">
+      <c r="F26" s="4" t="n">
         <v>19600</v>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>ラヴレンチー・ベリヤ｜数百万人を虐殺した悪魔。スターリンが絶賛したソ連の秘密警察長官【第二次世界大戦】</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=6KhwEtMg3-M</t>
-        </is>
-      </c>
-      <c r="F26" s="4" t="n">
-        <v>108893</v>
       </c>
       <c r="G26" s="5" t="n">
         <v>5.6</v>
       </c>
       <c r="H26" s="6" t="inlineStr">
         <is>
-          <t>ソ連史・独裁体制に興味がある層</t>
+          <t>ソ連史や独裁体制に興味がある層。コメントには、ヒムラーやハイドリヒと比べる人、カティンの森などの補足をする詳しい人がいる。アニメ「幼女戦記」の元ネタとして来た人もいる。</t>
         </is>
       </c>
       <c r="I26" s="6" t="inlineStr">
         <is>
-          <t>独裁者の陰にいた「本当に怖い人」の正体を知りたい。仲間に裏切られて終わる悪人の結末を見届けたい。</t>
+          <t>サムネ「大量虐殺した悪魔」「ベリヤの最期」と冷たい目の丸眼鏡の男で、「悪魔と呼ばれた男の正体と最期がわかる」と受け取れる。概要欄で、仲間に裏切られて銃殺されたと結末を明かしている。
+【コメントから】「許してくれ」「お前が消した連中も同じことを言ったはずだ」が最多で、因果応報の結末の約束が強く果たされている（いいね率1.41%）。</t>
         </is>
       </c>
       <c r="J26" s="6" t="inlineStr">
         <is>
-          <t>サムネ「大量虐殺した悪魔」「ベリヤの最期」と冷たい目の丸眼鏡の男で、「悪魔と呼ばれた男の正体と最期がわかる」と受け取れる。タイトル「スターリンが絶賛したソ連の秘密警察長官」で、独裁者の右腕という位置づけを示す。概要欄で、仲間に裏切られて銃殺されたと結末を明かしている。</t>
+          <t>独裁者の陰にいた「本当に怖い人」の正体を知りたい。人を消してきた人物が、同じ方法で消される結末を見届けたい。</t>
         </is>
       </c>
       <c r="K26" s="6" t="inlineStr">
         <is>
-          <t>有名なスターリンの名前を借りて、知名度の低い人物を見せる。秘密警察という陰の権力の怖さで引いている。</t>
+          <t>有名なスターリンの名前を借りて、知名度の低い人物を見せる。秘密警察という陰の権力の怖さと、裏切りで終わる結末で引く。</t>
         </is>
       </c>
       <c r="L26" s="6" t="inlineStr">
         <is>
-          <t>恐怖、権力者の裏側への好奇心</t>
+          <t>【コメントに出た感情】因果応報の納得。最多262いいねは「許してくれ」「お前が消した連中も同じことを言ったはずだ」の一言。「消されて当然」「前任者を処刑した時点でフラグ」と、悪人が同じ方法で消されることへの溜飲。
+【黙っている多数について】独裁者の陰にいた人物の正体を知る好奇心で見ていると推測。いいね率1.41%は毛沢東の回と並んで追伸で最高。</t>
         </is>
       </c>
       <c r="M26" s="6" t="inlineStr">
@@ -2188,56 +2238,58 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>エルヴィン・ロンメル｜ヒトラーに殺された男。伝説の無敵将校「砂漠の狐」の残酷すぎる最期【第二次世界大戦】</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=b0K8lXRPE_g</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="n">
+        <v>184439</v>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
           <t>追伸、戦場から失礼します。</t>
         </is>
       </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="E27" s="3" t="inlineStr">
         <is>
           <t>https://www.youtube.com/@hello-senjo</t>
         </is>
       </c>
-      <c r="C27" s="4" t="n">
+      <c r="F27" s="4" t="n">
         <v>19600</v>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>エルヴィン・ロンメル｜ヒトラーに殺された男。伝説の無敵将校「砂漠の狐」の残酷すぎる最期【第二次世界大戦】</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=b0K8lXRPE_g</t>
-        </is>
-      </c>
-      <c r="F27" s="4" t="n">
-        <v>184439</v>
       </c>
       <c r="G27" s="5" t="n">
         <v>9.4</v>
       </c>
       <c r="H27" s="6" t="inlineStr">
         <is>
-          <t>第二次世界大戦の軍人・名将に興味がある層</t>
+          <t>第二次世界大戦の軍人・名将が好きなミリタリー層。コメント最多は「ロンメルはナチ党員ではない」で、人物の扱いや映像の正確さに厳しい人が多い。</t>
         </is>
       </c>
       <c r="I27" s="6" t="inlineStr">
         <is>
-          <t>有能な英雄が理不尽に殺される悲劇に心を動かされたい。ナチスの中の「まともな人」を知りたい。</t>
+          <t>サムネ「ナチス最高の天才」「ロンメルの最期」と遠くを見る横顔で、「天才と呼ばれた将軍の悲劇的な最期を見られる」と受け取れる。タイトル「ヒトラーに殺された男」で、味方に殺される理不尽を約束する。
+【コメントから】悲劇への共感の声はあるが、「背景の戦車がドイツのものではない」「第一次大戦にこんな戦車はない」と映像の誤りの指摘が目立つ。ミリタリー層には、絵の正確さも約束の一部。</t>
         </is>
       </c>
       <c r="J27" s="6" t="inlineStr">
         <is>
-          <t>サムネ「ナチス最高の天才」「ロンメルの最期」と遠くを見る横顔で、「天才と呼ばれた将軍の悲劇的な最期を見られる」と受け取れる。タイトル「ヒトラーに殺された男」「砂漠の狐」で、味方に殺される理不尽を約束する。概要欄で「敵のチャーチル首相からも賞賛」「暗殺未遂事件への関与を疑われ自害」と、英雄の物語であることを示している。</t>
+          <t>悲劇の英雄に共感したい。「ナチスの中にもまともな軍人がいた」と知って、人物を正しく評価したい。</t>
         </is>
       </c>
       <c r="K27" s="6" t="inlineStr">
         <is>
-          <t>「最悪」ではなく「最高」の人物で、悪人シリーズの中に悲劇の英雄枠を作る。同じ型のまま、動かす感情の種類（怖さ→同情）だけを変えている。</t>
+          <t>「最悪」ではなく「最高」の人物で、悪人シリーズの中に悲劇の英雄枠を作る。同じ型のまま、動かす感情（怖さ→同情）だけを変えている。</t>
         </is>
       </c>
       <c r="L27" s="6" t="inlineStr">
         <is>
-          <t>悲劇への同情、英雄が裏切られる理不尽さへの怒り</t>
+          <t>【コメントに出た感情】擁護と、知識の訂正。最多は「ロンメルはナチ党員ではない」（114いいね）で、「ユダヤ人捕虜を釈放した」「最高の将官はマンシュタイン」など、詳しい人の補足や反論が多い。「背景の戦車がドイツのものではない」「第一次大戦にこんな戦車はない」と、映像の誤りの指摘もある。
+【黙っている多数について】悲劇の英雄への同情で見ていると推測。ミリタリー好きが多く、絵の正確さに厳しい層。</t>
         </is>
       </c>
       <c r="M27" s="6" t="inlineStr">
@@ -2254,56 +2306,58 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>アドルフ・アイヒマン｜500万人を殺した男。ナチスが最も恐れた男の残酷すぎる最期【第二次世界大戦】</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=bHrzNTlZntI</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="n">
+        <v>245871</v>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
           <t>追伸、戦場から失礼します。</t>
         </is>
       </c>
-      <c r="B28" s="3" t="inlineStr">
+      <c r="E28" s="3" t="inlineStr">
         <is>
           <t>https://www.youtube.com/@hello-senjo</t>
         </is>
       </c>
-      <c r="C28" s="4" t="n">
+      <c r="F28" s="4" t="n">
         <v>19600</v>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>アドルフ・アイヒマン｜500万人を殺した男。ナチスが最も恐れた男の残酷すぎる最期【第二次世界大戦】</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=bHrzNTlZntI</t>
-        </is>
-      </c>
-      <c r="F28" s="4" t="n">
-        <v>245871</v>
       </c>
       <c r="G28" s="5" t="n">
         <v>12.5</v>
       </c>
       <c r="H28" s="6" t="inlineStr">
         <is>
-          <t>第二次世界大戦・ナチスに興味がある層</t>
+          <t>ナチスやホロコーストに関心がある層。コメント最多は「平和な時代なら目立たない凡人が大半」で、「悪の凡庸さ」を考えたい人が多い。一方で、今のイスラエルに重ねる人や陰謀論を書く人もいる。</t>
         </is>
       </c>
       <c r="I28" s="6" t="inlineStr">
         <is>
-          <t>逃げた悪人が最後に捕まる「正義の結末」を見届けたい。普通に見える人が大量殺人に関わった理由を知りたい。</t>
+          <t>サムネ「ナチスが最も恐れた男」「アイヒマンの最期」と薄笑いの肖像で、「恐れられた男の最期」を見届けられると受け取れる。概要欄で「アルゼンチンに逃亡した彼に訪れた悲劇」と、逃亡から捕まるまでのサスペンスを約束している。
+【コメントから】「ただの一生懸命な役人」という見方が多く、サムネの「最も恐れた男」より「普通の人の怖さ」が刺さっている。</t>
         </is>
       </c>
       <c r="J28" s="6" t="inlineStr">
         <is>
-          <t>サムネ「ナチスが最も恐れた男」「アイヒマンの最期」と薄笑いの肖像で、「恐れられた男の最期」を見届けられると受け取れる。タイトル「500万人を殺した男」で罪の大きさを示す。概要欄で「アルゼンチンに逃亡した彼に訪れた悲劇」と、逃亡から捕まるまでのサスペンスを約束している。</t>
+          <t>普通の人が大量殺人を担う怖さを理解したい。逃げた悪人が捕まる結末を見届けたい。</t>
         </is>
       </c>
       <c r="K28" s="6" t="inlineStr">
         <is>
-          <t>定番の型。概要欄で「逃亡」という追跡劇の要素を出し、ただの人物紹介ではなく物語として見せている。</t>
+          <t>定番の型。概要欄で逃亡という追跡劇の要素を出し、人物紹介ではなく物語として見せる。題材が今の国際情勢に近く、コメント欄が政治的になりやすい。</t>
         </is>
       </c>
       <c r="L28" s="6" t="inlineStr">
         <is>
-          <t>恐怖、正義が下されるかどうかへの関心</t>
+          <t>【コメントに出た感情】「悪の凡庸さ」への気づきと、現代への重ね合わせ。最多は「平和な時代なら目立たない凡人が大半」。「ただの一生懸命な役人」「今の日本の官僚みたいなもの」と、普通の人が悪を担う怖さに反応している。今のイスラエルと重ねるコメントや、陰謀論的なコメントもある。
+【黙っている多数について】逃亡と逮捕の物語への興味で見ていると推測。コメント欄は政治的な主張が多く、熱心層の偏りが大きい。</t>
         </is>
       </c>
       <c r="M28" s="6" t="inlineStr">
@@ -2320,46 +2374,47 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>スターリンの最期！1000万人を殺した男の残酷すぎる7日間【第二次世界大戦】</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Rqgbenusa_8</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="n">
+        <v>510806</v>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
           <t>追伸、戦場から失礼します。</t>
         </is>
       </c>
-      <c r="B29" s="3" t="inlineStr">
+      <c r="E29" s="3" t="inlineStr">
         <is>
           <t>https://www.youtube.com/@hello-senjo</t>
         </is>
       </c>
-      <c r="C29" s="4" t="n">
+      <c r="F29" s="4" t="n">
         <v>19600</v>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>スターリンの最期！1000万人を殺した男の残酷すぎる7日間【第二次世界大戦】</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=Rqgbenusa_8</t>
-        </is>
-      </c>
-      <c r="F29" s="4" t="n">
-        <v>510806</v>
       </c>
       <c r="G29" s="5" t="n">
         <v>26.1</v>
       </c>
       <c r="H29" s="6" t="inlineStr">
         <is>
-          <t>近現代史・独裁者に興味がある層</t>
+          <t>近現代史・独裁者に興味がある層（51万再生）。コメントは「楽な死に方しやがって」などの断罪と、プーチンや北朝鮮の指導者に重ねる人が中心。</t>
         </is>
       </c>
       <c r="I29" s="6" t="inlineStr">
         <is>
-          <t>恐れられた独裁者が、最後は誰にも助けられずに死んでいく皮肉を見届けたい。</t>
+          <t>サムネ「スターリンの／最期の7日間」の大きな文字で、「独裁者の最後の1週間に何が起きたかを見られる」と受け取れる。概要欄で「医師が呼ばれるまで13時間の空白」「側近たちの思惑」と、側近に見捨てられた密室劇を約束している。
+【コメントから】「人を大事にしない独裁者は、人からも大切にされない」が最多で、見捨てられた最期という約束が、教訓として受け取られている。</t>
         </is>
       </c>
       <c r="J29" s="6" t="inlineStr">
         <is>
-          <t>サムネ「スターリンの／最期の7日間」の大きな文字で、「独裁者の最後の1週間に何が起きたかを見られる」と受け取れる。タイトル「1000万人を殺した男」で罪の大きさを足す。概要欄で「医師が呼ばれるまでに13時間もの空白」「側近たちの思惑とは？」と、側近に見捨てられた密室劇を約束している。</t>
+          <t>恐れられた独裁者が、誰にも助けられずに死ぬ皮肉を見届けたい。今の独裁者もこうなると思いたい。</t>
         </is>
       </c>
       <c r="K29" s="6" t="inlineStr">
@@ -2369,7 +2424,8 @@
       </c>
       <c r="L29" s="6" t="inlineStr">
         <is>
-          <t>怖いもの見たさ、独裁者が見捨てられる皮肉</t>
+          <t>【コメントに出た感情】因果応報と、現代の独裁者への投影。「人を大事にしない独裁者は、人からも大切にされない」（553いいね）、「楽な死に方しやがって」（525いいね）、「チャウセスクみたいなのが最高」など、苦しんでほしいという断罪が中心。「プーチンも同じく」「北朝鮮の同志も」と、今の独裁者に重ねる声も多い。
+【黙っている多数について】独裁者が誰にも助けられずに死ぬ皮肉を見届けたい気持ちと推測。51万再生でいいね率1.05%と、追伸の中で反応が強い。</t>
         </is>
       </c>
       <c r="M29" s="6" t="inlineStr">
@@ -2386,56 +2442,58 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>ムッソリーニの最期！逆さ吊りで公開処刑されるまでの残酷すぎる10日間【第二次世界大戦】</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=ANxbHSdWPUg</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="n">
+        <v>210398</v>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
           <t>追伸、戦場から失礼します。</t>
         </is>
       </c>
-      <c r="B30" s="3" t="inlineStr">
+      <c r="E30" s="3" t="inlineStr">
         <is>
           <t>https://www.youtube.com/@hello-senjo</t>
         </is>
       </c>
-      <c r="C30" s="4" t="n">
+      <c r="F30" s="4" t="n">
         <v>19600</v>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>ムッソリーニの最期！逆さ吊りで公開処刑されるまでの残酷すぎる10日間【第二次世界大戦】</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=ANxbHSdWPUg</t>
-        </is>
-      </c>
-      <c r="F30" s="4" t="n">
-        <v>210398</v>
       </c>
       <c r="G30" s="5" t="n">
         <v>10.7</v>
       </c>
       <c r="H30" s="6" t="inlineStr">
         <is>
-          <t>第二次世界大戦・独裁者に興味がある層</t>
+          <t>第二次世界大戦・独裁者に興味がある層。コメントには、結末（逆さ吊り）は知っていた人、正確さを気にする人（「処刑後に逆さ吊りされたのでは」）、今の政治家を名指しする人が混ざる。</t>
         </is>
       </c>
       <c r="I30" s="6" t="inlineStr">
         <is>
-          <t>独裁者が民衆に裁かれる劇的な結末を見届けたい。</t>
+          <t>サムネ「ムッソリーニの／最期の10日間」と側近に囲まれた尊大な顔で、「最後の10日間の転落を見られる」と受け取れる。タイトル「逆さ吊りで公開処刑」で結末を先に明かし、概要欄で「法を無視した私刑と正義」と、見た後に考えさせる問いを置く。
+【コメントから】「逆さ吊りのところしか知らなかったので勉強になった」と、結末に至る過程の約束は果たされている。「法による裁きが必要」と、概要欄の問いに答える声もある。</t>
         </is>
       </c>
       <c r="J30" s="6" t="inlineStr">
         <is>
-          <t>サムネ「ムッソリーニの／最期の10日間」と側近に囲まれた尊大な顔で、「最後の10日間の転落を見られる」と受け取れる。タイトル「逆さ吊りで公開処刑」で、結末の衝撃的な場面を先に明かす。概要欄で「法を無視した私刑と正義が物議を醸す」と、見た後に考えさせる問いも置いている。</t>
+          <t>結末を知っている独裁者の、そこに至る過程を確かめたい。独裁者の哀れな最期を見て、権力のむなしさを感じたい。</t>
         </is>
       </c>
       <c r="K30" s="6" t="inlineStr">
         <is>
-          <t>結末（逆さ吊り）を先に明かし、「そこに至るまで」を見させる。スターリン回と同じ「〇〇の／最期の〇日間」型で、シリーズの見た目をそろえている。</t>
+          <t>結末を先に明かし、「そこに至るまで」を見させる。スターリン回と同じ「〇〇の／最期の〇日間」型で、シリーズの見た目をそろえる。</t>
         </is>
       </c>
       <c r="L30" s="6" t="inlineStr">
         <is>
-          <t>衝撃、怖いもの見たさ</t>
+          <t>【コメントに出た感情】独裁者の哀れさへの複雑な感情。「愛人と最期を迎えたエヴァとクララはすごい」が最多で、「独裁者の最期はみんな哀れ」「逆さ吊りのところしか知らなかったので勉強になった」と続く。「処刑後に逆さ吊りされたのでは」という訂正、「法による裁きが必要」という意見もある。現代の政治家を名指しする書き込みも多い。
+【黙っている多数について】結末を知っている人が、そこに至る10日間を確かめたい気持ちで見ていると推測。</t>
         </is>
       </c>
       <c r="M30" s="6" t="inlineStr">
@@ -2452,56 +2510,58 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>ヒトラーの最期！最恐独裁者の悲惨すぎる最後の48時間【第二次世界大戦】</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=PINVVV6JeGg</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="n">
+        <v>243970</v>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
           <t>追伸、戦場から失礼します。</t>
         </is>
       </c>
-      <c r="B31" s="3" t="inlineStr">
+      <c r="E31" s="3" t="inlineStr">
         <is>
           <t>https://www.youtube.com/@hello-senjo</t>
         </is>
       </c>
-      <c r="C31" s="4" t="n">
+      <c r="F31" s="4" t="n">
         <v>19600</v>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>ヒトラーの最期！最恐独裁者の悲惨すぎる最後の48時間【第二次世界大戦】</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=PINVVV6JeGg</t>
-        </is>
-      </c>
-      <c r="F31" s="4" t="n">
-        <v>243970</v>
       </c>
       <c r="G31" s="5" t="n">
         <v>12.4</v>
       </c>
       <c r="H31" s="6" t="inlineStr">
         <is>
-          <t>第二次世界大戦・ヒトラーに興味がある層（最も広い入口）</t>
+          <t>第二次世界大戦・ヒトラーに興味がある、最も広い層。コメントには、映画『ヒトラー 〜最期の12日間〜』を知っている人や、そのネットのパロディを知る人が多い。</t>
         </is>
       </c>
       <c r="I31" s="6" t="inlineStr">
         <is>
-          <t>誰もが知る独裁者の、まだ知らない最後の場面を知りたい。</t>
+          <t>サムネ「ヒトラー最後の48時間」と四隅の「2通の遺言書を残す」「突然エヴァと結婚する」「青酸カリで愛犬を毒殺」「ヘルマンを処刑する」で、「地下壕の最後の2日間に起きた奇妙な出来事を具体的に見られる」と受け取れる。
+【コメントから】「愛犬ブロンディは生かしてほしかった」が複数あり、四隅の見どころの中でも犬の話が一番刺さった。「文字のフォントが雰囲気に合わない」という指摘もある。</t>
         </is>
       </c>
       <c r="J31" s="6" t="inlineStr">
         <is>
-          <t>サムネ「ヒトラー最後の48時間」と四隅の「2通の遺言書を残す」「突然エヴァと結婚する」「青酸カリで愛犬を毒殺」「ヘルマンを処刑する」で、「地下壕の最後の2日間に起きた奇妙な出来事を具体的に見られる」と受け取れる。見どころを4つ先に見せる約束で、概要欄も同じ見どころを並べている。</t>
+          <t>誰もが知る独裁者の、まだ知らない最後の場面を知りたい。皮肉で笑いたい（最多は「千年帝国が12年で終わった」）。</t>
         </is>
       </c>
       <c r="K31" s="6" t="inlineStr">
         <is>
-          <t>一番知名度の高い人物で、チャンネルの入口を作った初期の回。見どころを四隅に並べて「知らない話がある」と示す。後の回では、これを上下の帯＋肖像の型に絞り込んでいる。</t>
+          <t>一番知名度の高い人物で、チャンネルの入口を作った初期の回。見どころを四隅に並べて「知らない話がある」と示す。後の回ではこれを上下の帯＋肖像の型に絞り込んでいる。</t>
         </is>
       </c>
       <c r="L31" s="6" t="inlineStr">
         <is>
-          <t>怖いもの見たさ、緊迫感</t>
+          <t>【コメントに出た感情】皮肉の笑いと、犬への悲しみ。最多348いいねは「千年帝国と言っていたのに12年で終わった。988年足りない」。「愛犬ブロンディは生かしてほしかった」系のコメントが複数あり、サムネ四隅の「青酸カリで愛犬を毒殺」が強く刺さっている。「子供に罪はなかった」も同じ感情。「文字のフォントが雰囲気に合わない」という指摘もある。
+【黙っている多数について】誰もが知る独裁者の、知らない最後の場面を知りたい好奇心と推測。</t>
         </is>
       </c>
       <c r="M31" s="6" t="inlineStr">

--- a/youtube-world-history-research/output/video_analysis_sheet_filled.xlsx
+++ b/youtube-world-history-research/output/video_analysis_sheet_filled.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>見たら何が得られると約束しているか（サムネ＋タイトル＋概要欄から視聴者が受け取る約束）</t>
+          <t>見たら何が得られると約束しているか（サムネ＋タイトルから視聴者が受け取る約束）</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
@@ -572,8 +572,8 @@
       </c>
       <c r="I2" s="6" t="inlineStr">
         <is>
-          <t>サムネ「最強が負けた日」と落馬する騎馬武者で「無敵の軍団が負けた現場」を見せ、タイトルで主語がモンゴル、舞台がヨーロッパだと明かす。合わせると「モンゴルを止めたもっと強い何か（と理由）がわかる」と受け取れる。概要欄「最強には最強をぶつけんだよ。」で、強者どうしの対決を見る期待に変える。
-【コメントから】マムルーク朝の偽装退却に「鳥肌」という声があり、対決の約束は果たされている。地理や補給の補足が多く、答えの「なぜ」にはまだ語りたい余地が残る。</t>
+          <t>サムネ「最強が負けた日」と落馬する騎馬武者で「無敵の軍団が負けた現場」を見せ、タイトルで主語がモンゴル、舞台がヨーロッパだと明かす。合わせると「モンゴルを止めたもっと強い何か（と理由）がわかる」と受け取れる。
+【コメントから】マムルーク朝の偽装退却に「鳥肌」という声があり、「もっと強い何か」との対決という約束は果たされている。地理や補給の補足が多く、答えの「なぜ」にはまだ語りたい余地が残る。</t>
         </is>
       </c>
       <c r="J2" s="6" t="inlineStr">
@@ -640,8 +640,8 @@
       </c>
       <c r="I3" s="6" t="inlineStr">
         <is>
-          <t>タイトル「立場逆転」「狩られる側に」と、サムネの怯えるモンゴル兵と鬼の形相の武者で、「攻めてきた側が日本でどれだけ怖い目にあったかを、笑いながら追体験できる」と受け取れる。概要欄で「神風だけで勝負が決まったわけではない」と、通説を正すことも約束している。
-【コメントから】「元軍がうちの大将の首を掲げたら、逆に取り返そうと襲ってきた」などの逸話への反応が多く、追体験と通説の訂正の両方が果たされている。</t>
+          <t>タイトル「立場逆転」「狩られる側に」と、サムネの怯えるモンゴル兵と鬼の形相の武者で、「攻めてきた側が日本でどれだけ怖い目にあったかを、笑いながら追体験できる」と受け取れる。
+【コメントから】「元軍がうちの大将の首を掲げたら、逆に取り返そうと襲ってきた」などの逸話への反応が多く、追体験の約束は果たされている。「台風で勝ったと習った」という通説の見直しとしても受け取られている。</t>
         </is>
       </c>
       <c r="J3" s="6" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="I4" s="6" t="inlineStr">
         <is>
-          <t>サムネ「海外から見た倭寇、怖すぎる」と「ただのゴロツキだよ？」「じゃあなんでそんな強ぇんだよ…」の会話で、「被害を受けた側から見た倭寇のヤバさと、ゴロツキがなぜ強かったか」がわかると受け取れる。概要欄「気の毒すぎる」で、被害側に同情しながら笑って見る視点を指定している。
+          <t>サムネ「海外から見た倭寇、怖すぎる」と「ただのゴロツキだよ？」「じゃあなんでそんな強ぇんだよ…」の会話で、「被害を受けた側から見た倭寇のヤバさと、ゴロツキがなぜ強かったか」がわかると受け取れる。
 【コメントから】「賊にしては戦術が天才すぎる」と、強さの理由の約束は果たされている。ただ、上位のコメントは中身より「後期倭寇は日本人ではなかった」という話題に向かった。</t>
         </is>
       </c>
@@ -844,8 +844,8 @@
       </c>
       <c r="I6" s="6" t="inlineStr">
         <is>
-          <t>サムネ「実在した異常な国11選」と4分割の絵で、「信じられないけど本当にあった国を11個まとめて見られる」と受け取れる。概要欄「私も独立国家作ろうかな。」で、自分でも作れそうと思える軽いノリを約束している。
-【コメントから】「私も建国できる気がしてきました」が最多で、軽いノリの約束がそのまま返ってきている。</t>
+          <t>サムネ「実在した異常な国11選」と4分割の絵で、「信じられないけど本当にあった国を11個まとめて見られる」と受け取れる。
+【コメントから】「私も建国できる気がしてきました」が最多で、「異常な国」を怖がるより、自分にもできそうだと軽く楽しむ受け取り方をされている。</t>
         </is>
       </c>
       <c r="J6" s="6" t="inlineStr">
@@ -912,7 +912,7 @@
       </c>
       <c r="I7" s="6" t="inlineStr">
         <is>
-          <t>タイトル「致〇率99%」と、サムネ「先頭の兵士って、何考えてたの？」「●ぬよ？」「ですよね。」の会話で、「ほぼ死ぬとわかって突っ込んだ兵士の本音と、そうさせた仕組みがわかる」と受け取れる。概要欄「私はどんな理由があっても先頭にはなりたくないタイプです。」で、普通の人の目線で見ると約束している。
+          <t>タイトル「致〇率99%」と、サムネ「先頭の兵士って、何考えてたの？」「●ぬよ？」「ですよね。」の会話で、「ほぼ死ぬとわかって突っ込んだ兵士の本音と、そうさせた仕組みがわかる」と受け取れる。
 【コメントから】「名誉の仕組みは渡す側の損失がほぼない、よく考えられたシステム」が6,347いいねで最多。仕組みがわかるという約束は、強く果たされている。</t>
         </is>
       </c>
@@ -1048,8 +1048,8 @@
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
-          <t>サムネ「なぜ軍人は機関銃を嫌ったのか？」と、不機嫌な将校の「使わねぇよ」「●●だから。」で、「軍人が最強の兵器を拒んだ、意外で人間くさい理由がわかる」と受け取れる。概要欄「これは現代でもあるある。」で、「今の職場にも通じる話」という約束に広げている。
-【コメントから】今の組織に重ねるコメントが上位に並び、「現代でもあるある」の約束は果たされている。補給の問題など、動画が触れきれていない理由を足す人も多い。</t>
+          <t>サムネ「なぜ軍人は機関銃を嫌ったのか？」と、不機嫌な将校の「使わねぇよ」「●●だから。」で、「軍人が最強の兵器を拒んだ、意外で人間くさい理由がわかる」と受け取れる。
+【コメントから】今の組織に重ねるコメントが上位に並ぶ。サムネとタイトルが約束した「意外な理由」を超えて、視聴者が自分で「今の職場にもある話」として受け取っている。補給の問題など、動画が触れきれていない理由を足す人も多い。</t>
         </is>
       </c>
       <c r="J9" s="6" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="I10" s="6" t="inlineStr">
         <is>
-          <t>サムネ「※中世の歩兵、怖すぎ問題」と「こ、降参…」「じゃ●すね？」の会話で、「騎士の名誉のルールが通じない歩兵が、戦場をどう変えたかを見られる」と受け取れる。概要欄「戦争にも規律って必要なんだな。。。」で、降参や身代金のルールがなくなった怖さが中身だとわかる。
+          <t>サムネ「※中世の歩兵、怖すぎ問題」と「こ、降参…」「じゃ●すね？」の会話で、「騎士の名誉のルールが通じない歩兵が、戦場をどう変えたかを見られる」と受け取れる。タイトルの「”地獄”に変えた」で、その変化がどれほど残酷だったかを予告する。
 【コメントから】「槍を構えて騎士の突撃を受けるのはものすごい勇気」など、現場の怖さを想像するコメントが最多で、約束は果たされている。</t>
         </is>
       </c>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="I13" s="6" t="inlineStr">
         <is>
-          <t>サムネ「細長い国ではどう暮らしてる？」と3国の地図で、「細長い国の暮らしの大変さを見られる」と受け取れる。概要欄で具体的な苦労（運転しても端から端まで1週間など）を予告している。
+          <t>サムネ「細長い国ではどう暮らしてる？」と3国の地図で、「細長い国の暮らしの大変さを見られる」と受け取れる。タイトルの「日本より細長い」「過酷な宿命と驚きの共通点」で、日本との比較と苦労話を足す。
 【コメントから】「こういうの見たかった」「気楽に見られる」という声はあるが、「台本か動画のどちらかはそれなりの質に」と、中身の物足りなさも指摘されている。</t>
         </is>
       </c>
@@ -1592,8 +1592,8 @@
       </c>
       <c r="I17" s="6" t="inlineStr">
         <is>
-          <t>サムネ「アラスカをロシアはなぜ売った？」と「$7,200,000」の矢印で、「信じられない安値で売った理由がわかる」と受け取れる。概要欄で「本当に愚かだったから手放したのか？」と、通説をひっくり返すと約束している。
-【コメントから】最多の「宝の山を捨てたというより、守れない土地を手放しただけ」は、概要欄の問いにそのまま答えている。約束は果たされているが、「語尾が無音化して聞きにくい」「トランジションが多すぎる」と作りへの不満がある（いいね率0.24%）。</t>
+          <t>サムネ「アラスカをロシアはなぜ売った？」と「$7,200,000」の矢印で、「信じられない安値で売った理由がわかる」と受け取れる。タイトルの「世界最大の宝の山」「坪単価0.2円」で損の大きさをあおり、サムネで正体（アラスカ）を明かす。
+【コメントから】最多の「宝の山を捨てたというより、守れない土地を手放しただけ」は、「なぜ売った？」への視聴者自身の答えになっている。約束は果たされているが、「語尾が無音化して聞きにくい」「トランジションが多すぎる」と作りへの不満がある（いいね率0.24%）。</t>
         </is>
       </c>
       <c r="J17" s="6" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="I18" s="6" t="inlineStr">
         <is>
-          <t>サムネ「なぜ別の国になったのか？」「言葉も近い、隣同士なのに…」と2色の古地図で、「双子のような2国が分かれたドラマを見られる」と受け取れる。概要欄で「一本のオペラ」が独立のきっかけという意外な事実を予告している。
+          <t>サムネ「なぜ別の国になったのか？」「言葉も近い、隣同士なのに…」と2色の古地図で、「双子のような2国が分かれたドラマを見られる」と受け取れる。タイトルの「引き裂かれた歴史」で、悲劇のドラマを約束する。
 【コメントから】「鎖国の日本がオランダとだけ交易した理由がわかった」など、知識がつながった喜びが多く、約束は果たされている。</t>
         </is>
       </c>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="I20" s="6" t="inlineStr">
         <is>
-          <t>サムネ「イベリア半島の『二分割』という歴史的謎」と赤と青の地図で、「同じ半島に2つの国がある理由がわかる」と受け取れる。概要欄で「大国スペインはなぜ小さなポルトガルを飲み込めなかったのか」と、強い側が勝てなかった謎に絞っている。
+          <t>サムネ「イベリア半島の『二分割』という歴史的謎」と赤と青の地図で、「同じ半島に2つの国がある理由がわかる」と受け取れる。タイトルの「一つ屋根の下に二つの家族？」で、国の話を家族の話のように身近にすると約束する。
 【コメントから】「スペイン自体が多様すぎて統合が難しい」という補足が最多で、視聴者は答えをもう一段深く知りたがっている。</t>
         </is>
       </c>
@@ -2068,7 +2068,7 @@
       </c>
       <c r="I24" s="6" t="inlineStr">
         <is>
-          <t>サムネ「ナチス史上最悪の男」「ハイドリヒの最期」で、「最悪の男がどう死んだか」を見届けられると受け取れる。概要欄で「38歳の若さで暗殺」と結末の種類を明かしている。
+          <t>サムネ「ナチス史上最悪の男」「ハイドリヒの最期」で、「最悪の男がどう死んだか」を見届けられると受け取れる。タイトルの「数百万人を虐殺した悪魔」「ナチスが最も恐れた男」で、身内からも恐れられるほどの怖さを約束する。
 【コメントから】「有能すぎる」「この能力をいい方向に生かせなかったのか」と、優秀さと悪が結びつく怖さへの反応が多く、最期よりも人物像の方が刺さっている。</t>
         </is>
       </c>
@@ -2136,8 +2136,8 @@
       </c>
       <c r="I25" s="6" t="inlineStr">
         <is>
-          <t>サムネ「残酷すぎる44日間」「毛沢東の最期」と穏やかな薄笑いの肖像で、「最後の44日間に起きた残酷な出来事を見られる」と受け取れる。概要欄で「なぜ彼の死は16時間も隠されたのか」と、権力の裏側の謎を約束している。
-【コメントから】「16時間の空白って意外と少ない」「4人組の運命はそうだったのか、勉強になった」と、裏側の謎の約束には反応がある。ただ多くは中身より人物への断罪。</t>
+          <t>サムネ「残酷すぎる44日間」「毛沢東の最期」と穏やかな薄笑いの肖像で、「最後の44日間に起きた残酷な出来事を見られる」と受け取れる。タイトルの「4500万人を殺した男」で、罪の大きさと、その男の最期という落差を約束する。
+【コメントから】「16時間の空白って意外と少ない」「4人組の運命はそうだったのか、勉強になった」と、最後の日々の裏側への反応がある。ただ多くは中身より人物への断罪。</t>
         </is>
       </c>
       <c r="J25" s="6" t="inlineStr">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="I26" s="6" t="inlineStr">
         <is>
-          <t>サムネ「大量虐殺した悪魔」「ベリヤの最期」と冷たい目の丸眼鏡の男で、「悪魔と呼ばれた男の正体と最期がわかる」と受け取れる。概要欄で、仲間に裏切られて銃殺されたと結末を明かしている。
+          <t>サムネ「大量虐殺した悪魔」「ベリヤの最期」と冷たい目の丸眼鏡の男で、「悪魔と呼ばれた男の正体と最期がわかる」と受け取れる。タイトルの「スターリンが絶賛したソ連の秘密警察長官」で、独裁者の右腕という位置づけを示す。
 【コメントから】「許してくれ」「お前が消した連中も同じことを言ったはずだ」が最多で、因果応報の結末の約束が強く果たされている（いいね率1.41%）。</t>
         </is>
       </c>
@@ -2340,7 +2340,7 @@
       </c>
       <c r="I28" s="6" t="inlineStr">
         <is>
-          <t>サムネ「ナチスが最も恐れた男」「アイヒマンの最期」と薄笑いの肖像で、「恐れられた男の最期」を見届けられると受け取れる。概要欄で「アルゼンチンに逃亡した彼に訪れた悲劇」と、逃亡から捕まるまでのサスペンスを約束している。
+          <t>サムネ「ナチスが最も恐れた男」「アイヒマンの最期」と薄笑いの肖像で、「恐れられた男の最期」を見届けられると受け取れる。タイトルの「500万人を殺した男」で、罪の大きさを示す。
 【コメントから】「ただの一生懸命な役人」という見方が多く、サムネの「最も恐れた男」より「普通の人の怖さ」が刺さっている。</t>
         </is>
       </c>
@@ -2408,8 +2408,8 @@
       </c>
       <c r="I29" s="6" t="inlineStr">
         <is>
-          <t>サムネ「スターリンの／最期の7日間」の大きな文字で、「独裁者の最後の1週間に何が起きたかを見られる」と受け取れる。概要欄で「医師が呼ばれるまで13時間の空白」「側近たちの思惑」と、側近に見捨てられた密室劇を約束している。
-【コメントから】「人を大事にしない独裁者は、人からも大切にされない」が最多で、見捨てられた最期という約束が、教訓として受け取られている。</t>
+          <t>サムネ「スターリンの／最期の7日間」の大きな文字で、「独裁者の最後の1週間に何が起きたかを見られる」と受け取れる。タイトルの「1000万人を殺した男の残酷すぎる7日間」で、罪の大きさと最後の1週間の残酷さを約束する。
+【コメントから】「人を大事にしない独裁者は、人からも大切にされない」が最多で、最後の1週間の話が、独裁者への教訓として受け取られている。</t>
         </is>
       </c>
       <c r="J29" s="6" t="inlineStr">
@@ -2476,8 +2476,8 @@
       </c>
       <c r="I30" s="6" t="inlineStr">
         <is>
-          <t>サムネ「ムッソリーニの／最期の10日間」と側近に囲まれた尊大な顔で、「最後の10日間の転落を見られる」と受け取れる。タイトル「逆さ吊りで公開処刑」で結末を先に明かし、概要欄で「法を無視した私刑と正義」と、見た後に考えさせる問いを置く。
-【コメントから】「逆さ吊りのところしか知らなかったので勉強になった」と、結末に至る過程の約束は果たされている。「法による裁きが必要」と、概要欄の問いに答える声もある。</t>
+          <t>サムネ「ムッソリーニの／最期の10日間」と側近に囲まれた尊大な顔で、「最後の10日間の転落を見られる」と受け取れる。タイトル「逆さ吊りで公開処刑」で結末を先に明かし、「そこに至るまで」を見せると約束する。
+【コメントから】「逆さ吊りのところしか知らなかったので勉強になった」と、結末に至る過程の約束は果たされている。「法による裁きが必要」という意見もある。</t>
         </is>
       </c>
       <c r="J30" s="6" t="inlineStr">
